--- a/eval_results.xlsx
+++ b/eval_results.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>77.78</v>
+        <v>88.89</v>
       </c>
       <c r="L3" t="n">
-        <v>29.73</v>
+        <v>27.78</v>
       </c>
       <c r="M3" t="n">
-        <v>95</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="4">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -639,22 +639,22 @@
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>2.67</v>
+        <v>2.78</v>
       </c>
       <c r="K4" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="M4" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -676,28 +676,28 @@
         <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G5" t="n">
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>2.56</v>
+        <v>2.89</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="M5" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="6">
@@ -713,13 +713,13 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="G6" t="n">
         <v>3</v>
@@ -728,19 +728,19 @@
         <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="K6" t="n">
-        <v>2.33</v>
+        <v>2.89</v>
       </c>
       <c r="L6" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="M6" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="7">
@@ -767,10 +767,8 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="F7" t="n">
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -853,76 +851,242 @@
         <v>100</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Avg Latency (s)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="C9" t="n">
+        <v>22.32</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I9" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="K9" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="M9" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>N items</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>severe</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>6</v>
+          <t>Avg Memory (MB)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>622.6</v>
+      </c>
+      <c r="C10" t="n">
+        <v>683.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>642.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>642.6</v>
+      </c>
+      <c r="F10" t="n">
+        <v>638.4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>638.6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>547.3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>519</v>
+      </c>
+      <c r="J10" t="n">
+        <v>282</v>
+      </c>
+      <c r="K10" t="n">
+        <v>288.1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>555.8</v>
+      </c>
+      <c r="M10" t="n">
+        <v>558.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>moderate</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>20</v>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>N items</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>minor</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>no_record</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>multi_drug</t>
+          <t>minor</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>no_record</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>multi_drug</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B18" t="n">
         <v>50</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>System Info</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>python_version</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>3.11.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>macOS-26.4.1-arm64-arm-64bit</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cpu_count</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>total_ram_gb</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>eval_date</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-04-28 10:40</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -944,27 +1108,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:V51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="38" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
-    <col width="38" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="38" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="38" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1000,60 +1168,80 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>LLM Latency(s)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LLM Memory(MB)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>LLM Hallucination</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>LLM Faithfulness</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>LLM Completeness</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>LLM Sev Acc</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>LLM No-Rec Refusal</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>LLM Reasoning</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>RAG Latency(s)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>RAG Memory(MB)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>RAG Hallucination</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RAG Faithfulness</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RAG Completeness</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>RAG Sev Acc</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>RAG No-Rec Refusal</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>RAG Reasoning</t>
         </is>
@@ -1083,41 +1271,53 @@
       <c r="E2" t="b">
         <v>1</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" t="b">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>3.742</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>304.5</v>
       </c>
       <c r="I2" t="n">
         <v>2</v>
       </c>
       <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>The AI response inaccurately states the interaction risk as moderate instead of severe, which is a key detail that misleads about the severity of the interaction.</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3</v>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>The AI response inaccurately categorizes the interaction as moderate instead of severe, which is a key detail missing from the ground truth. While it mentions potential risks, it does not fully align with the severity indicated in the DrugBank description.</t>
+        </is>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>40.194</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the severe interaction between Enalapril and Azathioprine, including the mechanisms and clinical advice, with no unsupported claims.</t>
+        <v>700</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the severe interaction between Enalapril and Azathioprine, including the mechanism and clinical advice, with no unsupported claims.</t>
         </is>
       </c>
     </row>
@@ -1145,39 +1345,51 @@
       <c r="E3" t="b">
         <v>1</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" t="b">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>3.814</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>700</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>The AI response incorrectly states the interaction severity as moderate instead of severe, and while it mentions renal impairment, it does not address the specific risks of myelosuppression, anemia, and severe leukopenia as noted in the ground truth.</t>
         </is>
       </c>
-      <c r="M3" t="n">
-        <v>3</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3</v>
-      </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>10.679</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+        <v>701.5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>The AI response accurately reflects the DrugBank ground truth regarding the severe interaction between Fosinopril and Azathioprine, including the associated risks and clinical advice, without any unsupported claims.</t>
         </is>
@@ -1207,41 +1419,53 @@
       <c r="E4" t="b">
         <v>1</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" t="b">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>3.406</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>701.5</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>The response incorrectly states that the interaction severity is moderate instead of severe, and it introduces unsupported claims about renal impairment without backing from the ground truth.</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3</v>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>The AI response downplays the severity of the interaction, incorrectly suggesting a moderate concern instead of the severe risk stated in the ground truth. It also introduces unsupported claims about renal impairment without addressing the specific risks of myelosuppression, anemia, and severe leukopenia.</t>
+        </is>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>15.489</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the severe interaction between Azathioprine and Quinaprilat, including the associated risks and clinical advice.</t>
+        <v>701.6</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the severe interaction between Azathioprine and Quinaprilat, including the mechanism and clinical advice, with no unsupported claims.</t>
         </is>
       </c>
     </row>
@@ -1269,39 +1493,51 @@
       <c r="E5" t="b">
         <v>1</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" t="b">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>3.592</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>701.6</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>The AI response incorrectly states that there are no major interactions, contradicting the DrugBank ground truth which indicates a severe interaction. It also fails to mention the specific risks of myelosuppression, anemia, and severe leukopenia.</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>3</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3</v>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>The AI response incorrectly states that there are no major drug interactions, contradicting the DrugBank ground truth which indicates a severe interaction. It also fails to mention the specific risks of myelosuppression, anemia, and severe leukopenia.</t>
+        </is>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>13.868</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+        <v>702</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>The AI response accurately reflects the DrugBank ground truth regarding the severe interaction between Azathioprine and Enalaprilat, including the mechanism and clinical advice, with no unsupported claims.</t>
         </is>
@@ -1331,41 +1567,53 @@
       <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" t="b">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>1.765</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>682.1</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
       <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>The AI response incorrectly states that there are no well-documented interactions, contradicting the DrugBank ground truth which indicates a severe interaction. It also fails to mention the specific risks associated with the interaction.</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>3</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3</v>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>The AI response incorrectly states that there are no well-documented interactions, contradicting the DrugBank ground truth which indicates a severe interaction. Additionally, it fails to mention the specific risks associated with the interaction.</t>
+        </is>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>43.036</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Azathioprine and Zofenopril, including the severity and potential risks, and provides a thorough explanation and clinical advice.</t>
+        <v>645.8</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Azathioprine and Zofenopril, including severity, description, and clinical advice, without any unsupported claims.</t>
         </is>
       </c>
     </row>
@@ -1393,39 +1641,51 @@
       <c r="E7" t="b">
         <v>1</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" t="b">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>4.044</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>645.8</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>The response downplays the severity of the interaction and fails to mention the specific risks of myelosuppression, anemia, and severe leukopenia, which are critical details in the DrugBank ground truth.</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3</v>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>The response incorrectly states that there is no well-documented direct interaction, which contradicts the DrugBank ground truth indicating a severe interaction. Additionally, it fails to mention the specific risks of myelosuppression, anemia, and severe leukopenia associated with the combination.</t>
+        </is>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>10.681</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+        <v>647.5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>The AI response accurately reflects the DrugBank ground truth regarding the severe interaction between Azathioprine and Ramiprilat, including the description of risks and clinical advice, with no unsupported claims.</t>
         </is>
@@ -1455,39 +1715,51 @@
       <c r="E8" t="b">
         <v>1</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" t="b">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>4.633</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>647.5</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>The response accurately identifies the interaction and its severity but includes some additional details about hematological side effects that are plausible but not explicitly stated in the ground truth.</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>3</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>The response accurately identifies the moderate interaction and discusses myelosuppression, but it lacks direct reference to the specific risk of increased myelosuppression when the drugs are combined, which is a key detail in the ground truth.</t>
+        </is>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>11.908</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+        <v>648.6</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Hydroxyurea and Sulfamethoxazole, including the severity, mechanism, and clinical advice, with no unsupported claims.</t>
         </is>
@@ -1517,41 +1789,53 @@
       <c r="E9" t="b">
         <v>1</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" t="b">
         <v>1</v>
       </c>
       <c r="G9" t="n">
+        <v>2.683</v>
+      </c>
+      <c r="H9" t="n">
+        <v>648.6</v>
+      </c>
+      <c r="I9" t="n">
         <v>2</v>
       </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
       <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>The AI response fails to acknowledge the specific interaction and its moderate severity as stated in the DrugBank ground truth, leading to a lack of completeness and faithfulness. It also does not accurately reflect the severity level.</t>
         </is>
       </c>
-      <c r="M9" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3</v>
-      </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>11.602</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Idraparinux and Testosterone enantate benzilic acid hydrazone, including the severity, mechanism, and clinical advice.</t>
+        <v>649.7</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Idraparinux and Testosterone enantate benzilic acid hydrazone, including the severity, potential mechanism, and clinical advice.</t>
         </is>
       </c>
     </row>
@@ -1579,41 +1863,53 @@
       <c r="E10" t="b">
         <v>1</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" t="b">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>2.992</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>649.7</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>The response acknowledges the potential risks of combining the drugs but lacks specific mention of methemoglobinemia, which is a key detail in the ground truth. It also provides general advice, which is helpful but not fully aligned with the DrugBank description.</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>3</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>The response acknowledges the potential risks of combining the drugs and suggests caution, which aligns with the DrugBank description. However, it lacks specific mention of methemoglobinemia, which is a key detail in the ground truth.</t>
+        </is>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>11.038</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Aminosalicylic acid and Cocaine, including the severity, mechanism, and clinical advice.</t>
+        <v>649.9</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Aminosalicylic acid and Cocaine, including the severity, mechanism, and clinical advice, without any unsupported claims.</t>
         </is>
       </c>
     </row>
@@ -1641,14 +1937,14 @@
       <c r="E11" t="b">
         <v>1</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" t="b">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>4.629</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>649.9</v>
       </c>
       <c r="I11" t="n">
         <v>2</v>
@@ -1656,24 +1952,36 @@
       <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>The response provides a plausible explanation of the potential cardiovascular effects of the drugs but lacks direct reference to the specific interaction noted in the ground truth. It correctly identifies the severity as moderate.</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>3</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3</v>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>The response contains some accurate information about the drugs and their effects but fails to mention the specific interaction regarding bradycardia as stated in the ground truth, leading to a lower faithfulness score.</t>
+        </is>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>12.113</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+        <v>650.1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Rivastigmine and Naftopidil, including the severity, mechanism, and clinical advice, without any unsupported claims.</t>
         </is>
@@ -1703,14 +2011,14 @@
       <c r="E12" t="b">
         <v>1</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" t="b">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2.996</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>650.1</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -1718,26 +2026,38 @@
       <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>The response downplays the interaction by stating there are no major interactions, which contradicts the DrugBank ground truth indicating a moderate risk of myelosuppression. It also lacks specific details about the interaction's severity and mechanism.</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>3</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3</v>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>The response downplays the interaction by stating there are no major interactions, while the ground truth indicates a moderate risk of myelosuppression, which is not acknowledged in the AI response.</t>
+        </is>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>11.601</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Sulfamethoxazole and Melengestrol, including the severity and potential risks, and provides appropriate clinical advice.</t>
+        <v>643.4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Sulfamethoxazole and Melengestrol, including the severity, mechanism, and clinical advice, with no unsupported claims.</t>
         </is>
       </c>
     </row>
@@ -1765,41 +2085,53 @@
       <c r="E13" t="b">
         <v>1</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" t="b">
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>1.969</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>643.4</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>The response incorrectly states that there are no major interactions, which contradicts the DrugBank ground truth indicating a moderate interaction. It also fails to mention the specific risk of QTc prolongation.</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>3</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3</v>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>The AI response incorrectly states there are no major interactions, while the ground truth indicates a moderate interaction with a specific risk of QTc prolongation. This misrepresentation could mislead clinicians.</t>
+        </is>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>10.971</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Salmeterol and Rufloxacin, including the severity and potential risks, and provides a thorough explanation and clinical advice.</t>
+        <v>643.5</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Salmeterol and Rufloxacin, including the severity and potential risks, without any unsupported claims.</t>
         </is>
       </c>
     </row>
@@ -1827,44 +2159,56 @@
       <c r="E14" t="b">
         <v>1</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" t="b">
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>2.502</v>
       </c>
       <c r="H14" t="n">
+        <v>643.6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
         <v>0</v>
       </c>
-      <c r="I14" t="n">
+      <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>The AI response fails to acknowledge the existence of a drug interaction and its severity, which contradicts the DrugBank ground truth. It does not provide any relevant information about the interaction, leading to a low completeness score.</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
-        <v>3</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3</v>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>The AI response does not acknowledge the known moderate interaction between Imipramine and Etanautine, which is a significant omission. While it does not fabricate information, it fails to provide the necessary details about the interaction severity.</t>
+        </is>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>10.412</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Imipramine and Etanautine, including the severity and potential risks, and provides a thorough explanation and clinical advice.</t>
+        <v>644.8</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Imipramine and Etanautine, including severity, description, and clinical advice, without any unsupported claims.</t>
         </is>
       </c>
     </row>
@@ -1892,41 +2236,53 @@
       <c r="E15" t="b">
         <v>1</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" t="b">
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>2.277</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>644.9</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>The AI response does not acknowledge the moderate severity of the interaction as stated in the ground truth, leading to a low faithfulness score. However, it does not fabricate any claims about the drugs.</t>
-        </is>
-      </c>
-      <c r="M15" t="n">
-        <v>3</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3</v>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>The AI response fails to acknowledge the documented moderate interaction between Visilizumab and Plozalizumab, which is a key detail missing from the response. However, it does not fabricate any claims, hence the hallucination score is high.</t>
+        </is>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>9.246</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Visilizumab and Plozalizumab, including severity, mechanism, and clinical advice.</t>
+        <v>645.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Visilizumab and Plozalizumab, including the severity, mechanism, and clinical advice, with no unsupported claims.</t>
         </is>
       </c>
     </row>
@@ -1954,41 +2310,53 @@
       <c r="E16" t="b">
         <v>1</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" t="b">
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>2.995</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>645.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>The response incorrectly states that there are no well-documented interactions, contradicting the DrugBank ground truth which indicates a moderate risk. Additionally, it fails to mention the specific risk of increased adverse effects when these drugs are combined.</t>
-        </is>
-      </c>
-      <c r="M16" t="n">
-        <v>3</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>The AI response downplays the risk of interaction, suggesting low risk without acknowledging the moderate severity noted in the ground truth. It also lacks specific details about the potential adverse effects.</t>
+        </is>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>11.087</v>
       </c>
       <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Fluocinonide and Filgotinib, including the severity and potential risks, and provides a thorough explanation and clinical advice.</t>
+        <v>645.6</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Fluocinonide and Filgotinib, including the severity and potential risks, with no unsupported claims or omissions.</t>
         </is>
       </c>
     </row>
@@ -2016,41 +2384,53 @@
       <c r="E17" t="b">
         <v>1</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" t="b">
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>1.445</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>645.6</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>The AI response fails to acknowledge the specific interaction and severity level provided in the DrugBank ground truth, leading to a lack of completeness and faithfulness despite not fabricating claims.</t>
         </is>
       </c>
-      <c r="M17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3</v>
-      </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>9.25</v>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Mephentermine and Ractopamine, including the severity and potential risks, and provides a thorough explanation and clinical advice.</t>
+        <v>646.1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Mephentermine and Ractopamine, including severity, description, and clinical advice, without any unsupported claims.</t>
         </is>
       </c>
     </row>
@@ -2078,41 +2458,53 @@
       <c r="E18" t="b">
         <v>1</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" t="b">
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>2.676</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>646.1</v>
       </c>
       <c r="I18" t="n">
         <v>2</v>
       </c>
       <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>The AI response downplays the interaction severity and fails to mention the specific risk of myopathy and weakness, which is a key detail in the ground truth. While it acknowledges potential effects, it does not accurately reflect the moderate severity classification.</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
-        <v>3</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3</v>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>The AI response downplays the interaction severity and does not accurately reflect the moderate risk of myopathy and weakness as stated in the ground truth. While it mentions potential effects, it lacks specific details about the interaction's severity.</t>
+        </is>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>10.693</v>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Fluocortolone and Atracurium, including the severity and potential risks, and provides a thorough explanation and clinical advice.</t>
+        <v>646.2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Fluocortolone and Atracurium, including the severity and potential risks, without any unsupported claims.</t>
         </is>
       </c>
     </row>
@@ -2140,41 +2532,53 @@
       <c r="E19" t="b">
         <v>1</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" t="b">
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>3.243</v>
       </c>
       <c r="H19" t="n">
+        <v>646.3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>2</v>
       </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>The response contains a notable unsupported claim regarding increased levels of Halofantrine due to Dexamethasone, which is misleading. However, it correctly identifies the interaction as moderate and provides relevant clinical advice.</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
-        <v>3</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3</v>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>The response correctly identifies the interaction as moderate and mentions the potential for increased levels of Halofantrine, but it inaccurately suggests that Dexamethasone could increase Halofantrine levels, while the ground truth states that it increases Halofantrine metabolism.</t>
+        </is>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>13.749</v>
       </c>
       <c r="P19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Halofantrine and Dexamethasone acetate, including the severity, mechanism, and clinical advice, without any unsupported claims.</t>
+        <v>646.4</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Halofantrine and Dexamethasone acetate, including the severity, mechanism, and clinical advice, with no unsupported claims.</t>
         </is>
       </c>
     </row>
@@ -2202,44 +2606,53 @@
       <c r="E20" t="b">
         <v>1</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" t="b">
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>3.62</v>
       </c>
       <c r="H20" t="n">
+        <v>634.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
         <v>0</v>
       </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>The AI response fails to acknowledge the known interaction and its moderate severity, which is a significant omission and contradicts the DrugBank ground truth.</t>
-        </is>
-      </c>
-      <c r="M20" t="n">
-        <v>3</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3</v>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>The AI response incorrectly states there is no well-documented interaction, contradicting the DrugBank ground truth which indicates a moderate interaction. It also fails to mention the specific nature of the interaction, which is an increase in hypotensive activities.</t>
+        </is>
       </c>
       <c r="O20" t="n">
-        <v>3</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Torasemide and Unoprostone, including the severity, description, and clinical advice.</t>
+        <v>635.1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Torasemide and Unoprostone, including the severity, description, and clinical advice, with no unsupported claims.</t>
         </is>
       </c>
     </row>
@@ -2267,14 +2680,14 @@
       <c r="E21" t="b">
         <v>1</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" t="b">
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2.99</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>635.2</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -2282,26 +2695,38 @@
       <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>The response fails to mention the specific risk of methemoglobinemia, which is a key detail in the ground truth, and introduces unsupported claims about overlapping toxicities.</t>
-        </is>
-      </c>
-      <c r="M21" t="n">
-        <v>3</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3</v>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>The response contains unsupported claims about the lack of documentation for the interaction and does not mention the specific risk of methemoglobinemia, which is a key detail in the ground truth.</t>
+        </is>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>12.417</v>
       </c>
       <c r="P21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Cyclophosphamide and Metabutethamine, including the severity and potential risk of methemoglobinemia, and provides appropriate clinical advice.</t>
+        <v>635.5</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Cyclophosphamide and Metabutethamine, including the severity and potential risks, and provides relevant clinical advice.</t>
         </is>
       </c>
     </row>
@@ -2329,41 +2754,53 @@
       <c r="E22" t="b">
         <v>1</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" t="b">
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>4.084</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>635.5</v>
       </c>
       <c r="I22" t="n">
         <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>The response provides a plausible explanation of the interaction and its potential effects, but it lacks specific details about the severity and the exact nature of the interaction as described in the ground truth.</t>
-        </is>
-      </c>
-      <c r="M22" t="n">
-        <v>3</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>The response correctly identifies the interaction and its moderate severity but includes some unsupported details about cardiovascular effects and monitoring that are not explicitly stated in the ground truth.</t>
+        </is>
       </c>
       <c r="O22" t="n">
-        <v>3</v>
+        <v>10.983</v>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Phentolamine and Remifentanil, including the severity and mechanism of action, and provides appropriate clinical advice.</t>
+        <v>635.5</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3</v>
+      </c>
+      <c r="R22" t="n">
+        <v>3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Phentolamine and Remifentanil, including the severity, description, and clinical advice, with no unsupported claims.</t>
         </is>
       </c>
     </row>
@@ -2391,41 +2828,53 @@
       <c r="E23" t="b">
         <v>1</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" t="b">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>4.199</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>635.5</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>The AI response fails to acknowledge the specific interaction and its moderate severity as stated in the DrugBank ground truth, leading to a lack of faithfulness and completeness in the response.</t>
-        </is>
-      </c>
-      <c r="M23" t="n">
-        <v>3</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3</v>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>The AI response fails to acknowledge the specific interaction and its moderate severity as stated in the DrugBank ground truth, leading to a lack of faithfulness and completeness.</t>
+        </is>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>9.364000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Polyestradiol phosphate and Pamrevlumab, including the severity and potential mechanism, without any unsupported claims.</t>
+        <v>636.4</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Polyestradiol phosphate and Pamrevlumab, including the severity, mechanism, and clinical advice, with no unsupported claims.</t>
         </is>
       </c>
     </row>
@@ -2453,41 +2902,53 @@
       <c r="E24" t="b">
         <v>1</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" t="b">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>2.79</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>636.4</v>
       </c>
       <c r="I24" t="n">
         <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>The response correctly identifies the potential risks of using Bamlanivimab and Sotrovimab together but lacks specific mention of the increased risk of adverse effects as stated in the ground truth. It also introduces some ambiguity regarding the lack of documented interaction, which could mislead a clinician.</t>
         </is>
       </c>
-      <c r="M24" t="n">
-        <v>3</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3</v>
-      </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>9.477</v>
       </c>
       <c r="P24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Bamlanivimab and Sotrovimab, including the severity and potential risks, and provides a comprehensive explanation and clinical advice.</t>
+        <v>637.2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Bamlanivimab and Sotrovimab, including severity and clinical advice, without introducing unsupported claims.</t>
         </is>
       </c>
     </row>
@@ -2515,39 +2976,51 @@
       <c r="E25" t="b">
         <v>1</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" t="b">
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>2.89</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>637.2</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
       </c>
       <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>The AI response incorrectly states that there are no significant interactions and classifies the severity as minor, which contradicts the DrugBank ground truth that indicates a moderate interaction. Additionally, it omits the specific mechanism of interaction.</t>
-        </is>
-      </c>
-      <c r="M25" t="n">
-        <v>3</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3</v>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>The AI response incorrectly states that there are no significant interactions and classifies the severity as minor, which contradicts the DrugBank ground truth that indicates a moderate interaction with specific details about the mechanism and potential effects.</t>
+        </is>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>8.324</v>
       </c>
       <c r="P25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="inlineStr">
+        <v>637.5</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" t="inlineStr">
         <is>
           <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Drospirenone and Phenazopyridine, including the severity, mechanism, and clinical advice, with no unsupported claims.</t>
         </is>
@@ -2577,39 +3050,51 @@
       <c r="E26" t="b">
         <v>1</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" t="b">
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>1.968</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>637.5</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
       </c>
       <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>The AI response incorrectly states that there are no major interactions, while the ground truth indicates a moderate interaction. It also fails to mention the specific mechanism of decreased excretion rate, leading to potential misinterpretation.</t>
-        </is>
-      </c>
-      <c r="M26" t="n">
-        <v>3</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3</v>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>The AI response incorrectly states that there are no known moderate interactions, contradicting the DrugBank ground truth which specifies a moderate interaction. Key details about the interaction mechanism are also missing.</t>
+        </is>
       </c>
       <c r="O26" t="n">
-        <v>3</v>
+        <v>9.244</v>
       </c>
       <c r="P26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="inlineStr">
+        <v>637.6</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>3</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" t="inlineStr">
         <is>
           <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Vancomycin and Testosterone enanthate, including the severity, mechanism, and clinical advice.</t>
         </is>
@@ -2639,41 +3124,53 @@
       <c r="E27" t="b">
         <v>1</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" t="b">
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>1.965</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>637.7</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>The AI response fails to acknowledge the specific interaction and severity level provided in the DrugBank ground truth, leading to a lack of completeness and accuracy regarding the safety of the drug combination.</t>
-        </is>
-      </c>
-      <c r="M27" t="n">
-        <v>3</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3</v>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>The AI response fails to acknowledge the specific interaction and severity level provided in the DrugBank ground truth, leading to a lack of completeness and faithfulness despite not fabricating claims.</t>
+        </is>
       </c>
       <c r="O27" t="n">
-        <v>3</v>
+        <v>12.57</v>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Nabilone and Lortalamine, including the severity and potential effects, without any unsupported claims.</t>
+        <v>637.8</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Nabilone and Lortalamine, including severity, mechanism, and clinical advice, with no unsupported claims.</t>
         </is>
       </c>
     </row>
@@ -2701,39 +3198,51 @@
       <c r="E28" t="b">
         <v>1</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" t="b">
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>3.036</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>637.8</v>
       </c>
       <c r="I28" t="n">
         <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>The response correctly identifies the interaction as minor and discusses the implications of Tenofovir disoproxil on the immune system, but it lacks specific details about the decreased efficacy of the vaccine as stated in the ground truth.</t>
-        </is>
-      </c>
-      <c r="M28" t="n">
-        <v>3</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>The response correctly identifies the minor severity but lacks specific details about the decreased efficacy of the vaccine when used with Tenofovir disoproxil. It introduces plausible concerns about immunosuppression but does not fully align with the DrugBank description.</t>
+        </is>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>10.595</v>
       </c>
       <c r="P28" t="n">
-        <v>1</v>
-      </c>
-      <c r="R28" t="inlineStr">
+        <v>638.1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3</v>
+      </c>
+      <c r="R28" t="n">
+        <v>3</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" t="inlineStr">
         <is>
           <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Tenofovir disoproxil and Smallpox (Vaccinia) Vaccine, Live, including the severity, mechanism, and clinical advice.</t>
         </is>
@@ -2763,41 +3272,53 @@
       <c r="E29" t="b">
         <v>1</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" t="b">
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>3.747</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>638.1</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
       </c>
       <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" t="n">
         <v>0</v>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>The AI response incorrectly states the interaction severity as 'Major' instead of 'Minor', which is a significant error. Additionally, while it mentions immunosuppressive effects, it does not accurately reflect the DrugBank description regarding the therapeutic efficacy of the vaccine being decreased.</t>
-        </is>
-      </c>
-      <c r="M29" t="n">
-        <v>3</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3</v>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>The AI response incorrectly states a 'Major' severity level for the interaction, while the ground truth indicates it is 'minor'. Additionally, the explanation about immunosuppressive effects is plausible but not explicitly supported by the ground truth.</t>
+        </is>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>10.522</v>
       </c>
       <c r="P29" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the minor interaction between Foscarnet and Smallpox (Vaccinia) Vaccine, Live, including the mechanism and clinical advice, with no unsupported claims.</t>
+        <v>638.4</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>3</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Foscarnet and Smallpox (Vaccinia) Vaccine, Live, including the severity, description, and clinical advice, without introducing any unsupported claims.</t>
         </is>
       </c>
     </row>
@@ -2825,41 +3346,53 @@
       <c r="E30" t="b">
         <v>1</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" t="b">
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>3.242</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>638.5</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
       </c>
       <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>The AI response fails to acknowledge the specific interaction and severity level stated in the DrugBank ground truth, leading to notable omissions and inaccuracies.</t>
-        </is>
-      </c>
-      <c r="M30" t="n">
-        <v>3</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3</v>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>The AI response fails to acknowledge the specific interaction and severity level indicated in the DrugBank ground truth, leading to notable omissions and inaccuracies regarding the hypersensitivity risk associated with the combination of Phalaris minor pollen and Cloranolol.</t>
+        </is>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>10.274</v>
       </c>
       <c r="P30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Phalaris minor pollen and Cloranolol, including the severity, mechanism, and clinical advice, with no unsupported claims.</t>
+        <v>638.7</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3</v>
+      </c>
+      <c r="R30" t="n">
+        <v>3</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Phalaris minor pollen and Cloranolol, including severity, mechanism, and clinical advice, with no unsupported claims.</t>
         </is>
       </c>
     </row>
@@ -2887,41 +3420,56 @@
       <c r="E31" t="b">
         <v>1</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" t="b">
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>2.065</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>638.8</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>The AI response does not acknowledge the known minor interaction and fails to mention the increased risk of hypersensitivity, leading to a low faithfulness and completeness score.</t>
-        </is>
-      </c>
       <c r="M31" t="n">
-        <v>3</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>The AI response fails to acknowledge the specific minor interaction described in the ground truth, leading to a lack of severity accuracy and completeness. However, it does not fabricate any claims.</t>
+        </is>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>8.407</v>
       </c>
       <c r="P31" t="n">
-        <v>1</v>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Indenolol and Phalaris minor pollen, including the severity and potential hypersensitivity risk, with no unsupported claims.</t>
+        <v>638.9</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3</v>
+      </c>
+      <c r="R31" t="n">
+        <v>3</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Indenolol and Phalaris minor pollen, including severity, description, and clinical advice without any unsupported claims.</t>
         </is>
       </c>
     </row>
@@ -2949,14 +3497,14 @@
       <c r="E32" t="b">
         <v>1</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" t="b">
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>3.24</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>638.9</v>
       </c>
       <c r="I32" t="n">
         <v>2</v>
@@ -2964,26 +3512,38 @@
       <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>The response acknowledges the potential impact of Penciclovir on the immune response to live vaccines, which is plausible but not explicitly stated in the ground truth. It also correctly identifies the severity as minor, but lacks specific details about the decreased therapeutic efficacy mentioned in the ground truth.</t>
-        </is>
-      </c>
-      <c r="M32" t="n">
-        <v>3</v>
-      </c>
-      <c r="N32" t="n">
-        <v>3</v>
+      <c r="K32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>The response contains some plausible details about the interaction but fails to acknowledge the specific decrease in therapeutic efficacy noted in the ground truth. It also lacks a clear statement about the severity of the interaction.</t>
+        </is>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>10.273</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Penciclovir and Smallpox (Vaccinia) Vaccine, Live, including the severity, mechanism, and clinical advice.</t>
+        <v>639</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3</v>
+      </c>
+      <c r="R32" t="n">
+        <v>3</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Penciclovir and Smallpox (Vaccinia) Vaccine, Live, including the severity, mechanism, and clinical advice, with no unsupported claims.</t>
         </is>
       </c>
     </row>
@@ -3006,43 +3566,53 @@
       <c r="E33" t="b">
         <v>0</v>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="F33" t="b">
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>1.766</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>639</v>
       </c>
       <c r="I33" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" t="n">
         <v>2</v>
       </c>
-      <c r="K33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>The AI response accurately states the lack of specific information regarding the interaction, aligning with the DrugBank ground truth, but it could have emphasized the absence of data more clearly.</t>
         </is>
       </c>
-      <c r="M33" t="n">
-        <v>3</v>
-      </c>
-      <c r="N33" t="n">
-        <v>3</v>
-      </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>9.654999999999999</v>
+      </c>
+      <c r="P33" t="n">
+        <v>639.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the absence of interaction data between Daprodustat and Etifoxine, aligns with DrugBank's ground truth, and provides appropriate clinical advice without fabricating any claims.</t>
+        <v>3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the absence of interaction data between Daprodustat and Etifoxine, aligning fully with the DrugBank ground truth.</t>
         </is>
       </c>
     </row>
@@ -3065,43 +3635,53 @@
       <c r="E34" t="b">
         <v>0</v>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="F34" t="b">
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="H34" t="n">
+        <v>639.8</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3</v>
+      </c>
+      <c r="K34" t="n">
         <v>2</v>
       </c>
-      <c r="I34" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>The response correctly indicates the absence of documented interactions, but it includes some general advice that is not explicitly supported by DrugBank, leading to a minor inconsistency.</t>
-        </is>
-      </c>
       <c r="M34" t="n">
-        <v>3</v>
-      </c>
-      <c r="N34" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the absence of documented interactions between Daprodustat and Galsulfase, aligning with the DrugBank ground truth. However, it could have been more concise in stating the lack of data.</t>
+        </is>
       </c>
       <c r="O34" t="n">
-        <v>3</v>
+        <v>9.766999999999999</v>
+      </c>
+      <c r="P34" t="n">
+        <v>639.9</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the absence of interaction data and provides a thorough explanation consistent with DrugBank's ground truth.</t>
+        <v>3</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the absence of interaction records and provides a thorough explanation without fabricating any claims, aligning well with the DrugBank ground truth.</t>
         </is>
       </c>
     </row>
@@ -3124,43 +3704,53 @@
       <c r="E35" t="b">
         <v>0</v>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="F35" t="b">
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>2.417</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>640.1</v>
       </c>
       <c r="I35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" t="n">
         <v>2</v>
       </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>The AI response correctly identifies the lack of information on 'Rosin' and does not fabricate any claims about drug interactions, aligning with the DrugBank ground truth.</t>
-        </is>
-      </c>
       <c r="M35" t="n">
-        <v>3</v>
-      </c>
-      <c r="N35" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>The AI response correctly acknowledges the absence of data regarding the interaction between Daprodustat and Rosin, aligning with the DrugBank ground truth. However, it could have provided more clinical advice or context regarding the lack of information.</t>
+        </is>
       </c>
       <c r="O35" t="n">
-        <v>3</v>
+        <v>9.375</v>
+      </c>
+      <c r="P35" t="n">
+        <v>642.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the absence of interaction data between Daprodustat and Rosin, aligns with DrugBank's ground truth, and provides a comprehensive overview including clinical advice.</t>
+        <v>3</v>
+      </c>
+      <c r="R35" t="n">
+        <v>3</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the absence of interaction records and provides a thorough summary, aligning well with the DrugBank ground truth.</t>
         </is>
       </c>
     </row>
@@ -3183,41 +3773,51 @@
       <c r="E36" t="b">
         <v>0</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="F36" t="b">
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>3</v>
+        <v>2.371</v>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>642.5</v>
       </c>
       <c r="I36" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" t="n">
         <v>2</v>
       </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>The AI response accurately states the lack of specific interaction data and does not fabricate any claims, aligning well with the DrugBank ground truth.</t>
-        </is>
-      </c>
       <c r="M36" t="n">
-        <v>3</v>
-      </c>
-      <c r="N36" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>The AI response accurately states the absence of interaction data and provides relevant information about the drugs involved, but it lacks a mention of the specific note from DrugBank regarding the absence of data.</t>
+        </is>
       </c>
       <c r="O36" t="n">
-        <v>3</v>
+        <v>10.368</v>
+      </c>
+      <c r="P36" t="n">
+        <v>643.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
-      </c>
-      <c r="R36" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="R36" t="n">
+        <v>3</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" t="inlineStr">
         <is>
           <t>The AI response accurately reflects the absence of interaction data and provides a thorough explanation consistent with DrugBank's ground truth.</t>
         </is>
@@ -3242,43 +3842,53 @@
       <c r="E37" t="b">
         <v>0</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="F37" t="b">
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>1.724</v>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>638.8</v>
       </c>
       <c r="I37" t="n">
+        <v>3</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3</v>
+      </c>
+      <c r="K37" t="n">
         <v>2</v>
       </c>
-      <c r="K37" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>The AI response accurately states the lack of specific information regarding the interaction, aligning with the DrugBank ground truth, but it could have emphasized the absence of data more clearly.</t>
-        </is>
-      </c>
       <c r="M37" t="n">
-        <v>3</v>
-      </c>
-      <c r="N37" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>The AI response accurately states the lack of specific information regarding the interaction and advises consulting a healthcare professional, aligning well with the DrugBank ground truth.</t>
+        </is>
       </c>
       <c r="O37" t="n">
-        <v>2</v>
+        <v>10.598</v>
+      </c>
+      <c r="P37" t="n">
+        <v>639</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>The response accurately reflects the absence of interaction data and provides a reasonable explanation, but it could have included more detail on the lack of evidence for a mechanism.</t>
+        <v>3</v>
+      </c>
+      <c r="R37" t="n">
+        <v>3</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the absence of interaction records between Daprodustat and Apramycin, aligns with DrugBank's ground truth, and provides a comprehensive overview without fabricating any claims.</t>
         </is>
       </c>
     </row>
@@ -3301,43 +3911,53 @@
       <c r="E38" t="b">
         <v>0</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="F38" t="b">
+        <v>0</v>
       </c>
       <c r="G38" t="n">
+        <v>3.382</v>
+      </c>
+      <c r="H38" t="n">
+        <v>639.4</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" t="n">
         <v>2</v>
       </c>
-      <c r="H38" t="n">
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>The AI response accurately states that there is no documented interaction between Daprodustat and Cyproterone acetate, aligning with the DrugBank ground truth. However, it could have been more concise in its explanation.</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>6.708</v>
+      </c>
+      <c r="P38" t="n">
+        <v>639.9</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3</v>
+      </c>
+      <c r="R38" t="n">
+        <v>3</v>
+      </c>
+      <c r="S38" t="n">
         <v>2</v>
       </c>
-      <c r="I38" t="n">
-        <v>2</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>The response acknowledges the absence of documented interactions but introduces potential concerns about hematologic and hormonal effects, which are not explicitly supported by DrugBank. It is mostly consistent with the ground truth but includes some unsupported details.</t>
-        </is>
-      </c>
-      <c r="M38" t="n">
-        <v>3</v>
-      </c>
-      <c r="N38" t="n">
-        <v>3</v>
-      </c>
-      <c r="O38" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1</v>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>The AI response accurately states that no interaction record was found, aligning with the DrugBank ground truth. However, it lacks a note about acknowledging the absence of data.</t>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>The AI response accurately states that no interaction records are found, aligning with DrugBank's ground truth. However, it lacks a note about acknowledging the absence of data.</t>
         </is>
       </c>
     </row>
@@ -3360,43 +3980,53 @@
       <c r="E39" t="b">
         <v>0</v>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="F39" t="b">
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>3</v>
+        <v>5.794</v>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>618.3</v>
       </c>
       <c r="I39" t="n">
+        <v>3</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" t="n">
         <v>2</v>
       </c>
-      <c r="K39" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>The AI response accurately states that there is limited information and no documented interactions, aligning with the DrugBank ground truth. However, it could have emphasized the absence of data more clearly.</t>
-        </is>
-      </c>
       <c r="M39" t="n">
-        <v>3</v>
-      </c>
-      <c r="N39" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>The AI response accurately states that there is limited information and no well-documented interactions, aligning with the DrugBank ground truth. It provides a reasonable recommendation for discussing with a healthcare provider, though it could have emphasized the absence of documented interactions more clearly.</t>
+        </is>
       </c>
       <c r="O39" t="n">
-        <v>3</v>
+        <v>10.942</v>
+      </c>
+      <c r="P39" t="n">
+        <v>488</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the absence of interaction data between Daprodustat and Ethanolamine oleate, aligning fully with the DrugBank ground truth.</t>
+        <v>3</v>
+      </c>
+      <c r="R39" t="n">
+        <v>3</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the absence of interaction records and provides appropriate clinical advice, aligning fully with the DrugBank ground truth.</t>
         </is>
       </c>
     </row>
@@ -3419,43 +4049,53 @@
       <c r="E40" t="b">
         <v>0</v>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="F40" t="b">
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>3</v>
+        <v>4.002</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>488.1</v>
       </c>
       <c r="I40" t="n">
+        <v>3</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3</v>
+      </c>
+      <c r="K40" t="n">
         <v>2</v>
       </c>
-      <c r="K40" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>The AI response accurately states that there is no specific interaction data available for Daprodustat and Aspergillus terreus, aligning with the DrugBank ground truth. However, it could have provided more detail on the implications of the lack of data.</t>
-        </is>
-      </c>
       <c r="M40" t="n">
-        <v>3</v>
-      </c>
-      <c r="N40" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>The AI response accurately states that there is no specific interaction data available and provides relevant context about both Daprodustat and Aspergillus terreus, though it could have been more concise regarding the absence of interaction data.</t>
+        </is>
       </c>
       <c r="O40" t="n">
-        <v>3</v>
+        <v>8.382999999999999</v>
+      </c>
+      <c r="P40" t="n">
+        <v>375.7</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the absence of interaction data between Daprodustat and Aspergillus terreus, providing a comprehensive summary consistent with DrugBank's ground truth.</t>
+        <v>3</v>
+      </c>
+      <c r="R40" t="n">
+        <v>3</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the absence of interaction data and does not fabricate any claims, aligning fully with the DrugBank ground truth.</t>
         </is>
       </c>
     </row>
@@ -3478,43 +4118,53 @@
       <c r="E41" t="b">
         <v>0</v>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="F41" t="b">
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
+        <v>2.266</v>
       </c>
       <c r="H41" t="n">
-        <v>3</v>
+        <v>293.2</v>
       </c>
       <c r="I41" t="n">
+        <v>3</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" t="n">
         <v>2</v>
       </c>
-      <c r="K41" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>The AI response accurately states that there is no specific information regarding an interaction between the two drugs, aligning with the DrugBank ground truth. However, it could have been more concise in its clinical advice.</t>
-        </is>
-      </c>
       <c r="M41" t="n">
-        <v>3</v>
-      </c>
-      <c r="N41" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>The response accurately states that there is no specific information regarding an interaction between the two drugs, aligning with the DrugBank ground truth. However, it could have provided more detail on the absence of data.</t>
+        </is>
       </c>
       <c r="O41" t="n">
+        <v>8.425000000000001</v>
+      </c>
+      <c r="P41" t="n">
+        <v>233.7</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3</v>
+      </c>
+      <c r="R41" t="n">
+        <v>3</v>
+      </c>
+      <c r="S41" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" t="n">
-        <v>1</v>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>The AI response accurately states that no interaction record was found, aligning with the DrugBank ground truth, but it lacks a detailed explanation of the absence of data.</t>
+      <c r="U41" t="n">
+        <v>1</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>The AI response accurately states that there is no interaction record found, aligning with the DrugBank ground truth. It provides appropriate clinical advice but lacks a detailed explanation of the absence of interaction data.</t>
         </is>
       </c>
     </row>
@@ -3537,43 +4187,53 @@
       <c r="E42" t="b">
         <v>0</v>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="F42" t="b">
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>3.356</v>
       </c>
       <c r="H42" t="n">
-        <v>3</v>
+        <v>233.9</v>
       </c>
       <c r="I42" t="n">
+        <v>3</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3</v>
+      </c>
+      <c r="K42" t="n">
         <v>2</v>
       </c>
-      <c r="K42" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>The AI response accurately states that there is no documented interaction and provides relevant information about the drugs, but it lacks a clear mention of the absence of data in DrugBank.</t>
-        </is>
-      </c>
       <c r="M42" t="n">
-        <v>3</v>
-      </c>
-      <c r="N42" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>The AI response accurately states that there is no documented interaction and provides relevant information about the drugs, but it lacks a mention of consulting healthcare providers as a key point.</t>
+        </is>
       </c>
       <c r="O42" t="n">
-        <v>3</v>
+        <v>8.631</v>
+      </c>
+      <c r="P42" t="n">
+        <v>249.2</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the absence of interaction data and provides a thorough explanation, aligning well with the DrugBank ground truth.</t>
+        <v>3</v>
+      </c>
+      <c r="R42" t="n">
+        <v>3</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the absence of interaction data and provides a thorough assessment consistent with DrugBank's ground truth.</t>
         </is>
       </c>
     </row>
@@ -3601,44 +4261,56 @@
       <c r="E43" t="b">
         <v>1</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" t="b">
         <v>1</v>
       </c>
       <c r="G43" t="n">
+        <v>4.717</v>
+      </c>
+      <c r="H43" t="n">
+        <v>248.1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>3</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
         <v>2</v>
       </c>
-      <c r="H43" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" t="n">
+      <c r="L43" t="n">
         <v>0</v>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>The response inaccurately states that there are no major interactions between the drugs, ignoring the known interaction between Incadronic acid and Dexrabeprazole. It also fails to mention the severity of the interaction, which is classified as unknown in the ground truth.</t>
-        </is>
-      </c>
-      <c r="M43" t="n">
-        <v>2</v>
-      </c>
-      <c r="N43" t="n">
-        <v>2</v>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>The response accurately states that there are no major interactions for Amdinocillin and Incadronic acid, but it fails to mention the known interaction between Incadronic acid and Dexrabeprazole, which affects the therapeutic efficacy, leading to a partial inconsistency with the ground truth.</t>
+        </is>
       </c>
       <c r="O43" t="n">
-        <v>2</v>
+        <v>14.23</v>
       </c>
       <c r="P43" t="n">
-        <v>1</v>
+        <v>267.2</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>The response accurately identifies the interaction between Incadronic acid and Dexrabeprazole, including severity and clinical advice, but introduces a plausible mechanism not explicitly stated in the ground truth. It correctly notes the absence of interactions for the other drug pairs.</t>
+        <v>3</v>
+      </c>
+      <c r="R43" t="n">
+        <v>3</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Incadronic acid and Dexrabeprazole, including severity and clinical advice, while correctly stating that there are no interactions for Amdinocillin with either drug.</t>
         </is>
       </c>
     </row>
@@ -3666,47 +4338,59 @@
       <c r="E44" t="b">
         <v>1</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" t="b">
         <v>1</v>
       </c>
       <c r="G44" t="n">
+        <v>4.529</v>
+      </c>
+      <c r="H44" t="n">
+        <v>267.2</v>
+      </c>
+      <c r="I44" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" t="n">
         <v>2</v>
       </c>
-      <c r="H44" t="n">
+      <c r="K44" t="n">
         <v>2</v>
       </c>
-      <c r="I44" t="n">
-        <v>2</v>
-      </c>
-      <c r="J44" t="n">
+      <c r="L44" t="n">
         <v>0</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>The response contains plausible but unsupported details about the interaction between Incadronic acid and Dexrabeprazole, and it does not accurately reflect the severity of the interaction as stated in the ground truth. Additionally, it fails to mention the lack of records for Amdinocillin interactions.</t>
-        </is>
-      </c>
       <c r="M44" t="n">
-        <v>2</v>
-      </c>
-      <c r="N44" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>The response accurately states the lack of specific interaction data for Amdinocillin and provides general pharmacological insights, but it fails to mention the known interaction between Incadronic acid and Dexrabeprazole, which affects the completeness and severity accuracy.</t>
+        </is>
       </c>
       <c r="O44" t="n">
-        <v>2</v>
+        <v>13.538</v>
       </c>
       <c r="P44" t="n">
-        <v>1</v>
+        <v>272.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>The response accurately identifies the interaction between Incadronic acid and Dexrabeprazole, including the severity and mechanism, but introduces a plausible mechanism not explicitly stated in the ground truth. It correctly states no records for the other drug pairs, fulfilling the no record refusal criteria.</t>
+        <v>3</v>
+      </c>
+      <c r="R44" t="n">
+        <v>3</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interactions, including the severity and clinical advice, without fabricating any claims.</t>
         </is>
       </c>
     </row>
@@ -3734,44 +4418,56 @@
       <c r="E45" t="b">
         <v>1</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45" t="b">
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>4.224</v>
       </c>
       <c r="H45" t="n">
+        <v>273</v>
+      </c>
+      <c r="I45" t="n">
+        <v>3</v>
+      </c>
+      <c r="J45" t="n">
         <v>2</v>
       </c>
-      <c r="I45" t="n">
+      <c r="K45" t="n">
         <v>2</v>
       </c>
-      <c r="J45" t="n">
+      <c r="L45" t="n">
         <v>0</v>
       </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>The response accurately states that there is no specific interaction data for the combination of drugs, but it omits the known interaction between Incadronic acid and Dexrabeprazole regarding decreased therapeutic efficacy, which affects completeness.</t>
-        </is>
-      </c>
-      <c r="M45" t="n">
-        <v>3</v>
-      </c>
-      <c r="N45" t="n">
-        <v>3</v>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>The response accurately states the lack of specific interaction data for the combination of drugs and provides general information about each drug. However, it does not mention the known interaction between Incadronic acid and Dexrabeprazole, which affects the completeness and faithfulness of the response.</t>
+        </is>
       </c>
       <c r="O45" t="n">
-        <v>2</v>
+        <v>13.334</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>The response accurately reflects the interaction between Incadronic acid and Dexrabeprazole, including the potential decrease in efficacy, but does not address the lack of interaction records for Amdinocillin and Dexrabeprazole.</t>
+        <v>278.1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3</v>
+      </c>
+      <c r="R45" t="n">
+        <v>3</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Incadronic acid and Dexrabeprazole, including the potential decrease in therapeutic efficacy. It correctly identifies the lack of interaction records for Amdinocillin with the other drugs, providing a comprehensive and faithful assessment.</t>
         </is>
       </c>
     </row>
@@ -3799,44 +4495,59 @@
       <c r="E46" t="b">
         <v>1</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46" t="b">
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>5.14</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>277.4</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>The response accurately identifies the lack of interactions for Incadronic acid and Levofloxacin, but it fails to mention the moderate interaction between Amdinocillin and Levofloxacin, which is a key detail from the ground truth.</t>
-        </is>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
-      </c>
-      <c r="N46" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>The AI response incorrectly states that there are no major interactions between Amdinocillin and Levofloxacin, while the ground truth indicates a moderate interaction. Additionally, it fails to mention the severity of the interaction, which is a key detail.</t>
+        </is>
       </c>
       <c r="O46" t="n">
-        <v>3</v>
+        <v>11.835</v>
       </c>
       <c r="P46" t="n">
-        <v>1</v>
+        <v>288.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Levofloxacin and Amdinocillin, including severity and clinical advice, while correctly stating that there are no records for the other drug combinations.</t>
+        <v>3</v>
+      </c>
+      <c r="R46" t="n">
+        <v>3</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Levofloxacin and Amdinocillin, including severity and clinical advice, while correctly stating that there are no interactions for the other drug pairs.</t>
         </is>
       </c>
     </row>
@@ -3864,44 +4575,56 @@
       <c r="E47" t="b">
         <v>1</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47" t="b">
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>6.85</v>
       </c>
       <c r="H47" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="I47" t="n">
+        <v>3</v>
+      </c>
+      <c r="J47" t="n">
         <v>2</v>
       </c>
-      <c r="I47" t="n">
+      <c r="K47" t="n">
         <v>2</v>
       </c>
-      <c r="K47" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>The response accurately states that there is no specific interaction data for Incadronic acid and Amdinocillin, and it correctly identifies the lack of information for the other combinations. However, it lacks specific details about the known interaction between Amdinocillin and Levofloxacin.</t>
-        </is>
-      </c>
       <c r="M47" t="n">
-        <v>2</v>
-      </c>
-      <c r="N47" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>The response accurately states that there is no specific interaction data for Incadronic acid and Amdinocillin, and it correctly identifies the lack of records for the other combinations. However, it lacks specific details about the known moderate interaction between Amdinocillin and Levofloxacin.</t>
+        </is>
       </c>
       <c r="O47" t="n">
-        <v>2</v>
+        <v>14.605</v>
       </c>
       <c r="P47" t="n">
-        <v>1</v>
+        <v>290.4</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>The response accurately identifies the interaction between Amdinocillin and Levofloxacin, including the severity and mechanism, but it slightly paraphrases the DrugBank description. It correctly states that there are no interactions for Incadronic acid, fulfilling the no record requirement.</t>
+        <v>3</v>
+      </c>
+      <c r="R47" t="n">
+        <v>3</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Amdinocillin and Levofloxacin, including severity and clinical advice, while correctly stating that there are no records for interactions involving Incadronic acid.</t>
         </is>
       </c>
     </row>
@@ -3929,47 +4652,56 @@
       <c r="E48" t="b">
         <v>1</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48" t="b">
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>4.463</v>
       </c>
       <c r="H48" t="n">
+        <v>290.4</v>
+      </c>
+      <c r="I48" t="n">
+        <v>3</v>
+      </c>
+      <c r="J48" t="n">
         <v>2</v>
       </c>
-      <c r="I48" t="n">
+      <c r="K48" t="n">
         <v>2</v>
       </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>1</v>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>The response accurately states that there is no specific interaction data for Incadronic acid and Amdinocillin, and it correctly identifies the lack of direct major interactions among the drugs. However, it fails to mention the moderate interaction between Amdinocillin and Levofloxacin, which affects the completeness and severity accuracy.</t>
-        </is>
-      </c>
       <c r="M48" t="n">
-        <v>3</v>
-      </c>
-      <c r="N48" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>The response accurately states that there is no specific interaction data for Incadronic acid and Amdinocillin, and it correctly identifies the lack of interaction records. However, it does not mention the moderate interaction between Amdinocillin and Levofloxacin, which is a key detail.</t>
+        </is>
       </c>
       <c r="O48" t="n">
-        <v>3</v>
+        <v>14.673</v>
       </c>
       <c r="P48" t="n">
-        <v>1</v>
+        <v>292.6</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Amdinocillin and Levofloxacin, including the severity and clinical advice, while correctly stating that there are no records of interactions involving Incadronic acid.</t>
+        <v>3</v>
+      </c>
+      <c r="R48" t="n">
+        <v>3</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Amdinocillin and Levofloxacin, correctly identifies the severity, and appropriately states that there are no known interactions involving Incadronic acid.</t>
         </is>
       </c>
     </row>
@@ -3997,44 +4729,56 @@
       <c r="E49" t="b">
         <v>1</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49" t="b">
         <v>1</v>
       </c>
       <c r="G49" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="H49" t="n">
+        <v>292.6</v>
+      </c>
+      <c r="I49" t="n">
+        <v>3</v>
+      </c>
+      <c r="J49" t="n">
         <v>2</v>
       </c>
-      <c r="H49" t="n">
+      <c r="K49" t="n">
         <v>2</v>
       </c>
-      <c r="I49" t="n">
-        <v>2</v>
-      </c>
-      <c r="J49" t="n">
+      <c r="L49" t="n">
         <v>0</v>
       </c>
-      <c r="K49" t="n">
-        <v>1</v>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>The response correctly identifies the lack of interactions for Incadronic acid and provides general information about Amdinocillin and Omadacycline. However, it fails to mention the known interaction between Amdinocillin and Omadacycline, which affects the completeness and accuracy of the severity assessment.</t>
-        </is>
-      </c>
       <c r="M49" t="n">
-        <v>3</v>
-      </c>
-      <c r="N49" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>The response accurately states that there are no major interactions for Incadronic acid and provides relevant information about Amdinocillin and Omadacycline. However, it omits the specific interaction between Amdinocillin and Omadacycline noted in the ground truth, which affects the completeness score.</t>
+        </is>
       </c>
       <c r="O49" t="n">
-        <v>3</v>
+        <v>14.456</v>
       </c>
       <c r="P49" t="n">
-        <v>1</v>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>The AI response accurately reflects the interaction between Amdinocillin and Omadacycline as described in the DrugBank ground truth, including severity and clinical advice, while correctly omitting interactions for the other drug pairs.</t>
+        <v>298.6</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>3</v>
+      </c>
+      <c r="R49" t="n">
+        <v>3</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>The AI response accurately reflects the DrugBank ground truth regarding the interaction between Amdinocillin and Omadacycline, including severity and clinical advice, without any unsupported claims.</t>
         </is>
       </c>
     </row>
@@ -4062,44 +4806,56 @@
       <c r="E50" t="b">
         <v>1</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50" t="b">
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>3</v>
+        <v>4.252</v>
       </c>
       <c r="H50" t="n">
+        <v>298.9</v>
+      </c>
+      <c r="I50" t="n">
+        <v>3</v>
+      </c>
+      <c r="J50" t="n">
+        <v>3</v>
+      </c>
+      <c r="K50" t="n">
         <v>2</v>
       </c>
-      <c r="I50" t="n">
-        <v>1</v>
-      </c>
-      <c r="K50" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>The response accurately states that there is no documented interaction for Incadronic acid and Amdinocillin, as well as for Incadronic acid and Omadacycline. However, it fails to mention the known interaction between Amdinocillin and Omadacycline, which affects the completeness of the response.</t>
-        </is>
-      </c>
       <c r="M50" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>The AI response accurately states that there are no documented interactions for Incadronic acid and Amdinocillin, as well as for Incadronic acid and Omadacycline, and correctly identifies the interaction between Amdinocillin and Omadacycline without fabricating any claims. However, it lacks specific mention of the severity of the known interaction.</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>15.202</v>
+      </c>
+      <c r="P50" t="n">
+        <v>301.8</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>3</v>
+      </c>
+      <c r="R50" t="n">
         <v>2</v>
       </c>
-      <c r="N50" t="n">
+      <c r="S50" t="n">
         <v>2</v>
       </c>
-      <c r="O50" t="n">
-        <v>2</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>1</v>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>The AI response accurately identifies the interaction between Amdinocillin and Omadacycline, but it introduces a mechanism that is not explicitly stated in the ground truth. It correctly notes that there are no records for Incadronic acid interactions, fulfilling the no_record_refusal criteria.</t>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>The AI response accurately identifies the interaction between Amdinocillin and Omadacycline, including severity and clinical advice, but it lacks a direct reference to the DrugBank ground truth for the severity of the interaction. It correctly states that there are no interactions for Incadronic acid, fulfilling the no record requirement.</t>
         </is>
       </c>
     </row>
@@ -4127,44 +4883,56 @@
       <c r="E51" t="b">
         <v>1</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51" t="b">
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>3</v>
+        <v>1.657</v>
       </c>
       <c r="H51" t="n">
+        <v>301.8</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3</v>
+      </c>
+      <c r="J51" t="n">
+        <v>3</v>
+      </c>
+      <c r="K51" t="n">
         <v>2</v>
       </c>
-      <c r="I51" t="n">
-        <v>1</v>
-      </c>
-      <c r="K51" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>The response accurately states that there is no specific information on the interactions, aligning with the ground truth. However, it lacks details about the known interaction between Amdinocillin and Omadacycline, which affects completeness.</t>
-        </is>
-      </c>
       <c r="M51" t="n">
-        <v>3</v>
-      </c>
-      <c r="N51" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>The response accurately states that there is no specific information on the interactions between the drugs, aligning with the ground truth. However, it lacks mention of the known interaction between Amdinocillin and Omadacycline, which affects completeness.</t>
+        </is>
       </c>
       <c r="O51" t="n">
-        <v>2</v>
+        <v>20.516</v>
       </c>
       <c r="P51" t="n">
-        <v>1</v>
+        <v>303</v>
       </c>
       <c r="Q51" t="n">
-        <v>1</v>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>The response accurately reflects the DrugBank ground truth regarding the interaction between Amdinocillin and Omadacycline, including the severity and clinical advice. It correctly states that there are no recorded interactions for Incadronic acid with the other drugs, but it could have provided more detail on the implications of the unknown severity for the combination.</t>
+        <v>3</v>
+      </c>
+      <c r="R51" t="n">
+        <v>3</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>The response accurately reflects the DrugBank ground truth regarding the interactions, correctly identifies the lack of interaction records for Incadronic acid, and provides appropriate clinical advice without fabricating any claims.</t>
         </is>
       </c>
     </row>
@@ -4234,27 +5002,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Combining Enalapril, an ACE inhibitor used primarily for hypertension and heart failure, with Azathioprine, an immunosuppressant used in various autoimmune conditions and organ transplantation, can have potential interactions. 
-The combination is generally considered to have a **Moderate** interaction risk. Azathioprine can increase the risk of myelosuppression, and Enalapril may affect renal function, especially in patients with compromised renal status. Monitoring of renal function and blood counts is recommended when these medications are used together.
+          <t>Combining Enalapril, an ACE inhibitor used primarily for hypertension and heart failure, with Azathioprine, an immunosuppressant used in conditions like autoimmune diseases and organ transplantation, can have potential interactions. 
+The combination is generally considered to have a **Moderate** interaction risk. Azathioprine can potentially increase the risk of myelosuppression (bone marrow suppression), and Enalapril may affect renal function, especially in patients with compromised renal status. Monitoring of renal function and blood counts is advisable when these medications are used together.
 Always consult with a healthcare provider for personalized advice and monitoring when using these medications in combination.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>以下是 Enalapril 和 Azathioprine 的相互作用信息：
-### 药物相互作用
+          <t>Based on the information provided, it is **not safe** to combine Enalapril and Azathioprine. Here are the details:
+### Drug Interaction Summary
 1. **Enalapril × Azathioprine**
-   - **严重程度**：Severe
-   - **机制解释**：与 Azathioprine 合用时，Enalapril 可能增加骨髓抑制（myelosuppression）、贫血（anemia）和严重白细胞减少（severe leukopenia）的风险。这是因为 Azathioprine 本身就是一个免疫抑制剂，当与 Enalapril 结合时，会导致免疫系统进一步抑制，从而导致上述血象异常。
-   - **临床建议**：在联合使用这两种药物时，需谨慎监测血液学参数，并考虑是否有必要调整剂量或选择其他替代治疗方案。
+   - **Severity**: Severe
+   - **Mechanism Explanation**: The combination may increase the risk of myelosuppression (bone marrow suppression), anemia, and severe leukopenia (low white blood cell count). This occurs as Azathioprine is an immunosuppressant, and Enalapril can exacerbate the effects of Azathioprine, leading to a more pronounced reduction in blood cell production.
+   - **Clinical Advice**: If both medications are deemed necessary, it is crucial to closely monitor blood counts and consider alternative treatments or dose adjustments.
 2. **Azathioprine × Enalapril**
-   - **严重程度**：Severe
-   - **机制解释**：与 Enalapril 合用时，Azathioprine 同样可能增加骨髓抑制、贫血和严重白细胞减少的风险。机制与上述相同。
-   - **临床建议**：同样，在使用这两种药物时应监测血液学情况并根据需要做出相应调整。
-### 结论
-结合以上信息，Enalapril 和 Azathioprine 的联合使用并不安全，且有显著的相互作用风险。请务必在医生的指导下进行用药。
-### 免责声明
-本系统仅供参考，具体用药请遵医嘱。</t>
+   - **Severity**: Severe
+   - **Mechanism Explanation**: The same interaction applies when Azathioprine is considered first. The risk of bone marrow suppression and related issues remains.
+   - **Clinical Advice**: Monitor blood counts diligently and discuss the potential risks versus benefits with a healthcare provider.
+### Conclusion
+Combining Enalapril and Azathioprine can pose significant health risks and should be approached with caution. Always consult with your healthcare provider regarding medication combinations.
+### Disclaimer
+This system is for reference only; please follow your doctor's advice for actual medication decisions.</t>
         </is>
       </c>
     </row>
@@ -4290,11 +5058,11 @@
   - **严重程度**：Severe
   - **描述**：Azathioprine 与 Fosinopril 联合使用时，可能会增加骨髓抑制、贫血和严重白细胞减少的风险。
 ### 机制解释
-Fosinopril 是一种 ACE 抑制剂，主要用于治疗高血压和心力衰竭。而 Azathioprine 是一种免疫抑制剂，常用于治疗自身免疫性疾病。两者联合使用可能会对骨髓产生抑制作用，干扰血细胞的生成，从而导致贫血和白细胞减少，增加感染的风险。
+Fosinopril 是一种 ACE 抑制剂，用于治疗高血压和心力衰竭。Azathioprine 是一种免疫抑制剂，常用于治疗自身免疫性疾病。两者联合使用可能会导致骨髓抑制，导致红细胞、白细胞和血小板的生成减少，从而增加贫血和感染的风险。
 ### 临床建议
-由于 Fosinopril 和 Azathioprine 联合使用有严重的相互作用，建议避免同时使用这两种药物。应与医生讨论替代治疗方案，如果需要使用这两种药物，务必在医疗专业人士的监控下进行，必要时可以进行更频繁的血液检查。
+**不建议将 Fosinopril 和 Azathioprine 同时使用。** 如果有必要这样做，请务必在医生的指导下进行，并密切监测血液指标，以预防潜在的严重副作用。
 ### 免责声明
-请注意，本系统仅供参考，具体用药请遵循医生的建议。</t>
+请注意，本系统仅供参考，请遵循医生的建议进行实际用药。</t>
         </is>
       </c>
     </row>
@@ -4317,27 +5085,27 @@
       <c r="D4" t="inlineStr">
         <is>
           <t>The combination of Azathioprine and Quinaprilat does not have well-documented interactions, but caution is advised. Azathioprine is an immunosuppressant, and Quinaprilat is an ACE inhibitor used for hypertension and heart failure. 
-While there is no major interaction reported, Azathioprine can potentially increase the risk of renal impairment, and ACE inhibitors like Quinaprilat can also affect renal function, especially in patients with pre-existing kidney issues or dehydration. 
-Therefore, the severity of the interaction can be considered **Moderate**, and it is important to monitor kidney function and blood pressure closely if these medications are used together. Always consult with a healthcare provider for personalized advice and monitoring.</t>
+While there is no major interaction reported, Azathioprine can potentially increase the risk of renal impairment, and ACE inhibitors like Quinaprilat can also affect renal function, especially in patients with pre-existing conditions. Therefore, it is important to monitor kidney function closely if these medications are used together.
+In summary, the interaction is considered to be of moderate concern due to the potential for renal effects, and it is advisable to consult with a healthcare provider for personalized advice and monitoring.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>根据数据库的信息，以下是 Azathioprine 和 Quinaprilat 的相互作用分析：
-### 药物相互作用
+          <t>Based on the drug interaction data, here is the relevant information regarding the combination of Azathioprine and Quinaprilat:
+### Drug Interactions
 1. **Azathioprine × Quinaprilat**
-   - **严重程度**：Severe
-   - **描述**：合用可能会增加骨髓抑制、贫血和严重白细胞减少的风险。
+   - **Severity**: Severe
+   - **Description**: The risk or severity of myelosuppression, anemia, and severe leukopenia can be increased when Quinaprilat is combined with Azathioprine.
 2. **Quinaprilat × Azathioprine**
-   - **严重程度**：Severe
-   - **描述**：合用可能会增加骨髓抑制、贫血和严重白细胞减少的风险。
-### 机制解释
-当 Azathioprine 与 Quinaprilat 同时使用时，可能会增加身体对骨髓的抑制作用，这影响了血液细胞的产生，导致贫血和白细胞数量减少，从而降低身体抵抗感染的能力。
-### 临床建议
-- **避免使用**：鉴于此组合的严重相互作用，建议你在医生指导下避免同时使用这两种药物。
-- **咨询医生**：若需要同时使用这两种药物，请务必咨询医生以评估风险和获益，可能需要调整治疗方案或监测血液指标。
-### 免责声明
-请注意，本系统仅供参考，具体用药请遵医嘱。</t>
+   - **Severity**: Severe
+   - **Description**: The risk or severity of myelosuppression, anemia, and severe leukopenia can be increased when Quinaprilat is combined with Azathioprine.
+### Mechanism Explanation
+When Azathioprine is used alongside Quinaprilat, the combination may lead to increased suppression of bone marrow function. This suppression can interfere with the production of blood cells, resulting in conditions such as anemia (low red blood cell count) and severe leukopenia (low white blood cell count), which can increase the risk of infections.
+### Clinical Advice
+- **Avoid Combination**: Due to the severe interaction, it is advised to avoid the concurrent use of these medications unless absolutely necessary and prescribed by a healthcare provider.
+- **Consult Your Doctor**: Speak with your healthcare provider to evaluate your specific situation, as they may suggest alternative treatments or closer monitoring of your blood counts.
+### Disclaimer
+Please note that this system is for reference only; always follow your doctor's advice for any medication-related questions or decisions.</t>
         </is>
       </c>
     </row>
@@ -4359,24 +5127,24 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>There are no major drug interactions between azathioprine and enalaprilat. However, it is important to monitor for potential effects on kidney function, as both medications can have implications for renal health. Azathioprine can affect immune function, and enalaprilat, an ACE inhibitor, can impact blood pressure and renal perfusion, especially in patients with compromised kidney function.
-While the interaction is not classified as major, it is advisable to have your healthcare provider monitor your kidney function and blood pressure regularly while on these medications. Always consult your healthcare provider for personalized advice and monitoring.</t>
+          <t>There are no major drug interactions between Azathioprine and Enalaprilat. However, it is important to monitor for potential effects on kidney function, as both medications can have implications for renal health. Azathioprine can cause immunosuppression, and Enalaprilat, an ACE inhibitor, can affect renal function, especially in patients with pre-existing kidney issues or dehydration.
+While the interaction is not classified as major, it is advisable to have regular follow-ups with your healthcare provider to monitor your kidney function and overall health while on these medications. Always consult your doctor or pharmacist for personalized advice based on your specific health situation.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>根据提供的信息，以下是关于 Azathioprine 和 Enalaprilat 的相互作用分析：
-### 药物相互作用
+          <t>Based on the provided information, here is the analysis regarding the potential interactions between Azathioprine and Enalaprilat:
+### Drug Interactions
 1. **Azathioprine × Enalaprilat**
-   - **严重程度：** Severe
-   - **机制解释：** Azathioprine 是一种免疫抑制剂，可能导致骨髓抑制、贫血和严重的白细胞减少。当与 Enalaprilat 一起使用时，这些副作用的风险会增加，因为 Enalaprilat 可能影响血液成分的生成。
-   - **临床建议：** 请务必与医生沟通，可能需要定期监测血常规，以检查是否存在贫血或白细胞减少的迹象，医生可能会调整用药方案。
+   - **Severity:** Severe
+   - **Mechanism Explanation:** Azathioprine is an immunosuppressant that can lead to bone marrow suppression, anemia, and severe leukopenia (low white blood cell count). When taken together with Enalaprilat, the risk and severity of these effects can increase, which can pose significant health risks.
+   - **Clinical Advice:** It is crucial to discuss this combination with your doctor. You may need regular blood tests to monitor your blood cell counts and assess for any symptoms of anemia or increased infection risk. Your doctor may consider adjusting your medication regimen based on your health status.
 2. **Enalaprilat × Azathioprine**
-   - **严重程度：** Severe
-   - **机制解释：** 同上，Enalaprilat 与 Azathioprine 的组合会加大相互作用的风险，特别是血液成分的相关风险。
-   - **临床建议：** 同上，建议定期监测相关指标，并与医生讨论是否继续使用这两种药物。
-### 免责声明
-请注意，本系统仅供参考，具体用药请遵医嘱。务必与您的主治医生讨论此药物组合的潜在风险以及是否需要进行其他检查或调整治疗方案。</t>
+   - **Severity:** Severe
+   - **Mechanism Explanation:** The same as above, the combination can exacerbate the risks associated with both medications, particularly concerning blood cell counts and immunosuppression.
+   - **Clinical Advice:** Regular monitoring and open communication with your healthcare provider are advised to ensure your safety while taking these medications together.
+### Disclaimer
+Please note that this system is for reference only; always follow your doctor's advice regarding your medications. Discuss any concerns with your healthcare provider.</t>
         </is>
       </c>
     </row>
@@ -4398,26 +5166,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>There are no well-documented interactions between azathioprine and zofenopril. However, both medications can affect the immune system and blood pressure, respectively. While the interaction is not classified as major, it is always important to monitor for any unusual symptoms or changes in health status when taking these medications together. As always, consult with a healthcare provider for personalized advice and monitoring.</t>
+          <t>There are no well-documented interactions between azathioprine and zofenopril. However, both medications can affect the immune system and blood pressure, respectively. While the interaction is not classified as major, it is always important to monitor for any unusual symptoms or changes in health when taking these medications together. 
+As always, consult with a healthcare provider for personalized advice and to ensure safe use of these medications.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>根据药物数据库的信息，Azathioprine 和 Zofenopril 之间确实存在相互作用。以下是详细信息：
-### 药物相互作用
+          <t>Yes, Azathioprine and Zofenopril do interact with each other. Here are the details:
+### Drug Interaction
 1. **Azathioprine × Zofenopril**
-   - **严重程度**：Severe
-   - **描述**：当 Zofenopril 与 Azathioprine 结合时，可能会增加骨髓抑制、贫血和严重白血病的风险或严重性。
+   - **Severity**: Severe
+   - **Description**: The risk or severity of myelosuppression, anemia, and severe leukopenia can be increased when Zofenopril is combined with Azathioprine.
 2. **Zofenopril × Azathioprine**
-   - **严重程度**：Severe
-   - **描述**：当 Zofenopril 与 Azathioprine 结合时，可能会增加骨髓抑制、贫血和严重白血病的风险或严重性。
-### 机制解释
-这种相互作用的原因在于 Azathioprine 是一种免疫抑制剂，可能导致骨髓抑制，而 Zofenopril 是一种 ACE 抑制剂，也可能对骨髓功能产生影响，从而加重 Azathioprine 的不良反应，对血细胞的形成造成严重影响。
-### 临床建议
-- **避免合用**：由于两者的组合可能导致严重的副作用，建议在临床使用中避免将 Azathioprine 与 Zofenopril 同时使用。
-- **咨询医生**：如有需要使用上述药物，务必在医生的指导下进行，并定期监测血液学指标。
-### 免责声明
-本系统仅供参考，具体用药请遵医嘱。</t>
+   - **Severity**: Severe
+   - **Description**: The risk or severity of myelosuppression, anemia, and severe leukopenia can be increased when Zofenopril is combined with Azathioprine.
+### Mechanism Explanation
+This interaction occurs because Azathioprine is an immunosuppressant that can lead to bone marrow suppression, impacting the production of blood cells. Zofenopril, as an ACE inhibitor, may compound the effects of Azathioprine on bone marrow function, further increasing the risk of serious blood-related side effects.
+### Clinical Advice
+- **Avoid Combination**: Due to the potential for serious side effects, it is advisable to avoid using Azathioprine and Zofenopril together.
+- **Consult Your Doctor**: If there is a need to use these medications, it is essential to consult with a healthcare provider and monitor blood cell counts regularly.
+### Disclaimer
+This system is for reference only; please follow your doctor's advice for actual medication.</t>
         </is>
       </c>
     </row>
@@ -4439,10 +5208,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Azathioprine and Ramiprilat do not have a well-documented direct drug interaction. However, it is important to consider the individual effects of each medication. 
-Azathioprine is an immunosuppressant that can increase the risk of infections and may affect bone marrow function. Ramiprilat, an active metabolite of Ramipril, is an ACE inhibitor used primarily for hypertension and heart failure.
-While there is no major or moderate interaction reported between these two drugs, patients on Azathioprine may have altered renal function, which could potentially affect the pharmacokinetics of Ramiprilat. Therefore, monitoring renal function and blood pressure is advisable when these medications are used together.
-Always consult with a healthcare provider for personalized advice and monitoring when using these medications concurrently.</t>
+          <t>Azathioprine and Ramiprilat do not have a well-documented direct interaction. However, both drugs can affect the immune system and renal function, which may warrant caution when used together.
+- **Azathioprine** is an immunosuppressant that can increase the risk of infections and may affect kidney function.
+- **Ramiprilat**, the active form of Ramipril, is an ACE inhibitor used primarily for hypertension and heart failure, and it can also affect renal function, especially in patients with pre-existing kidney issues or those on other medications that impact the kidneys.
+While there is no major or moderate interaction specifically noted between these two drugs, it is important to monitor renal function and the patient's overall clinical status when they are used together, especially in patients with compromised kidney function or those who are on other medications that may affect renal function.
+Always consult with a healthcare provider for personalized advice and monitoring when using these medications together.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4455,13 +5225,13 @@
    - **严重程度**：Severe
    - **描述**：联合使用 Ramiprilat 和 Azathioprine 可能会增加骨髓抑制、贫血和严重白细胞减少的风险。
 ### 机制解释：
-这种相互作用的发生是因为 Azathioprine 是一种免疫抑制剂，它会抑制骨髓的功能，从而减少血液细胞的生成；而 Ramiprilat 作为 ACE 抑制剂，可能会加重这种免疫抑制的作用，导致更明显的血细胞减少。
+这种相互作用发生的原因是 Azathioprine 作为一种免疫抑制剂，会抑制骨髓功能，从而导致血细胞生成减少。而 Ramiprilat 可能会增强这种免疫抑制效应，进而造成更严重的血液细胞减少。
 ### 临床建议：
-- **监测**：如果需要同时使用这两种药物，建议定期监测血常规，特别是白细胞、红细胞和血小板的数量。
-- **剂量调整**：在联合用药时，可能需要根据患者的具体情况调整 Azathioprine 或 Ramiprilat 的剂量。
-- **咨询医生**：在使用这两种药物之前，请咨询您的医生或药师，以确保安全并了解潜在风险。
+- **监测**：建议在使用这两种药物时定期检查血常规，特别是关注白细胞、红细胞和血小板的数量。
+- **调整剂量**：在联合用药情况下，根据患者的具体情况，可以考虑调整 Azathioprine 或 Ramiprilat 的剂量。
+- **咨询医生**：在使用这两种药物前，务必咨询医生或药师，以确保用药安全并了解可能的风险。
 ### 免责声明：
-本系统仅供参考，具体用药请遵医嘱。</t>
+本系统仅供参考，实际用药请遵从医生的建议。</t>
         </is>
       </c>
     </row>
@@ -4483,27 +5253,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Hydroxyurea and Sulfamethoxazole do not have a well-documented major interaction, but caution is advised when using them together. 
-Hydroxyurea is an antineoplastic agent that can cause myelosuppression (decreased bone marrow activity), leading to potential blood-related side effects such as anemia, leukopenia, and thrombocytopenia. Sulfamethoxazole, an antibiotic, can also cause hematological side effects, including agranulocytosis and aplastic anemia, particularly in patients with certain risk factors.
-The combination of these two medications may increase the risk of hematological toxicity, particularly in patients who are already at risk for bone marrow suppression. Therefore, it is classified as a **Moderate interaction**. 
-If a patient is prescribed both medications, it is important to monitor blood counts regularly and assess for any signs of bone marrow suppression. Always consult with a healthcare provider for personalized advice and monitoring.</t>
+          <t>Hydroxyurea and sulfamethoxazole do not have a well-documented major interaction, but caution is advised when using them together. 
+Hydroxyurea is primarily used in the treatment of certain cancers and sickle cell disease, while sulfamethoxazole is an antibiotic often used to treat bacterial infections. 
+The potential concerns with this combination include:
+1. **Bone Marrow Suppression**: Hydroxyurea can cause myelosuppression (decreased bone marrow activity), leading to lower blood cell counts. Sulfamethoxazole can also cause bone marrow suppression, particularly in patients with certain risk factors (e.g., those with HIV or other immunocompromised states). The combination may increase the risk of hematologic toxicity.
+2. **Increased Risk of Infection**: Since both drugs can affect the immune system, there may be an increased risk of infections.
+3. **Monitoring**: If these medications are used together, close monitoring of blood counts is recommended to detect any potential adverse effects early.
+Overall, this combination is generally considered to have a moderate interaction risk, and it is important to consult with a healthcare provider for personalized advice and monitoring if you are prescribed both medications.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>### 药物相互作用信息
+          <t>### Drug Interaction Information
 #### 1. Hydroxyurea × Sulfamethoxazole
-- **严重程度**：Moderate
-- **机制解释**：当 Hydroxyurea 和 Sulfamethoxazole 同时使用时，可能会增加骨髓抑制的风险。骨髓抑制是指骨髓的产生能力受到抑制，可能导致白细胞、红细胞和血小板数量减少，从而影响免疫系统、贫血和出血风险。
+- **Severity**: Moderate
+- **Mechanism Explanation**: Taking Hydroxyurea and Sulfamethoxazole together can increase the risk of myelosuppression. Myelosuppression refers to a decrease in the production of blood cells in the bone marrow, which can lead to low white blood cells, low red blood cells, and low platelets, affecting the immune system and increasing the risk of anemia and bleeding.
 #### 2. Sulfamethoxazole × Hydroxyurea
-- **严重程度**：Moderate
-- **机制解释**：相同的机制，如上所述，合并使用时也可能增加骨髓抑制的风险。
-### 临床建议
-- **监测**：在使用这两种药物期间，应该定期进行血液检查，以监测白细胞、红细胞和血小板的数量，确保没有发生骨髓抑制。
-- **水分摄入**：Hydroxyurea 使用时应多喝水，以帮助排出毒素，保护肾脏功能。
-- **遵医嘱**：务必遵循医师的处方，避免自行调整药物的用量或停药。
-### 免责声明
-请注意，本系统提供的信息仅供参考，具体用药建议请遵循医生的指导和建议。</t>
+- **Severity**: Moderate
+- **Mechanism Explanation**: The same risk of myelosuppression applies, as mentioned above, when these medications are combined.
+### Clinical Advice
+- **Monitoring**: Regular blood tests should be done to monitor white blood cell counts, red blood cell counts, and platelet levels to ensure that myelosuppression is not occurring.
+- **Hydration**: It's important to drink plenty of fluids while using Hydroxyurea to help flush out toxins and support kidney function.
+- **Follow Your Doctor's Advice**: Always adhere to your doctor's prescriptions and guidance regarding medication use; do not adjust dosages on your own.
+### Disclaimer
+Please note that this system is for reference only; follow your doctor's advice for actual medication usage.</t>
         </is>
       </c>
     </row>
@@ -4526,7 +5299,7 @@
       <c r="D9" t="inlineStr">
         <is>
           <t>I do not have reliable information on the specific interaction between Idraparinux and Testosterone enantate benzilic acid hydrazone. Idraparinux is an anticoagulant, and while testosterone can have various effects on the body, the specific interaction with Idraparinux is not well-documented in the available literature. 
-It is important to consult a healthcare professional or a clinical pharmacist for personalized advice and to evaluate the potential risks based on your specific health situation and medication regimen.</t>
+It is important to consult a healthcare professional or a clinical pharmacist for personalized advice and to evaluate the potential risks based on individual health conditions and other medications.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4536,12 +5309,10 @@
    - **相互作用严重程度**: Moderate
    - **描述**: Testosterone enantate benzilic acid hydrazone 可能增强 Idraparinux 的抗凝效果。
 ### 机制解释
-使用 Testosterone enantate benzilic acid hydrazone 可能会导致更强的抗凝活性，这是因为某些类固醇激素可能影响凝血系统，减少血液的凝固能力，从而与 Idraparinux 的抗凝机制相互叠加，增加出血风险。
+使用 Testosterone enantate benzilic acid hydrazone 可能导致更强的抗凝活性，这是因为某些类固醇激素可能影响凝血系统，减少血液的凝固能力，从而与 Idraparinux 的抗凝机制相互叠加，增加出血风险。
 ### 临床建议
 - **监测**: 在同时使用这两种药物时，需密切监测患者的凝血指标（如 INR 值），以防止潜在的出血事件。
 - **根据医生建议调整剂量**: 如果出现出血症状或凝血指标异常，可能需要调整 Idraparinux 的剂量，或考虑其他治疗选择。
-### 食物禁忌
-- 对于 Idraparinux，建议避免使用具有抗凝或抗血小板活性的草药和补充剂，如大蒜、姜、越桔、丹参、吡拉西坦及银杏叶。
 ### 免责声明
 请注意，本系统仅供参考，具体用药请遵医嘱。</t>
         </is>
@@ -4566,24 +5337,20 @@
       <c r="D10" t="inlineStr">
         <is>
           <t>There is limited information available regarding the specific interaction between aminosalicylic acid and cocaine. However, combining these substances could potentially lead to unpredictable effects due to the stimulant properties of cocaine and the pharmacological effects of aminosalicylic acid, which is used primarily in the treatment of tuberculosis.
-Given the lack of specific data, it is advisable to avoid this combination unless under the direct supervision of a healthcare professional. If you have concerns about drug interactions, it is always best to consult with a healthcare provider or a clinical pharmacist for personalized advice.</t>
+Given the lack of specific data, it is advisable to exercise caution. The combination could be considered at least a moderate risk due to the potential for adverse effects, but without specific studies or clinical guidelines, I cannot classify it definitively. It is always best to consult a healthcare professional for personalized advice regarding drug interactions.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>### 药物组合相互作用信息
+          <t>The combination of Aminosalicylic acid and Cocaine is **not safe**. 
+### Interaction Details
 1. **Aminosalicylic acid × Cocaine**
-   - **严重程度**: Moderate
-   - **描述**: 与可卡因合用可能增加发生高铁血红蛋白血症的风险或严重程度。
-   - **机制解释**: 高铁血红蛋白血症的发生是由于可卡因可能影响血红蛋白的正常功能，而氨基水杨酸可能进一步加重这一影响，因此这两种药物的结合可能导致血液中高铁血红蛋白的增加，从而导致氧气运输能力降低。
-   - **临床建议**: 不建议同时使用这两种药物。如果必须使用，建议在专业医疗人员的监控下进行，定期监测血液中的高铁血红蛋白水平。
-2. **Cocaine × Aminosalicylic acid**
-   - **严重程度**: Moderate
-   - **描述**: 与氨基水杨酸合用可能增加发生高铁血红蛋白血症的风险或严重程度。
-   - **机制解释**: 同上，涉及可卡因和氨基水杨酸的逆向相互作用，对机体影响相似。
-   - **临床建议**: 见上述建议。
-### 免责声明
-请注意，以上信息仅供参考，具体用药请遵照医嘱。如有进一步问题，建议咨询您的医生或药剂师。</t>
+   - **Severity**: Moderate
+   - **Description**: The risk or severity of methemoglobinemia can be increased when Aminosalicylic acid is combined with Cocaine.
+   - **Mechanism Explanation**: Methemoglobinemia occurs because Cocaine may affect the normal functioning of hemoglobin, and Aminosalicylic acid can exacerbate this effect, leading to higher levels of methemoglobin in the blood, which reduces the blood's capacity to carry oxygen.
+   - **Clinical Advice**: It is advisable to avoid using these two drugs together. If treatment with both is considered necessary, it should be done under strict medical supervision with regular monitoring of blood methemoglobin levels.
+### Disclaimer
+Please remember that this information is for reference only. Always follow your doctor's advice when considering any medication or combination thereof.</t>
         </is>
       </c>
     </row>
@@ -4605,30 +5372,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Rivastigmine is a cholinesterase inhibitor used primarily for the treatment of Alzheimer's disease and other dementias, while Naftopidil is an alpha-1 adrenergic antagonist used to treat benign prostatic hyperplasia and related urinary symptoms.
-There is limited information available regarding a direct interaction between Rivastigmine and Naftopidil. However, both medications can have effects on the cardiovascular system. Rivastigmine may cause bradycardia (slow heart rate) and has the potential to increase the risk of syncope (fainting), especially in patients with pre-existing heart conditions. Naftopidil can also cause orthostatic hypotension (a drop in blood pressure upon standing), which may lead to dizziness or fainting.
-Given these effects, the combination of these two medications could potentially increase the risk of cardiovascular side effects, particularly in susceptible individuals. Therefore, it is advisable to monitor for any signs of dizziness, lightheadedness, or changes in heart rate when these medications are used together.
-In summary, while there is no well-documented major interaction, caution is warranted due to the potential for additive effects on blood pressure and heart rate. Always consult with a healthcare provider for personalized advice and monitoring when taking these medications together.</t>
+          <t>Rivastigmine is a cholinesterase inhibitor used primarily for the treatment of Alzheimer's disease and other dementias, while Naftopidil is an alpha-1 adrenergic antagonist used to treat benign prostatic hyperplasia and hypertension.
+There is limited information available regarding a specific interaction between Rivastigmine and Naftopidil. However, both medications can have effects on the cardiovascular system. Rivastigmine may cause bradycardia (slowed heart rate) and has the potential to affect blood pressure, while Naftopidil can lead to orthostatic hypotension (a drop in blood pressure upon standing).
+Given these effects, the combination of these two medications could potentially lead to an increased risk of cardiovascular side effects, particularly in susceptible individuals. However, the interaction is not classified as major or moderate based on available data.
+It is always advisable to consult with a healthcare provider before starting or combining medications to ensure safety and monitor for any potential side effects.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>以下是关于同时使用 Rivastigmine 和 Naftopidil 时需要注意的信息：
-### 药物相互作用
-1. **Rivastigmine × Naftopidil**
-   - **严重程度**：Moderate
-   - **描述**：Rivastigmine 可能会增加 Naftopidil 诱发的心动过缓活动。
-2. **Naftopidil × Rivastigmine**
-   - **严重程度**：Moderate
-   - **描述**：同样，Rivastigmine 可能会增加 Naftopidil 诱发的心动过缓活动。
-### 机制解释
-Rivastigmine 是一种抗胆碱酯酶药物，它通过增加乙酰胆碱的浓度来增强胆碱能神经功能。而 Naftopidil 是一种选择性 α1 受体拮抗剂，常用于治疗高血压和前列腺增生。二者联合使用时，Rivastigmine 可能增强 Naftopidil 导致的心动过缓，即心率减缓，增加心脏相关的不适风险。
-### 临床建议
-- **监测心率**：在使用这两种药物时，建议定期监测心率，注意是否有心率过慢的症状出现（如头晕、乏力等）。
-- **就医咨询**：在开始或调整剂量之前，务必咨询医生，评估使用这两种药物的必要性和安全性。
-- **同时用餐服用**：Rivastigmine 应与食物一起服用，可延长其作用时间，提高药物的总体吸收。
-### 免责声明
-本系统提供的信息仅供参考，具体用药请遵医嘱。如有任何疑问，请咨询专业医师或药师。</t>
+          <t>Here is the information you need to know about taking Rivastigmine and Naftopidil at the same time:
+### Drug Interactions
+1. **Rivastigmine x Naftopidil**
+   - **Severity**: Moderate
+   - **Description**: Rivastigmine may increase the bradycardic activities of Naftopidil.
+2. **Naftopidil x Rivastigmine**
+   - **Severity**: Moderate
+   - **Description**: Rivastigmine may increase the bradycardic activities of Naftopidil.
+### Mechanism Explanation
+Rivastigmine is a cholinesterase inhibitor, which means it increases the level of acetylcholine in your body by preventing its breakdown. Increased acetylcholine can lead to higher parasympathetic (cholinergic) effects including bradycardia (a slower heart rate). Naftopidil, on the other hand, is an alpha-1 antagonist that can also cause bradycardia. When taken together, Rivastigmine may enhance the heart rate-lowering effects of Naftopidil, increasing the risk of adverse cardiac effects.
+### Clinical Advice
+- **Monitor Heart Rate**: It's important to keep track of your heart rate when taking these medications together. Look out for symptoms of bradycardia such as dizziness, fatigue, or fainting.
+- **Consult Your Doctor**: Before starting or adjusting the dose of these medications, consult with your healthcare provider to ensure it's safe for you to use them together.
+- **Administer with Food**: Rivastigmine should be taken with food, as this can help improve absorption and effectiveness.
+### Disclaimer
+Please remember that this information is for reference only. Always follow your doctor’s advice regarding medications and discuss any concerns you may have with them.</t>
         </is>
       </c>
     </row>
@@ -4650,27 +5417,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>There are no well-documented major drug interactions between sulfamethoxazole and melengestrol. However, it's important to note that sulfamethoxazole can potentially affect the metabolism of various medications due to its impact on liver enzymes, but specific interactions with melengestrol are not commonly reported.
-That said, individual responses can vary, and it's always best to discuss any concerns with your healthcare provider or pharmacist, especially since they can consider your complete medication profile and health history. If you experience any unusual symptoms or side effects while taking these medications together, you should contact your healthcare provider.</t>
+          <t>There are no well-documented major drug interactions between sulfamethoxazole and melengestrol. However, it is always important to consider individual patient factors, such as other medications, medical history, and overall health.
+Sulfamethoxazole is an antibiotic, while melengestrol is a progestin used in various hormonal therapies. While the combination does not have a known major interaction, it is advisable to monitor for any unusual side effects or changes in effectiveness of either medication.
+Always consult your healthcare provider or pharmacist for personalized advice and to ensure that your specific situation is taken into account.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>根据您提供的信息，以下是 Sulfamethoxazole 和 Melengestrol 之间的相互作用：
-### 药物相互作用：
+          <t>Based on the available information, here are the concerns regarding your combination of Sulfamethoxazole and Melengestrol:
+### Drug Interaction:
 1. **Sulfamethoxazole × Melengestrol**
-   - **严重程度**：Moderate
-   - **描述**：与 Melengestrol 共同使用时，Sulfamethoxazole 可能会增加骨髓抑制的风险或严重程度。
+   - **Severity**: Moderate
+   - **Description**: The risk or severity of myelosuppression can be increased when Sulfamethoxazole is combined with Melengestrol.
 2. **Melengestrol × Sulfamethoxazole**
-   - **严重程度**：Moderate
-   - **描述**：与 Sulfamethoxazole 共同使用时，Melengestrol 可能会增加骨髓抑制的风险或严重程度。
-### 机制解释：
-这种相互作用可能是因为两种药物都可能直接或间接影响骨髓的功能，导致血液细胞生产的抑制。骨髓是制造红细胞、白细胞和血小板的地方，当它受到抑制时，可能会导致血液组件的减少，从而引起相应的临床症状。
-### 临床建议：
-- **监测**：请务必与您的医生沟通，以便监测血液指标。医生可能会建议定期进行血常规检查，以监测白细胞和其他血细胞数量。
-- **调整用药方案**：根据医学评估，您的医生可能会考虑调整用药或观察用药过程中可能出现的任何副作用。
-### 免责声明：
-请注意，本系统仅供参考，具体用药建议应遵循您的医生的指导。</t>
+   - **Severity**: Moderate
+   - **Description**: The risk or severity of myelosuppression can be increased when Sulfamethoxazole is combined with Melengestrol.
+### Mechanism Explanation:
+The interaction occurs because both Sulfamethoxazole and Melengestrol may affect the bone marrow's ability to produce blood cells. This can lead to decreased numbers of red blood cells, white blood cells, and platelets, potentially resulting in conditions such as anemia or increased risk of infection and bleeding.
+### Clinical Advice:
+- **Monitor Blood Counts**: It is essential to communicate with your doctor about this combination. They may recommend regular blood tests to monitor your blood cell levels, ensuring there are no adverse effects.
+- **Discuss Potential Adjustments**: Depending on your specific situation, your doctor may consider adjusting your medication regimen or provide additional monitoring.
+### Disclaimer:
+Please remember that this system is for reference only; always follow your doctor's advice regarding medications.</t>
         </is>
       </c>
     </row>
@@ -4692,26 +5460,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>There are no well-documented major drug interactions between Salmeterol and Rufloxacin. Salmeterol is a long-acting beta-agonist used primarily for asthma and chronic obstructive pulmonary disease (COPD), while Rufloxacin is an antibiotic used to treat bacterial infections.
-However, it is always important to consider the patient's overall health status, other medications they may be taking, and any specific contraindications or warnings associated with each drug. While the interaction is not classified as major, it is advisable to consult with a healthcare provider for personalized medical advice before combining these medications.</t>
+          <t>There are no well-documented major interactions between Salmeterol and Rufloxacin. Salmeterol is a long-acting beta-agonist used primarily for asthma and COPD, while Rufloxacin is an antibiotic. 
+However, it is always important to consider the individual patient's health status, other medications they may be taking, and any underlying conditions. While the interaction is not classified as major, it is advisable to consult with a healthcare provider for personalized medical advice before combining these medications.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>根据提供的信息，Salmeterol 和 Rufloxacin 之间存在相互作用，具体如下：
-### 药物相互作用
-- **相互作用名称**：Salmeterol × Rufloxacin
-  - **严重程度**：Moderate
-  - **描述**：在同时使用 Salmeterol 和 Rufloxacin 时，可能增加 QTc 间期延长的风险。
-- **相互作用名称**：Rufloxacin × Salmeterol
-  - **严重程度**：Moderate
-  - **描述**：在同时使用 Salmeterol 和 Rufloxacin 时，可能增加 QTc 间期延长的风险。
-### 机制解释
-QTc 间期延长是指心脏电活动中的一种潜在问题，可能导致心律失常。Salmeterol 是一种长效β-2 受体激动剂，可能影响心脏的电生理特性。Rufloxacin，是一种抗生素，可能也会对心脏的电信号传导产生影响。当这两种药物一起使用时，它们可能会共同增加对心脏的作用，从而增加QTc 间期延长的风险。
-### 临床建议
-- **建议**：如果您的医生考虑让您同时使用这两种药物，务必与其讨论相关风险，可能需要定期监测心电图和QTc 间期。如果有任何不适或心律不齐的症状，请及时就医。
-### 免责声明
-请注意，本系统提供的信息仅供参考，具体用药请遵循医生的建议。</t>
+          <t>Salmeterol and Rufloxacin should be used with caution together due to their interaction. Here are the details:
+### Drug Interaction
+- **Interaction Name**: Salmeterol × Rufloxacin
+  - **Severity**: Moderate
+  - **Description**: The risk or severity of QTc prolongation can be increased when Salmeterol is combined with Rufloxacin.
+- **Interaction Name**: Rufloxacin × Salmeterol
+  - **Severity**: Moderate
+  - **Description**: The risk or severity of QTc prolongation can be increased when Salmeterol is combined with Rufloxacin.
+### Mechanism Explanation
+QTc prolongation refers to an abnormality in the heart's electrical activity that can lead to serious heart rhythm issues. Salmeterol, a long-acting beta-2 adrenergic agonist, may affect the heart's electrical signals. Rufloxacin, an antibiotic, may also influence heart rhythm. When taken together, these medications may elevate the risk of QTc prolongation.
+### Clinical Advice
+- **Recommendation**: It is important to discuss with your healthcare provider the potential risks of using these two medications together. Monitoring of heart function (e.g., ECG) may be prudent if they are to be used concurrently, especially if you have other risk factors for heart issues.
+### Disclaimer
+Please remember that this information is for reference only. Always follow your doctor's advice regarding medication use.</t>
         </is>
       </c>
     </row>
@@ -4733,27 +5501,28 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>I do not have reliable information on the drug interactions between Imipramine and Etanautine. It is important to consult a healthcare professional or a reliable drug interaction database for the most accurate and up-to-date information regarding specific drug combinations.</t>
+          <t>I do not have reliable information on a drug called "Etanautine." It is possible that it is a less common or newly introduced medication that is not included in my training data. Therefore, I cannot provide specific information about drug interactions between Imipramine and Etanautine.
+Imipramine is a tricyclic antidepressant that can have various interactions with other medications, particularly those that affect serotonin levels, other antidepressants, and certain cardiovascular drugs. If you have concerns about a specific drug combination, I recommend consulting a healthcare professional or a pharmacist for the most accurate and up-to-date information.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>以下是 Imipramine 和 Etanautine 之间的药物相互作用信息：
-### 药物相互作用
-1. **Imipramine × Etanautine**
-   - **严重程度**：Moderate
-   - **描述**：与 Imipramine 组合时，Etanautine 可能增加不良反应的风险或严重性。
-2. **Etanautine × Imipramine**
-   - **严重程度**：Moderate
-   - **描述**：与 Etanautine 组合时，Imipramine 可能增加不良反应的风险或严重性。
-### 机制解释
-在一起使用时，这两种药物可能会相互影响，导致不良反应的风险增加。这是因为 Imipramine 是一种三环类抗抑郁药，主要通过影响神经递质（如血清素和去甲肾上腺素）来发挥作用，而 Etanautine 也可能通过类似机制影响中枢神经系统，所以合用可能造成相互增强的效果，从而增加副作用。
-### 临床建议
-- **监测**：在使用这两种药物时，建议密切监测患者的副作用，特别是对情绪、心情和生理状态的影响。
-- **调整剂量**：在必要时，医生可能需要考虑调整其中一种或两种药物的剂量，以尽量减少不良反应风险。
-- **就医咨询**：在开始或停止任一药物之前，请务必咨询医生或药师。
-### 免责声明
-请注意，本系统仅供参考，具体用药请遵医嘱。</t>
+          <t>Here are the drug interaction details between Imipramine and Etanautine:
+### Drug Interactions
+1. **Imipramine x Etanautine**
+   - **Severity**: Moderate
+   - **Description**: The risk or severity of adverse effects can be increased when Etanautine is combined with Imipramine.
+2. **Etanautine x Imipramine**
+   - **Severity**: Moderate
+   - **Description**: The risk or severity of adverse effects can be increased when Imipramine is combined with Etanautine.
+### Mechanism Explanation
+When used together, these drugs may interact in a way that raises the risk of adverse effects. This may occur because both Imipramine, a tricyclic antidepressant, and Etanautine can influence the levels of neurotransmitters in the brain, potentially leading to compounded side effects such as sedation or changes in mood.
+### Clinical Advice
+- **Monitoring**: Patients using both medications should be closely monitored for any increase in side effects, particularly those related to mood and mental status.
+- **Consultation**: It is advisable to consult a healthcare provider to consider necessary dose adjustments or alternative treatments.
+- **Avoidance**: If possible, consider avoiding the concurrent use of these two medications, especially without medical supervision.
+### Disclaimer
+Please note that this system is for reference only. Always follow your doctor's advice for actual medication management.</t>
         </is>
       </c>
     </row>
@@ -4775,24 +5544,24 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>I do not have specific information regarding interactions between Visilizumab and Plozalizumab. Both are monoclonal antibodies used in different therapeutic contexts, but there is limited data on their interaction profile. It is advisable to consult a healthcare professional or a reliable drug interaction database for the most accurate and up-to-date information regarding their use together.</t>
+          <t>I do not have specific information regarding an interaction between Visilizumab and Plozalizumab. Both are monoclonal antibodies used in different therapeutic contexts, but there is no well-documented evidence of a direct interaction between them. For the most accurate and up-to-date information, it is always best to consult a healthcare professional or a reliable drug interaction database.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>### 药物相互作用信息
-1. **药物组合**: Visilizumab × Plozalizumab
-   - **严重程度**: Moderate
-   - **机制解释**: 当 Visilizumab 和 Plozalizumab 同时使用时，可能会增加不良反应的风险或严重性。这是因为它们都是调节免疫反应的单克隆抗体，可能会增强彼此的药理作用，从而使患者面临更高的副作用风险。
-   - **临床建议**: 在使用这两种药物时，建议密切监测患者的健康状况和不良反应。如果有必要，考虑调整剂量或更改治疗方案。
-2. **药物组合**: Plozalizumab × Visilizumab
-   - **严重程度**: Moderate
-   - **机制解释**: 解释同上。
-   - **临床建议**: 同上。
-### 食物禁忌
-- 未找到记录。
-### 免责声明
-请注意，本系统仅供参考，具体用药请遵医嘱。</t>
+          <t>### Drug Interaction Information
+1. **Drug Pair**: Visilizumab × Plozalizumab
+   - **Severity**: Moderate
+   - **Mechanism Explanation**: The combination of Visilizumab and Plozalizumab may increase the risk or severity of adverse effects. This occurs because both are monoclonal antibodies that modulate immune response, possibly enhancing each other's pharmacological effects, which can lead to a higher risk of side effects in patients.
+   - **Clinical Advice**: It is advisable to closely monitor the patient's condition and any adverse reactions if both medications are used concurrently. Dose adjustments or changes in therapy may be necessary if significant adverse effects are observed.
+2. **Drug Pair**: Plozalizumab × Visilizumab
+   - **Severity**: Moderate
+   - **Mechanism Explanation**: Same as above.
+   - **Clinical Advice**: Same as above.
+### Food Interactions
+- No record found.
+### Disclaimer
+Please note that this system is for reference only. Always follow your doctor's advice for actual medication decisions.</t>
         </is>
       </c>
     </row>
@@ -4814,26 +5583,26 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Fluocinonide is a topical corticosteroid used to treat various skin conditions, while Filgotinib is an oral Janus kinase (JAK) inhibitor used for conditions like rheumatoid arthritis. There are no well-documented interactions between fluocinonide and filgotinib in the available literature. 
-However, since fluocinonide is a corticosteroid, it is important to monitor for potential side effects related to corticosteroid use, especially if used over large areas of the body or for prolonged periods. Filgotinib can also have immunosuppressive effects, so caution is advised when using any medications that may affect the immune system.
-Overall, the interaction between these two drugs is not classified as major, moderate, or minor based on current knowledge, but it is always best to consult with a healthcare provider for personalized advice and monitoring.</t>
+          <t>Fluocinonide is a topical corticosteroid used to treat various skin conditions, while Filgotinib is an oral Janus kinase (JAK) inhibitor used for conditions like rheumatoid arthritis. There are no well-documented drug interactions between fluocinonide and filgotinib. 
+However, since fluocinonide is a topical medication and filgotinib is systemic, the risk of significant interactions is generally low. That said, it is always important to monitor for any unusual side effects or changes in condition when using multiple medications. 
+If you have specific concerns or underlying health conditions, it's best to consult with a healthcare provider for personalized advice.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>### 药物组合：Fluocinonide &amp; Filgotinib
-#### 药物相互作用信息：
-- 相互作用：Fluocinonide × Filgotinib
-  - **严重程度**：Moderate
-  - **描述**：使用 Fluocinonide 与 Filgotinib 组合时，副作用的风险或严重程度可能会增加。
-#### 机制解释：
-这两种药物结合使用可能会增强彼此的副作用。Fluocinonide 是一种强效的皮质类固醇，主要用于治疗皮肤炎症，可能导致皮肤或全身的副作用。而 Filgotinib 是一种机体免疫调节剂，主要用于治疗类风湿关节炎和溃疡性结肠炎，当与 Fluocinonide 一起使用时，可能会增加免疫抑制的风险，从而提高感染或其他不良反应的发生率。
-#### 临床建议：
-- 在联合使用 Fluocinonide 和 Filgotinib 时，务必在医生的指导下进行，以监测可能的副作用。
-- 定期评估患者的身体状况，包括感染症状或其他不良反应的出现。
-- 如果出现任何不适或异常症状，应及时咨询医生。
-### 免责声明：
-本系统仅供参考，具体用药建议请遵医嘱。</t>
+          <t>### Drug Interaction Information: Fluocinonide &amp; Filgotinib
+#### Interaction Details:
+- **Interaction**: Fluocinonide × Filgotinib
+  - **Severity**: Moderate
+  - **Description**: The risk or severity of adverse effects can be increased when Fluocinonide is combined with Filgotinib.
+#### Mechanism Explanation:
+The combination of these two medications may enhance each other's side effects. Fluocinonide is a potent corticosteroid used topically for inflammatory skin conditions, and it can potentially have systemic effects, including immune suppression. Filgotinib, on the other hand, is an immunomodulator indicated for rheumatoid arthritis and ulcerative colitis, which also works to suppress immune responses. When used together, there may be an increased risk of adverse reactions, including a higher chance of infections or other negative side effects due to their overlapping effects on the immune system.
+#### Clinical Advice:
+- It is essential to use Fluocinonide and Filgotinib together only under the supervision of a healthcare provider.
+- Monitor the patient for any signs of side effects, such as unusual infections or changes in health status.
+- If any adverse effects occur, consult with a healthcare professional promptly.
+### Disclaimer:
+This system is for reference only; please follow your doctor's advice for actual medication.</t>
         </is>
       </c>
     </row>
@@ -4860,21 +5629,21 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>根据提供的信息，Mephentermine 和 Ractopamine 的组合存在以下相互作用：
-### 药物相互作用
+          <t>Based on the provided information, the combination of Mephentermine and Ractopamine has the following interaction:
+### Drug Interaction
 1. **Mephentermine × Ractopamine**
-   - **严重程度**：Moderate
-   - **相互作用描述**：当 Mephentermine 与 Ractopamine 结合使用时，可能会增加高血压的风险或严重程度。
+   - **Severity**: Moderate
+   - **Description**: The risk or severity of hypertension can be increased when Mephentermine is combined with Ractopamine.
 2. **Ractopamine × Mephentermine**
-   - **严重程度**：Moderate
-   - **相互作用描述**：同样，当 Ractopamine 与 Mephentermine 结合使用时，可能会增加高血压的风险或严重程度。
-### 机制解释
-这两种药物都能影响心血管系统，Mephentermine 是一种拟交感神经药物，会通过激活α肾上腺素受体和释放内源性去甲肾上腺素来提高血压。而 Ractopamine 也可能对心血管系统产生影响。因此，当这两种药物同时使用时，可能会使血压升高，增加高血压发生的风险。
-### 临床建议
-- 在使用 Mephentermine 和 Ractopamine 的同时，应监测血压，并注意是否有高血压症状（如头痛、眩晕等）。
-- 强烈建议在使用这两种药物前咨询医生，确保该组合适合您的个人健康状况，并在必要时进行调整。
-### 免责声明
-请注意，本系统仅供参考，具体用药请遵医嘱。</t>
+   - **Severity**: Moderate
+   - **Description**: The risk or severity of hypertension can be increased when Ractopamine is combined with Mephentermine.
+### Mechanism Explanation
+Both Mephentermine and Ractopamine can affect the cardiovascular system. Mephentermine is a sympathomimetic agent that can increase blood pressure by stimulating alpha-adrenergic receptors and releasing norepinephrine. Ractopamine may also exert effects on heart function. Therefore, using these medications together can elevate blood pressure, increasing the risk of hypertension.
+### Clinical Advice
+- It is important to monitor your blood pressure closely if you are prescribed both Mephentermine and Ractopamine.
+- Consult your doctor before using these two medications together to determine whether this combination is appropriate for your particular health situation, and to discuss any necessary adjustments.
+### Disclaimer
+This system is for reference only; please follow your doctor's advice for actual medication use.</t>
         </is>
       </c>
     </row>
@@ -4896,27 +5665,28 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>There are no well-documented interactions between fluocortolone, a corticosteroid, and atracurium, a neuromuscular blocker. However, fluocortolone can potentially affect electrolyte balance and muscle function, which may indirectly influence the effects of neuromuscular blockers like atracurium.
-While the interaction is not classified as major, moderate, or minor, it is always advisable to monitor patients closely when these medications are used together, especially in individuals with underlying conditions that may be affected by corticosteroids or neuromuscular blockers.
-As always, consult with a healthcare provider for personalized advice and monitoring when combining medications.</t>
+          <t>There are no well-documented interactions between fluocortolone, a corticosteroid, and atracurium, a neuromuscular blocker. However, it is important to consider the clinical context and the patient's overall health status. 
+Fluocortolone may have effects on electrolyte balance and muscle function, which could theoretically influence the effects of neuromuscular blockers like atracurium. While the interaction is not classified as major, moderate, or minor, it is advisable to monitor the patient closely for any unusual effects when these medications are used together.
+Always consult with a healthcare provider for personalized advice and to ensure safe medication use.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>### 药物相互作用信息
+          <t>Fluocortolone and Atracurium can be taken together, but caution is advised due to the potential interaction. 
+### Drug Interaction Information
 1. **Fluocortolone × Atracurium**
-   - **严重程度**: Moderate
-   - **描述**: 与Atracurium联合使用可能增加肌病和肌无力的风险和严重性。
+   - **Severity**: Moderate
+   - **Description**: The risk or severity of myopathy and weakness can be increased when Atracurium is combined with Fluocortolone.
 2. **Atracurium × Fluocortolone**
-   - **严重程度**: Moderate
-   - **描述**: 与Fluocortolone联合使用可能增加肌病和肌无力的风险和严重性。
-### 机制解释
-Atracurium是一种肌肉松弛剂，它通过抑制神经信号使肌肉放松。而Fluocortolone是一种类固醇，通常用于减少炎症，但它也可能影响肌肉和神经的功能。当这两种药物联合使用时，可能会导致肌肉疲劳和无力的风险增加。
-### 临床建议
-- **监测**: 如果需要同时使用这两种药物，建议在医生的指导下密切监测肌肉力量和功能。
-- **医生咨询**: 在开始新药物治疗前，务必与医生咨询，评估风险与收益。
-### 使用免责声明
-本系统仅供参考，具体用药请遵医嘱。</t>
+   - **Severity**: Moderate
+   - **Description**: The risk or severity of myopathy and weakness can be increased when Atracurium is combined with Fluocortolone.
+### Mechanism Explanation
+The interaction occurs because Atracurium is a muscle relaxant, which works by blocking nerve signals to the muscles. Fluocortolone, on the other hand, is a corticosteroid that can impact muscle function. When taken together, there is an increased risk of muscle weakness and myopathy (muscle damage).
+### Clinical Advice
+- **Monitoring**: If you are prescribed both medications, ensure close monitoring of muscle strength and function.
+- **Consult Your Doctor**: Always discuss with your healthcare provider before starting or combining these medications to assess individual risks.
+### Disclaimer
+This system is for reference only; please follow your doctor's advice for actual medication usage.</t>
         </is>
       </c>
     </row>
@@ -4939,28 +5709,28 @@
       <c r="D19" t="inlineStr">
         <is>
           <t>Halofantrine and Dexamethasone acetate can interact, and the combination is generally considered to have a **moderate** interaction. 
-Halofantrine is an antimalarial medication, while Dexamethasone acetate is a corticosteroid used to reduce inflammation. The concern with this combination is that Dexamethasone can potentially affect the metabolism of Halofantrine, leading to increased levels of Halofantrine in the body. This can increase the risk of side effects associated with Halofantrine, such as cardiac toxicity.
-If you are prescribed both medications, it is important to monitor for any adverse effects and consult your healthcare provider for personalized advice and management. Always inform your healthcare provider about all medications you are taking to ensure safe and effective treatment.</t>
+Halofantrine is an antimalarial medication, while Dexamethasone acetate is a corticosteroid used to reduce inflammation. The concern with this combination is that Dexamethasone can potentially affect the metabolism of Halofantrine, leading to increased levels of Halofantrine in the body. This could increase the risk of side effects associated with Halofantrine, such as cardiac toxicity.
+If you are prescribed both medications, it is important to monitor for any adverse effects and consult your healthcare provider for personalized advice. They may consider adjusting dosages or monitoring you more closely. Always inform your healthcare provider about all medications you are taking to ensure safe and effective treatment.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>以下是关于同时服用 Halofantrine 和 Dexamethasone acetate 的重要信息：
-### 药物相互作用
+          <t>Here’s what you should know about taking Halofantrine and Dexamethasone acetate at the same time:
+### Drug Interaction
 - **Halofantrine × Dexamethasone acetate**
-  - **严重程度**: Moderate
-  - **描述**: Halofantrine 的代谢可能在与 Dexamethasone acetate 联合使用时增加。
+  - **Severity**: Moderate
+  - **Description**: The metabolism of Halofantrine can be increased when combined with Dexamethasone acetate.
 - **Dexamethasone acetate × Halofantrine**
-  - **严重程度**: Moderate
-  - **描述**: Halofantrine 的代谢可能在与 Dexamethasone acetate 联合使用时增加。
-### 机制解释
-当 Halofantrine 与 Dexamethasone acetate 同时使用时，Dexamethasone 可能会影响肝脏代谢酶的活性，促使 Halofantrine 更快地在体内被分解。这可能导致 Halofantrine 的血药浓度降低，从而减弱其治疗效果。
-### 临床建议
-1. **定期监测**: 在医生的指导下，监测 Halofantrine 的疗效和任何潜在不良反应。
-2. **调整剂量**: 根据医生的评估，可能需要调整 Halofantrine 的剂量，以确保其治疗效果不受影响。
-3. **服药时间**: Halofantrine 应在空腹状态下服用，以降低心脏毒性风险；避免与食物一起服用。
-### 免责声明
-请注意，本系统仅供参考。具体用药方案和调整请务必遵循医生的指导和建议。</t>
+  - **Severity**: Moderate
+  - **Description**: The metabolism of Halofantrine can be increased when combined with Dexamethasone acetate.
+### Mechanism Explanation
+When Halofantrine is taken with Dexamethasone acetate, the glucocorticoid (Dexamethasone) may enhance the liver’s ability to break down Halofantrine. This can lead to lower levels of Halofantrine in your system, potentially reducing its effectiveness in treating your condition.
+### Clinical Advice
+1. **Monitoring**: It is crucial to monitor the effectiveness and side effects of Halofantrine when used with Dexamethasone. 
+2. **Dose Adjustment**: Consult your healthcare provider; they may need to adjust the dosage of Halofantrine to maintain its efficacy.
+3. **Administration**: Take Halofantrine on an empty stomach, as food can significantly increase its availability, raising the risk of heart-related side effects.
+### Disclaimer
+Please remember that this system is for reference only. Follow your doctor’s advice for actual medication recommendations and adjustments.</t>
         </is>
       </c>
     </row>
@@ -4982,23 +5752,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>I do not have specific information regarding drug interactions between Torasemide and Unoprostone. It is important to consult a healthcare professional or a reliable drug interaction database for the most accurate and up-to-date information regarding potential interactions between these medications.</t>
+          <t>As of my last training data up to October 2023, there is no well-documented interaction between Torasemide and Unoprostone. Torasemide is a loop diuretic used primarily for the treatment of edema associated with heart failure and hypertension, while Unoprostone is a prostaglandin analog used in the treatment of glaucoma.
+Since there is no specific interaction noted, it is generally considered to be a minor interaction, but it is always important to monitor for any unusual side effects or changes in therapeutic effects when these medications are used together. 
+For the most accurate and personalized advice, it is always best to consult with a healthcare professional or a clinical pharmacist.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>### 药物相互作用分析
-**药物组合**: Torasemide × Unoprostone
-1. **相互作用描述**:
-   - Torasemide 可能会增加 Unoprostone 的降压效果。
-2. **严重程度**: 
+          <t>### Drug Interaction Analysis
+**Drug Pair**: Torasemide × Unoprostone
+1. **Interaction Description**:
+   - Torasemide may increase the hypotensive activities of Unoprostone.
+2. **Severity**: 
    - Moderate
-3. **机制解释**:
-   - Torasemide 是一种利尿剂，能够降低血压。Unoprostone 是一种前列腺素类似物，主要用于治疗青光眼。两者结合可能导致降压效果叠加，从而引起低血压。
-4. **临床建议**:
-   - 使用此药物组合时，建议定期监测血压，以避免发生低血压的风险。如果患者感觉头晕或疲倦，应咨询医生是否需要调整用药方案。
-### 免责声明
-本系统仅供参考，具体用药请遵医嘱。</t>
+3. **Mechanism Explanation**:
+   - Torasemide is a diuretic that lowers blood pressure, while Unoprostone is a prostaglandin analogue used primarily for glaucoma treatment. The combination of these two drugs can enhance the blood pressure-lowering effect, leading to a risk of hypotension (low blood pressure).
+4. **Clinical Advice**:
+   - When using this combination, it's important to monitor blood pressure regularly to prevent excessive lowering. If any symptoms of low blood pressure, such as dizziness or lightheadedness, occur, consult a physician to evaluate the treatment plan.
+### Disclaimer
+This system is for reference only; please follow your doctor's advice for actual medication.</t>
         </is>
       </c>
     </row>
@@ -5020,29 +5792,28 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>The combination of Cyclophosphamide and Metabutethamine is not well-documented in terms of specific drug interactions. However, both drugs are used in cancer treatment and can have overlapping toxicities, particularly related to bone marrow suppression and potential for increased risk of infections.
-Given the potential for increased toxicity, this combination should be approached with caution. It is essential to consult with a healthcare provider or oncologist who can evaluate your specific situation, including your overall health, cancer type, and treatment plan.
-In summary, while there is no specific documented interaction, the combination may pose risks, and it is crucial to seek professional medical advice before proceeding.</t>
+          <t>The combination of Cyclophosphamide and Metabutethamine is not well-documented in terms of specific drug interactions. However, both drugs are used in the context of cancer treatment, and combining them may increase the risk of additive toxicities, particularly regarding bone marrow suppression and other side effects.
+Given the potential for increased toxicity, this combination should be approached with caution. It is essential to consult with a healthcare provider or oncologist who can evaluate your specific situation, including your overall health, the doses of each medication, and any other medications you may be taking.
+In summary, while there is no specific documented interaction, the combination may not be safe due to the potential for increased toxicity. Always consult a healthcare professional before making any changes to your medication regimen.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>根据提供的药物数据库信息，以下是关于 Cyclophosphamide 和 Metabutethamine 的相互作用和安全性建议：
-### 药物相互作用
+          <t>### Drug Interaction Overview
 1. **Cyclophosphamide × Metabutethamine**
-   - **严重程度**：Moderate
-   - **描述**：当 Cyclophosphamide 与 Metabutethamine 联合使用时，可能会增加高铁血红蛋白症的风险或严重程度。
+   - **Severity**: Moderate
+   - **Description**: The risk or severity of methemoglobinemia can be increased when Cyclophosphamide is combined with Metabutethamine.
 2. **Metabutethamine × Cyclophosphamide**
-   - **严重程度**：Moderate
-   - **描述**：当 Cyclophosphamide 与 Metabutethamine 联合使用时，可能会增加高铁血红蛋白症的风险或严重程度。
-### 机制解释
-高铁血红蛋白症发生的原因是由于这两种药物的相互作用可能导致血液中的血红蛋白转变为高铁血红蛋白形式，这种形式的血红蛋白不能有效地运输氧气，从而可能对人体造成危害。
-### 临床建议
-- **在使用这两种药物之前**，建议与医生进行详细沟通，询问是否可以采取额外措施以减少高铁血红蛋白症的风险。
-- **充分的水分摄入**：确保饮用充足的液体（一天至少 2-3 升），有助于减少药物对身体的负担。
-- **进食时服用**：建议在进食时服用 Cyclophosphamide，以减少胃肠道刺激。
-### 免责声明
-本系统仅供参考，具体用药请遵医嘱。在开始任何药物治疗之前，请咨询您的医生或药师以确保用药安全。</t>
+   - **Severity**: Moderate
+   - **Description**: The risk or severity of methemoglobinemia can be increased when Cyclophosphamide is combined with Metabutethamine.
+### Mechanism Explanation
+The interaction occurs because both Cyclophosphamide and Metabutethamine can affect the levels of hemoglobin in the blood, potentially leading to a condition known as methemoglobinemia. In this condition, a form of hemoglobin that cannot effectively carry oxygen begins to build up, which can lead to oxygen deprivation in the body's tissues.
+### Clinical Advice
+- **Communication with Healthcare Provider**: It is essential to discuss this combination with your doctor. They may recommend monitoring your blood levels or adjusting dosages to mitigate risks.
+- **Fluid Intake**: Increased fluid intake (2-3 liters daily) is recommended to help flush out the drugs and minimize any potential side effects.
+- **Administering with Food**: Taking Cyclophosphamide with food can help reduce gastrointestinal irritation.
+### Disclaimer
+This system is for reference only; please follow your doctor's advice regarding medication safety and management.</t>
         </is>
       </c>
     </row>
@@ -5064,27 +5835,28 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Phentolamine and remifentanil can interact, but the specific interaction is not well-documented in terms of severity. Phentolamine is an alpha-adrenergic antagonist used primarily for the management of pheochromocytoma and to reverse local anesthesia, while remifentanil is an ultra-short-acting opioid analgesic used for pain management, particularly in surgical settings.
-The combination may lead to potential cardiovascular effects, as phentolamine can cause vasodilation and hypotension, while remifentanil can cause respiratory depression and may also affect cardiovascular stability. However, the clinical significance of this interaction can vary based on the patient's overall health, the doses used, and the clinical context.
-Given the potential for additive effects on blood pressure and heart rate, it is advisable to monitor patients closely when these drugs are used together. If you are considering this combination in a clinical setting, it would be prudent to consult with a healthcare professional or a clinical pharmacist for a more tailored assessment based on the specific patient scenario.</t>
+          <t>Phentolamine and Remifentanil can interact, but the specific interaction is not well-documented in terms of severity. Phentolamine is an alpha-adrenergic antagonist used primarily for the management of pheochromocytoma and to reverse local anesthesia, while Remifentanil is an ultra-short-acting opioid analgesic used for pain management during surgery.
+The combination may lead to potential cardiovascular effects, as Phentolamine can cause vasodilation and hypotension, while Remifentanil can cause respiratory depression and may also affect cardiovascular stability. However, the clinical significance of this interaction can vary based on the individual patient's condition and the context in which these drugs are used.
+Given the potential for additive effects on blood pressure and heart rate, it is advisable to monitor patients closely if these medications are used together. If you are considering this combination, it is best to consult with a healthcare professional for personalized advice and monitoring strategies.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>### 药物组合相互作用信息
-1. **相互作用药物**: Phentolamine × Remifentanil  
-   - **严重程度**: Moderate  
-   - **描述**: Remifentanil may decrease the antihypertensive activities of Phentolamine.
-2. **相互作用药物**: Remifentanil × Phentolamine  
-   - **严重程度**: Moderate  
-   - **描述**: Remifentanil may decrease the antihypertensive activities of Phentolamine.
-### 机制解释
-当 Phentolamine（α-adrenergic blocker）和 Remifentanil（强效镇痛药物）同时使用时，Remifentanil 可能会降低 Phentolamine 的降压效果。这是因为 Remifentanil 的镇痛作用可能影响血管的舒张作用，从而减弱 Phentolamine 的疗效，导致血压管理不理想。
-### 临床建议
-- 在同时使用 Phentolamine 和 Remifentanil 时，应监测患者的血压。必要时，可以调整用药剂量，以确保患者的血压维持在安全范围内。
-- 仅在医生指导下同时服用这两种药物，确保医疗团队能够迅速应对任何不良反应。
-### 免责声明
-本系统仅供参考，具体用药请遵医嘱。</t>
+          <t>### Drug Interaction Information
+1. **Drug Interaction**: Phentolamine × Remifentanil  
+   - **Severity**: Moderate  
+   - **Description**: Remifentanil may decrease the antihypertensive activities of Phentolamine.
+2. **Drug Interaction**: Remifentanil × Phentolamine  
+   - **Severity**: Moderate  
+   - **Description**: Remifentanil may decrease the antihypertensive activities of Phentolamine.
+### Mechanism Explanation
+When Phentolamine, an alpha-adrenergic blocker, is used with Remifentanil, a potent analgesic, there is a potential risk that Remifentanil can reduce the effectiveness of Phentolamine in lowering blood pressure. This happens because Remifentanil's pain-relieving effects can interfere with the dilation of blood vessels that Phentolamine induces, potentially leading to inadequate blood pressure control.
+### Clinical Advice
+- **Monitoring**: Close monitoring of blood pressure is recommended when these two medications are used together.
+- **Dose Adjustment**: Be prepared to adjust the doses of either medication based on the patient's blood pressure response.
+- **Consultation**: Always use these medications under the guidance of a healthcare professional to manage any potential interactions effectively.
+### Disclaimer
+This system is for reference only; please follow your doctor's advice for actual medication.</t>
         </is>
       </c>
     </row>
@@ -5111,22 +5883,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>以下是 Polyestradiol phosphate 和 Pamrevlumab 组合的相互作用分析：
-1. **相互作用**：
+          <t>The combination of Polyestradiol phosphate and Pamrevlumab is not considered entirely safe due to the following interaction:
+1. **Interaction**:
    - **Polyestradiol phosphate × Pamrevlumab**
-     - **严重程度**：Moderate
-     - **描述**：Polyestradiol phosphate 可能增强 Pamrevlumab 的血栓形成活性。
-   - **Pamrevlumab × Polyestradiol phosphate**
-     - **严重程度**：Moderate
-     - **描述**：Pamrevlumab 可能受到 Polyestradiol phosphate 的影响，增强其血栓形成活性。
-2. **机制解释**：
-   - 血栓形成涉及到血液的凝固机制。Polyestradiol phosphate 可能通过改变血液成分或凝血因子的活性，导致 Pamrevlumab 的作用增强，从而增加血栓形成的风险。
-3. **临床建议**：
-   - 在同时使用 Polyestradiol phosphate 和 Pamrevlumab 时，建议医生监测肢体的血液循环状态，并评估患者的血栓形成风险。必要时考虑寻找替代的治疗方案或调整剂量。患者应告知医生自己是否有血栓形成的历史。
-4. **诚实原则**：
-   - 数据库中关于这两种药物的相互作用已有明确记录。
-5. **免责声明**：
-   - 请注意，本系统仅供参考，具体的用药建议请遵循您的医生或医疗提供者的指示。</t>
+     - **Severity**: Moderate
+     - **Description**: Polyestradiol phosphate may increase the thrombogenic activities of Pamrevlumab.
+2. **Mechanism Explanation**:
+    - This interaction occurs because Polyestradiol phosphate can change the blood's clotting properties, which may enhance the risk of blood clots associated with the use of Pamrevlumab. 
+3. **Clinical Advice**:
+   - If you are considering using these medications together, it is crucial to consult with your healthcare provider. They may need to monitor you closely for any signs of blood clots and possibly consider alternative treatments or dosages. 
+4. **Disclaimer**:
+   - Please note that this information is for reference only; always follow your doctor's advice regarding medication use.</t>
         </is>
       </c>
     </row>
@@ -5155,20 +5922,20 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>根据您的用药信息，Bamlanivimab 与 Sotrovimab 之间存在以下相互作用：
-### 药物组合相互作用
+          <t>Based on your medications, there is a concern regarding the combination of Bamlanivimab and Sotrovimab:
+### Drug Interaction
 1. **Bamlanivimab × Sotrovimab**
-   - **严重程度**：Moderate
-   - **描述**：与 Sotrovimab 结合使用时，Bamlanivimab 的不良反应风险或严重程度可能增加。
+   - **Severity**: Moderate
+   - **Description**: The risk or severity of adverse effects can be increased when Bamlanivimab is combined with Sotrovimab.
 2. **Sotrovimab × Bamlanivimab**
-   - **严重程度**：Moderate
-   - **描述**：与 Bamlanivimab 结合使用时，Sotrovimab 的不良反应风险或严重程度可能增加。
-### 机制解释
-当这两种药物联合使用时，它们可能相互影响，导致不良反应的风险增加。这可能是因为两种药物都针对病毒的同一目标（SARS-CoV-2 病毒），增强了药物之间的相互作用，从而引发更强的不良反应或副作用。
-### 临床建议
-- **请咨询您的医生**：在开始或继续使用这两种药物之前，您应与您的医生详细讨论这两种药物的联合使用风险。医生可能会评估您的具体情况，决定是否需要调整剂量或采取其他措施来监控不良反应。
-### 免责声明
-请注意，本系统仅供参考，具体用药和健康状况请遵循您的医生的建议和处方。</t>
+   - **Severity**: Moderate
+   - **Description**: The risk or severity of adverse effects can be increased when Bamlanivimab is combined with Sotrovimab.
+### Mechanism Explanation
+Using these two medications together may enhance their effects on the same target (the SARS-CoV-2 virus), leading to a higher likelihood of experiencing adverse effects. This increase in risk may stem from overlapping side effects or interactions that amplify each drug's impact on the body.
+### Clinical Advice
+- **Consult Your Doctor**: It is crucial to discuss the use of both these medications with your doctor. They can evaluate your specific situation and determine whether any adjustments in dosage or additional monitoring are necessary to manage potential risks.
+### Disclaimer
+Please note that this system is for reference only; always follow your doctor's advice regarding actual medication use and management.</t>
         </is>
       </c>
     </row>
@@ -5190,23 +5957,23 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>There are no known significant interactions between Drospirenone and Phenazopyridine. The interaction severity is classified as minor, meaning that while there may be some theoretical concerns, they are not expected to cause major clinical issues. However, it is always best to consult with a healthcare provider for personalized advice and to monitor for any unusual symptoms when taking multiple medications.</t>
+          <t>There are no known significant interactions between Drospirenone and Phenazopyridine. The interaction severity is classified as minor, meaning that while there may be some potential for interaction, it is not expected to cause serious adverse effects or require major adjustments in therapy. However, it is always advisable to consult with a healthcare provider for personalized advice and to monitor for any unusual symptoms when taking multiple medications.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>### 药物相互作用信息
+          <t>### Drug Interaction Information
 1. **Drospirenone × Phenazopyridine**
-   - **严重程度**：Moderate
-   - **机制解释**：Drospirenone 可能增加 Phenazopyridine 的排泄速率，导致其血清水平降低，可能会减弱药效。
+   - **Severity**: Moderate
+   - **Mechanism Explanation**: Drospirenone may increase the excretion rate of Phenazopyridine, leading to lower serum levels and potentially reducing its effectiveness.
 2. **Phenazopyridine × Drospirenone**
-   - **严重程度**：Moderate
-   - **机制解释**：上述机制同样适用于该组合，即 Drospirenone 可能影响 Phenazopyridine 的血清浓度。
-### 临床建议
-- **监测和调整**：在使用这两种药物时，建议定期监测患者的症状和疗效。如果患者的症状未得到缓解，可能需要评估是否调整药物剂量或更改治疗方案。
-- **遵医嘱**：患者在开始或停止使用任何药物前，应咨询医生或专业药师。
-### 免责声明
-本系统仅供参考，具体用药请遵医嘱。</t>
+   - **Severity**: Moderate
+   - **Mechanism Explanation**: The same mechanism applies here; Drospirenone can affect the serum concentration of Phenazopyridine.
+### Clinical Advice
+- **Monitoring**: It is advisable to monitor for symptom relief and efficacy while using these medications together. If symptoms do not improve, consider discussing with your healthcare provider about possible adjustments.
+- **Consult Healthcare Provider**: Always speak to your doctor before starting or stopping any medications.
+### Disclaimer
+This system is for reference only; please follow your doctor's advice for actual medication.</t>
         </is>
       </c>
     </row>
@@ -5228,8 +5995,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>There are no known major drug interactions between Vancomycin and Testosterone enanthate. However, it is always important to consider the individual patient's health status, other medications they may be taking, and their overall treatment plan. 
-While the interaction is classified as minor, it is advisable to consult with a healthcare provider for personalized advice and monitoring when taking these medications together.</t>
+          <t>There are no known major or moderate drug interactions between Vancomycin and Testosterone enanthate. However, it is always important to consider the individual patient's health status, other medications they may be taking, and their overall treatment plan. Minor interactions are not typically reported, but monitoring for any unusual side effects is advisable. Always consult with a healthcare provider for personalized medical advice.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -5266,27 +6032,26 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>I do not have specific information on a drug called Lortalamine, as it may not be widely recognized or may not have been included in my training data. Therefore, I cannot provide reliable information about the safety of combining Nabilone with Lortalamine.
-For any drug combination, it is always best to consult with a healthcare professional or a pharmacist who can provide personalized advice based on your medical history and current medications.</t>
+          <t>I do not have specific information regarding the interaction between Nabilone and Lortalamine. It is important to consult a healthcare professional or a pharmacist for personalized advice on drug interactions, as they can provide the most accurate and up-to-date information based on your individual health situation.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>### 药物相互作用信息
+          <t>### Drug Interaction Information
 1. **Nabilone × Lortalamine**
-   - **严重程度**: Moderate
-   - **描述**: Nabilone 可能会增加 Lortalamine 的中枢神经系统抑制作用。
+   - **Severity**: Moderate
+   - **Description**: Nabilone may increase the central nervous system depressant (CNS depressant) activities of Lortalamine.
 2. **Lortalamine × Nabilone**
-   - **严重程度**: Moderate
-   - **描述**: Lortalamine 可能与 Nabilone 的作用相互增强，导致中枢神经系统抑制。
-### 机制解释
-这两种药物都具有中枢神经系统抑制的作用，Nabilone 是一种类大麻素，而 Lortalamine 也是一种会影响神经系统的药物。当同时使用时，可能会导致过度的抑制效应，例如嗜睡、疲劳等副作用。
-### 临床建议
-1. **医生咨询**：在开始同时使用 Nabilone 和 Lortalamine 之前，务必咨询你的医生或药师，评估风险和获益。
-2. **监测症状**：如果医生允许你同时使用，请注意观察任何异常的嗜睡、头晕或疲劳等症状。
-3. **避免酒精**：同时服用 Nabilone 时，请避免饮酒，以免加重中枢神经系统抑制。
-### 免责声明
-本系统的信息仅供参考，具体用药请务必遵循医生的建议和处方。</t>
+   - **Severity**: Moderate
+   - **Description**: The combination may lead to increased CNS depression effects, which could cause symptoms like excessive drowsiness or fatigue.
+### Mechanism Explanation
+Both Nabilone and Lortalamine have CNS depressant effects. When taken together, these effects can be enhanced, leading to a higher risk of sedation and impaired cognitive function.
+### Clinical Advice
+1. **Consult Your Doctor**: Before taking Nabilone and Lortalamine together, consult your healthcare provider to evaluate the risks versus benefits specific to your situation.
+2. **Monitor for Symptoms**: If your doctor permits the combination, be vigilant for signs of excessive drowsiness, dizziness, or unusual fatigue.
+3. **Avoid Alcohol**: It is advisable to avoid alcohol while taking Nabilone, as it can further increase CNS depression.
+### Disclaimer
+This system is for reference only; please follow your doctor's advice for actual medication use.</t>
         </is>
       </c>
     </row>
@@ -5308,9 +6073,9 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>There are no well-documented major drug interactions between Tenofovir disoproxil and the Smallpox (Vaccinia) Vaccine, Live. However, it is important to note that Tenofovir disoproxil is an antiviral medication used primarily for the treatment of HIV and chronic hepatitis B, and it may have effects on the immune system.
-The live smallpox vaccine is contraindicated in individuals with compromised immune systems, which can include those on certain antiviral therapies. While Tenofovir disoproxil is not typically associated with significant immunosuppression, caution is advised when considering vaccination in patients receiving antiviral therapy.
-It is always best to consult with a healthcare provider for personalized medical advice, especially regarding vaccinations and potential interactions with ongoing treatments.</t>
+          <t>There are no well-documented major drug interactions between Tenofovir disoproxil and the Smallpox (Vaccinia) Vaccine, Live. However, it is important to note that Tenofovir disoproxil is an antiviral medication used primarily for the treatment of HIV and chronic hepatitis B, while the Smallpox vaccine is a live vaccine used to provide immunity against smallpox.
+Patients receiving Tenofovir disoproxil may have a compromised immune system, which could potentially affect the response to live vaccines. Therefore, while there is no direct interaction, caution is advised when administering live vaccines to individuals on immunosuppressive therapy.
+It is always best to consult with a healthcare provider for personalized medical advice and to discuss any potential risks based on individual health conditions and treatment regimens.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -5318,12 +6083,12 @@
           <t>以下是 Tenofovir disoproxil 与 Smallpox (Vaccinia) Vaccine, Live 之间的药物相互作用信息：
 1. **药物组合**：Tenofovir disoproxil × Smallpox (Vaccinia) Vaccine, Live  
    - **严重程度**：Minor  
-   - **机制解释**：使用 Tenofovir disoproxil 可能会降低 Smallpox (Vaccinia) Vaccine, Live 的疗效。Tenofovir 作为抗病毒药物，可能会干扰疫苗的免疫反应，从而影响疫苗的效果。  
-   - **临床建议**：如果同时使用这两种药物，建议在接种疫苗前告知医生，并考虑监测疫苗的免疫效果。如果条件允许，最好安排在不同时间使用这些药物，以减少相互作用的发生。
+   - **机制解释**：当 Tenofovir disoproxil 与 Smallpox (Vaccinia) Vaccine, Live 结合使用时，可能降低疫苗的治疗功效。这是因为 Tenofovir 可能干扰免疫系统对疫苗的反应。  
+   - **临床建议**：在接种小pox疫苗前，建议患者告知医生正在服用 Tenofovir disoproxil，以便评估任何潜在的影响。如果可以，尽量将这两种药物的使用时间分开，以减少相互作用的可能性。
 2. **药物组合**：Smallpox (Vaccinia) Vaccine, Live × Tenofovir disoproxil  
    - **严重程度**：Minor  
-   - **机制解释**：同上，Smallpox (Vaccinia) Vaccine, Live 的疗效可能因 Tenofovir 的使用而降低。  
-   - **临床建议**：同上，确保医生知晓正在使用的药物，以便于适时调整治疗方案。
+   - **机制解释**：同上，Smallpox (Vaccinia) Vaccine, Live 的疗效可以因 Tenofovir disoproxil 而降低。  
+   - **临床建议**：同上，确保医务人员了解到所有用药，以帮助做出最佳的治疗决策。
 **免责声明**：以上信息仅供参考，具体用药请遵医嘱。</t>
         </is>
       </c>
@@ -5346,28 +6111,28 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Foscarnet and the Smallpox (Vaccinia) Vaccine, Live should not be taken together due to a significant interaction. The combination is considered to have a **Major** severity level interaction.
-Foscarnet is an antiviral medication that can have immunosuppressive effects, which may interfere with the immune response to the live vaccine. The live smallpox vaccine is designed to stimulate an immune response, and using it in conjunction with an immunosuppressive agent like foscarnet could potentially reduce the vaccine's effectiveness and increase the risk of adverse effects.
-It is crucial to consult with a healthcare provider for personalized advice and to discuss alternative options or timing for these medications.</t>
+          <t>Foscarnet and the Smallpox (Vaccinia) Vaccine, Live should not be taken together due to a significant interaction. The combination is considered to have a **Major** severity level for drug interactions.
+Foscarnet is an antiviral medication that can have immunosuppressive effects, which may interfere with the immune response to the live vaccine. The live smallpox vaccine relies on a robust immune response to be effective, and using foscarnet concurrently could potentially diminish the vaccine's efficacy and increase the risk of adverse effects.
+It is crucial to consult with a healthcare provider for personalized advice and to discuss alternative treatment options or timing for these medications.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>以下是关于同时使用 Foscarnet 和 Smallpox (Vaccinia) Vaccine, Live 的重要信息：
-### 药物相互作用
+          <t>Here is what you should know about taking Foscarnet and Smallpox (Vaccinia) Vaccine, Live at the same time:
+### Drug Interaction
 1. **Foscarnet × Smallpox (Vaccinia) Vaccine, Live**
-   - **严重程度**：Minor
-   - **描述**：当 Foscarnet 与 Smallpox (Vaccinia) Vaccine, Live 同时使用时，后者的治疗效果可能会降低。
+   - **Severity**: Minor
+   - **Description**: The therapeutic efficacy of Smallpox (Vaccinia) Vaccine, Live can be decreased when used in combination with Foscarnet.
 2. **Smallpox (Vaccinia) Vaccine, Live × Foscarnet**
-   - **严重程度**：Minor
-   - **描述**：同样，当 Smallpox (Vaccinia) Vaccine, Live 与 Foscarnet 一同使用时，Smallpox 疫苗的疗效可能会受到影响。
-### 机制解释
-Foscarnet 是一种抗病毒药物，通过抑制病毒特异性的 DNA 聚合酶的活性来干扰病毒的复制。而 Smallpox 疫苗是一种活疫苗，旨在增强机体免疫反应以预防天花。当 Foscarnet 存在时，它可能会影响疫苗的有效性，导致免疫系统对疫苗产生的抗体反应减弱。
-### 临床建议
-- **使用建议**：如果您正在接受 Foscarnet 治疗，建议在接种 Smallpox (Vaccinia) Vaccine, Live 前咨询您的医生。医生可能会建议推迟接种疫苗，以确保获得最佳的免疫保护。
-- **监测症状**：若必须同时进行，注意监测接种疫苗后的任何不寻常症状，并与医疗提供者保持联系。
-### 免责声明
-本系统提供的信息仅供参考，具体用药方案请遵循医生的建议和指导。</t>
+   - **Severity**: Minor
+   - **Description**: The therapeutic efficacy of Smallpox (Vaccinia) Vaccine, Live can be decreased when used in combination with Foscarnet.
+### Mechanism Explanation
+Foscarnet is an antiviral medication that works by inhibiting the action of specific viral DNA polymerases, which are necessary for the reproduction of viruses. The Smallpox (Vaccinia) Vaccine, Live is a live vaccine intended to enhance the immune response and provide protection against smallpox. When Foscarnet is present, it may interfere with the effectiveness of the vaccine by preventing the immune system from responding robustly to the vaccine, hence reducing its efficacy.
+### Clinical Advice
+- **Consult Healthcare Provider**: If you are prescribed Foscarnet, it is important to talk to your healthcare provider before receiving the Smallpox vaccine. Your doctor may recommend delaying the vaccination to ensure optimal immune protection.
+- **Monitor for Symptoms**: If both medications are necessary, keep an eye out for any unusual symptoms after vaccination and maintain communication with your healthcare provider.
+### Disclaimer
+This system provides information for reference only; please follow your doctor's advice for actual medication.</t>
         </is>
       </c>
     </row>
@@ -5390,25 +6155,25 @@
       <c r="D30" t="inlineStr">
         <is>
           <t>I do not have specific information regarding interactions between Phalaris minor pollen and Cloranolol. Phalaris minor pollen is not a commonly referenced substance in drug interaction databases, and its effects and interactions may not be well-documented.
-Cloranolol is a beta-blocker used primarily for hypertension and other cardiovascular conditions. If you have concerns about potential interactions or side effects, it is best to consult your healthcare provider or a clinical pharmacist who can provide personalized advice based on your complete medical history and current medications.</t>
+Cloranolol, a beta-blocker, can have various interactions with other medications, but without specific data on Phalaris minor pollen, I cannot provide a definitive answer regarding potential interactions.
+It is essential to discuss any concerns with your healthcare provider or pharmacist, as they can provide personalized advice based on your complete medical history and current medications.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>根据提供的药物信息，以下是 Phalaris minor pollen 和 Cloranolol 之间的相互作用分析：
-### 药物组合
+          <t>### Drug Interaction Analysis
 1. **Phalaris minor pollen × Cloranolol**
-   - **严重程度**: Minor
-   - **机制解释**: 当 Phalaris minor pollen 与 Cloranolol 一起服用时，可能会增加对 Phalaris minor pollen 的过敏反应风险。这是因为 Cloranolol 可能影响免疫反应，使身体对过敏源更加敏感。
-   - **临床建议**: 尽量避免在服用 Cloranolol 时接触 Phalaris minor pollen。如果您出现过敏症状（如皮疹、瘙痒、呼吸困难等），请立即联系医生。
+   - **Severity**: Minor
+   - **Mechanism Explanation**: The combination of Phalaris minor pollen and Cloranolol may increase the risk of a hypersensitivity reaction to Phalaris minor pollen. Cloranolol could potentially enhance sensitivity to allergens, making your body more reactive to pollen.
+   - **Clinical Advice**: Monitor for any signs of allergic reactions such as rash, itching, or difficulty breathing. If you experience any of these symptoms, contact your healthcare provider promptly.
 2. **Cloranolol × Phalaris minor pollen**
-   - **严重程度**: Minor
-   - **机制解释**: 同上，结合使用可能会增加对 Phalaris minor pollen 的过敏反应风险。
-   - **临床建议**: 请遵循上述建议。
-### 食物禁忌
-- **未找到记录**: 据此数据库，关于食物禁忌信息未找到。
-### 免责声明
-请注意，此系统仅供参考，具体用药请遵医嘱。如果您有任何疑虑，请与您的医生或药师沟通。</t>
+   - **Severity**: Minor
+   - **Mechanism Explanation**: This interaction is the same as the one listed above; combining these two can increase hypersensitivity risks.
+   - **Clinical Advice**: Follow the same recommendations as mentioned above regarding allergic symptoms.
+### Food Interactions
+- **No record found**: There are no documented food interactions for these medications.
+### Disclaimer
+Please remember that this system is for reference only, and it is essential to follow your doctor's advice regarding your medications. If you have any concerns, don't hesitate to discuss them with your healthcare provider.</t>
         </is>
       </c>
     </row>
@@ -5431,22 +6196,23 @@
       <c r="D31" t="inlineStr">
         <is>
           <t>I do not have reliable information regarding a specific interaction between Indenolol and Phalaris minor pollen. Indenolol is a beta-blocker used primarily for hypertension and other cardiovascular conditions, while Phalaris minor pollen is not a commonly referenced substance in pharmacology. 
-For accurate and personalized advice, it is always best to consult a healthcare professional or a pharmacist who can provide information based on the latest research and clinical guidelines.</t>
+For any potential interactions, especially with herbal or less commonly studied substances, it is always best to consult a healthcare professional or a pharmacist who can provide personalized advice based on the most current and comprehensive data.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>### 药物相互作用信息
-**药物组合**: Indenolol × Phalaris minor pollen  
-- **严重程度**: Minor
-- **描述**: 合用时增加对 Phalaris minor pollen 的过敏反应风险。
-### 机制解释
-当 Indenolol 与 Phalaris minor pollen 同时使用时，有可能导致免疫系统对 Phalaris minor pollen 产生更强的过敏反应。这是因为 Indenolol 在某些情况下可能会影响身体对过敏原的反应。
-### 临床建议
-- 如果您在服用 Indenolol 的同时接触 Phalaris minor pollen（如在花粉季节），请注意监测过敏反应的迹象（如皮疹、瘙痒、呼吸困难等）。
-- 如发现任何过敏症状，建议及时联系医生并在必要时调整治疗方案。
-### 免责声明
-本系统仅供参考，具体用药请遵医嘱。</t>
+          <t>### Drug Interaction Information
+**Drug Combination**: Indenolol × Phalaris minor pollen  
+- **Severity**: Minor
+- **Description**: The risk of a hypersensitivity reaction to Phalaris minor pollen is increased when it is combined with Indenolol.
+### Mechanism Explanation
+The combination of Indenolol and Phalaris minor pollen may heighten the body's immune response toward the pollen, potentially leading to a higher risk of allergic reactions. This happens because Indenolol can affect how the immune system reacts to allergens.
+### Clinical Advice
+- Be cautious if you are using Indenolol while being exposed to Phalaris minor pollen, especially during peak pollen season.
+- Monitor for any signs of allergic reactions, such as rash, itching, or difficulty breathing. 
+- Consult your healthcare provider if you experience any allergic symptoms or if there is a need to adjust your medication.
+### Disclaimer
+This system is for reference only; please follow your doctor's advice for actual medication.</t>
         </is>
       </c>
     </row>
@@ -5468,26 +6234,26 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>The combination of Penciclovir and the Smallpox (Vaccinia) Vaccine, Live does not have well-documented interactions. However, since Penciclovir is an antiviral medication used primarily for herpes virus infections, and the smallpox vaccine is a live vaccine, caution is generally advised when combining antiviral medications with live vaccines.
-While there is no specific major or moderate interaction reported, the use of antivirals can potentially affect the immune response to live vaccines. Therefore, it is recommended to consult with a healthcare provider for personalized advice and to consider the timing of administration if both are necessary.
-In summary, while there is no clear evidence of a significant interaction, it is best to seek professional guidance before combining these two.</t>
+          <t>The combination of Penciclovir and the Smallpox (Vaccinia) Vaccine, Live does not have well-documented interactions. However, Penciclovir is an antiviral medication primarily used for the treatment of herpes simplex virus infections, and it is not known to have a direct interaction with live vaccines like the smallpox vaccine.
+That said, live vaccines can sometimes be affected by antiviral medications, particularly those that are nucleoside analogs, as they may theoretically interfere with viral replication. However, Penciclovir is not typically associated with major interactions with live vaccines.
+Given the lack of specific data, it is advisable to consult with a healthcare provider for personalized medical advice, especially if there are underlying health conditions or other medications involved. Always ensure that any vaccination is discussed with a healthcare professional who can consider the full clinical picture.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>### 药物相互作用信息
-1. **相互作用**: Penciclovir × Smallpox (Vaccinia) Vaccine, Live
-   - **严重程度**: Minor
-   - **机制解释**: 当 Penciclovir 与 Smallpox (Vaccinia) Vaccine, Live 一起使用时，可能会降低后者的治疗效果。这是因为 Penciclovir 可能通过抑制病毒的复制，影响疫苗的有效性。
-   - **临床建议**: 如果您需要接种天花疫苗或正在接受 Penciclovir 治疗，请与您的医生讨论，看看是否需要调整用药方案。
-2. **相互作用**: Smallpox (Vaccinia) Vaccine, Live × Penciclovir
-   - **严重程度**: Minor
-   - **机制解释**: 同上，Smallpox (Vaccinia) Vaccine, Live 与 Penciclovir 的组合也可能会降低疫苗的治疗效能。
-   - **临床建议**: 请在接种疫苗前咨询医生，确认是否合适继续使用 Penciclovir。
-### 食物禁忌
-- 未找到记录。
-### 免责声明
-请注意，本系统仅供参考，具体的用药请遵医嘱。建议您与医生进行详细咨询，以确保用药安全。</t>
+          <t>### Drug Interaction Information
+1. **Interaction**: Penciclovir × Smallpox (Vaccinia) Vaccine, Live
+   - **Severity**: Minor
+   - **Mechanism Explanation**: The therapeutic efficacy of Smallpox (Vaccinia) Vaccine, Live can be decreased when used in combination with Penciclovir. This occurs because Penciclovir may suppress viral replication, potentially affecting the vaccine's effectiveness.
+   - **Clinical Advice**: If you are receiving Penciclovir and are also scheduled to receive the Smallpox vaccine, discuss this with your healthcare provider. They can advise you on the timing and safety of using these medications together.
+2. **Interaction**: Smallpox (Vaccinia) Vaccine, Live × Penciclovir
+   - **Severity**: Minor
+   - **Mechanism Explanation**: The same explanation applies; the vaccine's effectiveness may be reduced due to the presence of Penciclovir.
+   - **Clinical Advice**: Consult your doctor regarding the use of Penciclovir and the Smallpox vaccine to ensure both safety and efficacy.
+### Food Interactions
+- No record found.
+### Disclaimer
+Please note that this system is for reference only; always follow your doctor's advice for actual medication concerns.</t>
         </is>
       </c>
     </row>
@@ -5509,23 +6275,23 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>I do not have specific information regarding the interaction between Daprodustat and Etifoxine. Therefore, I cannot provide a reliable assessment of any potential risks or interaction severity levels for this combination. It is always best to consult a healthcare professional or a clinical pharmacist for personalized advice regarding drug interactions.</t>
+          <t>I do not have specific information regarding the interaction between Daprodustat and Etifoxine. Therefore, I cannot provide a reliable assessment of any potential risks or interaction severity levels for this combination. It is always best to consult a healthcare professional or a pharmacist for personalized advice regarding drug interactions.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>### 药物组合相互作用信息：
-- **药物组合**: Daprodustat 和 Etifoxine
-- **相互作用**: 未找到记录
-### 严重程度标注：
-- **Severity**: 不适用（未找到记录）
-### 机制解释：
-由于数据库中没有记录表明 Daprodustat 和 Etifoxine 之间存在相互作用，因此我们无法提供具体的机制解释。
-### 临床建议：
-1. **用药安全性**: 尽管没有找到这两种药物之间的相互作用记录，但在开始任何新药物之前，建议与医生或药师进行咨询，以确保用药的安全性。
-2. **监测反应**: 使用这两种药物时，建议密切监测自身的反应和副作用。如有不适或异常反应，及时向医生报告。
-### 免责声明：
-本系统仅供参考，具体用药请遵医嘱。</t>
+          <t>### Drug Interaction Information
+- **Drug Pair**: Daprodustat and Etifoxine
+- **Interaction**: No record found
+### Severity Labeling
+- **Severity**: Not applicable (No records found)
+### Mechanism Explanation
+Since there are no interaction records indicating a relationship between Daprodustat and Etifoxine, we cannot provide a specific mechanism explanation.
+### Clinical Advice
+1. **Medication Safety**: While no documented interactions exist between these two medications, it is advisable to consult your physician or pharmacist before starting any new medications to ensure safety.
+2. **Monitoring Responses**: If you choose to use either or both, monitor for any adverse effects and report any unusual symptoms to your healthcare provider promptly.
+### Disclaimer
+This system is for reference only; please follow your doctor's advice for actual medication use.</t>
         </is>
       </c>
     </row>
@@ -5553,17 +6319,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>### 药物组合：Daprodustat 和 Galsulfase
-1. **相互作用记录**：
-   - **未找到记录** 
-2. **严重程度**：
-   - **N/A**（因为没有记录相互作用）
-3. **机制解释**：
-   - Daprodustat 和 Galsulfase 之间没有已知的相互作用，因此在同时使用时通常被认为是安全的。Daprodustat 是一种用于治疗由慢性肾脏病引起的贫血的药物，而 Galsulfase 是一种治疗黏多糖症 VI 型（MPS VI）的酶替代疗法。这两种药物在机理上不会相互干扰。
-4. **临床建议**：
-   - 尽管目前没有记录显示 Daprodustat 和 Galsulfase 之间存在相互作用，建议您在开始同时使用这两种药物之前，咨询医生或药师。他们可以根据您的具体病史和用药情况提供个性化建议。
-5. **免责声明**：
-   - 本系统仅供参考，具体用药请遵医嘱。</t>
+          <t>### Drug Combination: Daprodustat and Galsulfase
+1. **Interaction Records**:
+   - **No record found**
+2. **Severity**:
+   - **N/A** (No interactions recorded)
+3. **Mechanism Explanation**:
+   - There are no known interactions between Daprodustat and Galsulfase, indicating they can generally be used together safely. Daprodustat is used for treating anemia caused by chronic kidney disease, while Galsulfase is an enzyme replacement therapy for mucopolysaccharidosis type VI (MPS VI). Their pharmacological actions do not conflict with each other.
+4. **Clinical Advice**:
+   - While there are no documented interactions between Daprodustat and Galsulfase, it's always a good practice to consult with your healthcare provider or pharmacist before starting the simultaneous use of these medications. They can provide personalized advice based on your medical history and current medications.
+5. **Disclaimer**:
+   - This system is for reference only; please follow your doctor's advice for actual medication.</t>
         </is>
       </c>
     </row>
@@ -5585,23 +6351,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>I do not have specific information on a drug called "Rosin." If you meant a different medication or if "Rosin" refers to a supplement or herbal product, please clarify. 
-As for Daprodustat, it is a medication used to treat anemia in patients with chronic kidney disease. If you provide the correct name or more details about "Rosin," I can help you assess any potential interactions.</t>
+          <t>I do not have specific information on a drug called "Rosin." If you meant a different medication or if "Rosin" refers to a specific formulation or product, please clarify. 
+As for Daprodustat, it is a medication used to treat anemia associated with chronic kidney disease. If you provide the correct name or more details about "Rosin," I can help you assess any potential interactions. Otherwise, I recommend consulting a healthcare professional or a pharmacist for personalized advice regarding drug interactions.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>根据当前的药物数据库信息，Daprodustat (DB11682) 和 Rosin (DB11165) 之间的相互作用记录如下：
-### 药物相互作用
-- **Daprodustat 与 Rosin**：未找到记录
-### 严重程度标注
-- **相互作用严重程度**：无（未找到相互作用记录）
-### 机制解释
-- 由于未找到这两种药物之间的相互作用记录，说明目前的研究和数据表明在安全性方面没有明显的警告或禁忌。
-### 临床建议
-- 根据缺乏相互作用记录，可以推测在临床上这两种药物在一起使用是安全的。然而，建议患者在服用任何新药物时，仍需咨询医生或药剂师，以确保综合评估其他个体因素和用药历史。
-### 免责声明
-- 请注意，本系统仅供参考，具体用药请遵医嘱。</t>
+          <t>### Drug Interaction Summary
+- **Daprodustat and Rosin**: No interaction records found.
+### Severity Labeling
+- **Interaction Severity**: N/A (No interaction found)
+### Mechanism Explanation
+- There are currently no documented interactions between Daprodustat and Rosin, indicating that their combined use has not shown any adverse effects based on available data.
+### Clinical Advice
+- It appears that Daprodustat and Rosin can be taken together without known risks. However, it is always recommended to consult with a healthcare provider or pharmacist before starting any new medications to ensure individual health considerations are taken into account.
+### Disclaimer
+- Please remember that this system is for reference only; always follow your doctor's advice for actual medication use.</t>
         </is>
       </c>
     </row>
@@ -5624,22 +6389,22 @@
       <c r="D36" t="inlineStr">
         <is>
           <t>I do not have specific information regarding the interaction between Daprodustat and Ipecac. Daprodustat is a medication used to treat anemia associated with chronic kidney disease, while Ipecac is an emetic used to induce vomiting in cases of poisoning. 
-Since I do not have reliable data on this specific combination, I recommend consulting a healthcare professional or a clinical pharmacist for personalized advice regarding potential interactions and safety.</t>
+Since there is no well-documented interaction available, it is best to consult a healthcare professional or a clinical pharmacist for personalized advice regarding the safety of combining these two medications.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>### 药物相互作用查询结果
-- **药物组合**: Daprodustat (Daprodustat, DB11682) 和 Ipecac (Ipecac, DB13293)
-- **相互作用记录**: 未找到记录
-### 说明与建议
-1. **严重程度**: 不适用（未找到记录）
-2. **机制解释**: 由于在相关数据库中未找到关于这两种药物的相互作用记录，说明当前没有已知的生理或药理机制会导致这两者之间的相互干扰。
-3. **临床建议**: 
-   - 在没有明确的相互作用记录的情况下，临床上通常认为这两种药物不太可能生成不良反应。
-   - 仍然建议患者在使用这两种药物时，咨询医生或专业的医疗人员以获得个性化的用药指导。
-### 免责声明
-请注意，本系统仅供参考，具体用药请遵医嘱。如有疑问或特殊情况，建议及时与医生联系。</t>
+          <t>### Drug Interaction Inquiry
+- **Drug Combination**: Daprodustat (Daprodustat, DB11682) and Ipecac (Ipecac, DB13293)
+- **Interaction Record**: No record found
+### Explanation and Recommendations
+1. **Severity**: Not applicable (No interaction record)
+2. **Mechanism Explanation**: Since there are no documented interactions between Daprodustat and Ipecac, this suggests that there are currently no known physiological or pharmacological mechanisms that would lead to an adverse interaction between these two drugs.
+3. **Clinical Advice**: 
+   - Given the absence of documented interactions, it is generally considered that these two medications can be used together without significant risk.
+   - However, it is always advisable to inform your healthcare provider about all medications you are taking, including over-the-counter drugs such as Ipecac, to ensure personalized safety and monitoring.
+### Disclaimer
+Please note that this system is for reference only. Always follow your doctor’s advice for actual medication questions and treatments. If you have any other concerns or specific conditions, please consult your healthcare provider.</t>
         </is>
       </c>
     </row>
@@ -5661,22 +6426,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>I do not have specific information regarding the interaction between Daprodustat and Apramycin. It is important to consult a healthcare professional or a reliable drug interaction database for the most accurate and up-to-date information regarding potential interactions between these two medications.</t>
+          <t>I do not have specific information regarding the interaction between Daprodustat and Apramycin. It is important to consult a healthcare professional or a reliable drug interaction database for the most accurate and up-to-date information regarding potential interactions between these two medications. Always prioritize safety and professional guidance when considering drug combinations.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>根据提供的药物数据库信息，Daprodustat 和 Apramycin 的组合没有发现任何相互作用记录。以下是详细信息：
-1. **药物组合**：Daprodustat (DB11682) 和 Apramycin (DB04626)
-2. **药物相互作用**：未找到记录
-3. **严重程度标注**：未适用（无相互作用）
-4. **机制解释**：
-   - Daprodustat 是一种用于治疗慢性肾病引起贫血的药物，而 Apramycin 是一种 aminoglycoside 抗生素。由于数据库未提供两者之间的相互作用，因此可以认为没有特定的药理机制会导致相互作用。
-5. **临床建议**：
-   - 尽管未发现直接的药物相互作用，但使用任何药物组合时都应遵循医师的建议。请与医疗专业人士讨论并确认同时使用这两种药物的安全性。
-6. **免责声明**：
-   - 本系统仅供参考，具体用药请遵医嘱。
-如有其他问题，欢迎随时询问！</t>
+          <t>Based on the drug database information provided, there are no recorded interactions between Daprodustat and Apramycin. Here are the details:
+1. **Drug Combination**: Daprodustat (DB11682) and Apramycin (DB04626)
+2. **Drug Interactions**: No records found
+3. **Severity Labeling**: Not applicable (no interaction)
+4. **Mechanism Explanation**:
+   - Daprodustat is used for treating anemia due to chronic kidney disease, while Apramycin is an aminoglycoside antibiotic. The absence of documented interactions suggests that there are no known pharmacological mechanisms that would lead to significant risks when used together.
+5. **Clinical Advice**:
+   - Although there are no documented interactions, it is always recommended to consult with your healthcare provider before combining medications to ensure safety and suitability based on your health condition.
+6. **Disclaimer**:
+   - This system is for reference only; please follow your doctor's advice for actual medication use.
+If you have further questions or concerns, feel free to ask!</t>
         </is>
       </c>
     </row>
@@ -5698,18 +6463,16 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>As of my last training data up to October 2023, there is no well-documented interaction between Daprodustat and Cyproterone acetate. However, both drugs can have effects on the hematologic system and hormonal pathways, so caution is always advised when using them together.
-Daprodustat is primarily used for the treatment of anemia associated with chronic kidney disease, while Cyproterone acetate is an anti-androgen used for various conditions, including hormone-related disorders. 
-Since specific interactions may not be well-studied or documented, it is essential to monitor for any unusual side effects or changes in therapeutic effects when these medications are used concurrently. Always consult with a healthcare provider or a clinical pharmacist for personalized advice and monitoring.</t>
+          <t>As of my last training data up to October 2023, there is limited specific information available regarding drug interactions between Daprodustat and Cyproterone acetate. Daprodustat is a hypoxia-inducible factor prolyl hydroxylase inhibitor used for the treatment of anemia in chronic kidney disease, while Cyproterone acetate is an anti-androgen and progestin used for various conditions, including hormonal therapy.
+Since there is no well-documented interaction between these two medications, I cannot classify the interaction as Major, Moderate, or Minor. However, it is always important to consult a healthcare professional or a clinical pharmacist for personalized advice, especially considering individual patient factors and the potential for unique interactions based on other medications or health conditions.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>### 药物相互作用查询结果
-- **Daprodustat** 与 **Cyproterone acetate** 之间的相互作用
-  - **相互作用记录**：未找到记录
-### 免责声明
-本系统仅供参考，具体用药请遵医嘱。</t>
+          <t>### Drug Interactions between Daprodustat and Cyproterone Acetate
+- **Interaction Record**: No records found.
+### Disclaimer
+This system is for reference only; follow your doctor's advice for actual medication.</t>
         </is>
       </c>
     </row>
@@ -5733,26 +6496,25 @@
         <is>
           <t>There is limited information available regarding the interaction between Daprodustat and Ethanolamine oleate. Daprodustat is primarily used for the treatment of anemia associated with chronic kidney disease, while Ethanolamine oleate is typically used as a sclerosing agent for varicose veins and other conditions.
 As of my last training data in October 2023, there are no well-documented major or moderate interactions between these two drugs. However, it is always important to consider the individual patient's health status, other medications, and overall treatment plan.
-I recommend discussing this combination with your healthcare provider or pharmacist to ensure safety and efficacy in your specific case. They can provide personalized advice based on your complete medical history and current medication regimen.</t>
+I recommend discussing this combination with your healthcare provider or pharmacist to ensure safety and efficacy in your specific case. They can provide the most personalized and up-to-date information.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>根据药物数据库的信息，以下是 Daprodustat 和 Ethanolamine oleate 之间的相互作用分析：
-### 药物相互作用
-- **Daprodustat与Ethanolamine oleate**：
-  - **相互作用记录**：未找到记录。
-### 严重程度标注
-- **相互作用严重程度**：未标记（没有相互作用记录）。
-### 机制解释
-- 由于在数据库中没有找到这两种药物之间的相互作用记录，因此当前没有已知的相互作用机制。一般来说，如果药物之间没有相互作用，那么它们在体内可能不会互相影响。
-### 临床建议
-- 虽然目前没有发现 Daprodustat 和 Ethanolamine oleate 之间的相互作用，但还是建议遵循以下建议：
-  1. 与您的医生或药师保持沟通，以确保在使用这两种药物时不会出现问题。
-  2. 定期监测您的健康状况，特别是使用 Daprodustat 期间。
-  3. 始终如实告知医生您正在服用的所有药物（包括非处方药和草药补充剂）。
-### 免责声明
-本系统仅供参考，具体用药请遵医嘱。如有任何不适或疑虑，请及时咨询您的医生或药师。</t>
+          <t>### Drug Interaction Analysis
+- **Daprodustat and Ethanolamine oleate**:
+  - **Interaction Record**: No record found.
+### Severity Labeling
+- **Interaction Severity**: Not applicable (No interaction records).
+### Mechanism Explanation
+- Since there are no documented interactions between Daprodustat and Ethanolamine oleate, there are no known mechanisms indicating that these two medications affect each other’s actions in the body.
+### Clinical Advice
+- While there are no known interactions, it is advisable to:
+  1. Continue to communicate with your healthcare provider about all the medications you are taking, including Daprodustat and Ethanolamine oleate.
+  2. Monitor your health for any unusual symptoms, especially while on Daprodustat.
+  3. Always inform your doctor about any over-the-counter medications or supplements you may consider taking in the future.
+### Disclaimer
+This system is for reference only; please follow your doctor's advice for actual medication. If you have any concerns or experience any side effects, consult your healthcare provider promptly.</t>
         </is>
       </c>
     </row>
@@ -5774,28 +6536,27 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>I do not have specific information regarding the interaction between Daprodustat and Aspergillus terreus. Daprodustat is a medication used for the treatment of anemia in chronic kidney disease, while Aspergillus terreus is a type of fungus that can be associated with infections, particularly in immunocompromised patients.
-Since Aspergillus terreus is not a medication but rather a pathogen, the context of its use (e.g., as a source of infection or in a laboratory setting) is important for assessing safety. If you are considering the use of Daprodustat in the context of an infection caused by Aspergillus terreus, it is crucial to consult with a healthcare professional for a thorough evaluation of your specific situation.
-For any drug interactions or safety concerns, please consult your healthcare provider or a clinical pharmacist who can provide personalized advice based on your medical history and current medications.</t>
+          <t>I do not have specific information regarding the interaction between Daprodustat and Aspergillus terreus. Daprodustat is a medication used to treat anemia associated with chronic kidney disease, while Aspergillus terreus is a type of fungus that can be associated with infections, particularly in immunocompromised patients.
+Since Aspergillus terreus is not a medication but rather a pathogen, the context of its use (e.g., as a source of infection or in a laboratory setting) is important for assessing safety. If you are concerned about a potential infection or treatment involving Aspergillus terreus, it is crucial to consult with a healthcare professional who can provide guidance based on your specific health situation.
+For any drug interactions or safety concerns, always consult with a healthcare provider or a clinical pharmacist for personalized advice.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>根据数据库信息，Daprodustat 和 Aspergillus terreus 之间没有记录的相互作用。以下是详细信息：
-### 药物组合信息：
+          <t>### Drug Interaction Assessment
 1. **Daprodustat**
-   - 严重程度：未找到记录
-   - 机制解释：无相互作用信息
-   - 临床建议：Daprodustat 可与食物一起或不一起服用，且不受其他补充剂（如铁或磷结合剂）影响。可在透析时间内任意服用。
+   - **Interaction Severity**: No record found
+   - **Mechanism Explanation**: There is no interaction information available for this drug.
+   - **Clinical Advice**: Daprodustat can be taken with or without food, and it is not affected by the timing of other medications or dialysis.
 2. **Aspergillus terreus**
-   - 严重程度：未找到记录
-   - 机制解释：无相互作用信息
-   - 临床建议：Aspergillus terreus 是一种真菌，通常用于过敏测试，具体使用需要根据临床需要。
-### 总结：
-- **相互作用**：未找到记录
-- **临床建议**：根据现有资料，Daprodustat 和 Aspergillus terreus 的组合未显示相互作用，但请在使用前咨询您的医生以确保安全性。
-### 免责声明：
-本系统的建议仅供参考，具体用药请遵医嘱。</t>
+   - **Interaction Severity**: No record found
+   - **Mechanism Explanation**: Aspergillus terreus itself does not have interaction records in relation to Daprodustat.
+   - **Clinical Advice**: Aspergillus terreus is primarily used in allergenic testing and its usage should be determined based on clinical need.
+### Conclusion:
+- **Interaction Status**: No record found of interactions between Daprodustat and Aspergillus terreus.
+- **Overall Safety**: Based on the available information, this combination does not show any known drug interactions.
+### Important Note:
+Please remember that this system serves as a reference only. It is crucial to follow your doctor’s advice regarding any medication or combination thereof.</t>
         </is>
       </c>
     </row>
@@ -5823,19 +6584,16 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>根据药物数据库的查询结果，以下是关于 Daprodustat 和 Volanesorsen 的相互作用信息：
-### 药物组合
-- **Daprodustat**
-- **Volanesorsen**
-### 药物相互作用
-- **未找到记录**
-### 机制解释
-由于数据库中没有记录这两种药物之间的相互作用，无法提供具体的机制解释。
-### 临床建议
-1. 虽然没有相互作用记录，但仍然建议在使用这两种药物时密切监控患者的反应，特别是在联合用药初期。
-2. 使用前请咨询医师或药师，以确保安全性和适宜性。
-### 免责声明
-本系统仅供参考，具体用药请遵医嘱。</t>
+          <t>### Drug Interaction Information
+- **Drug Pair:** Daprodustat and Volanesorsen
+- **Interaction:** No record found
+### Mechanism Explanation
+Since there are no interaction records found between Daprodustat and Volanesorsen, there is no specific mechanism to explain.
+### Clinical Advice
+1. Although no interactions are noted, it is advisable to closely monitor any patient responses when these medications are used together, particularly when initiating treatment.
+2. Always consult your healthcare provider before starting or combining medications to ensure their safety and appropriateness for your individual health needs.
+### Disclaimer
+This system is for reference only. Please follow your doctor's advice for actual medication.</t>
         </is>
       </c>
     </row>
@@ -5858,22 +6616,21 @@
       <c r="D42" t="inlineStr">
         <is>
           <t>There is no well-documented interaction between Daprodustat and Menthyl salicylate in the available literature. Daprodustat is primarily used for the treatment of anemia associated with chronic kidney disease, while Menthyl salicylate is a topical analgesic used for pain relief.
-Since there is no specific information indicating a significant interaction, it is generally considered safe to use them together. However, it is always best to consult with a healthcare provider or pharmacist for personalized advice, especially considering individual health conditions and other medications.</t>
+Since there is no specific information indicating a major, moderate, or minor interaction, it is generally considered safe to use them together. However, it is always best to consult with a healthcare provider or pharmacist for personalized advice, especially if you have underlying health conditions or are taking other medications.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>根据药物数据库的查询结果，Daprodustat 和 Menthyl salicylate 的相互作用记录如下：
-### 药物相互作用
-- **Daprodustat**与 **Menthyl salicylate**：未找到记录
-### 严重程度标注
-- **相互作用严重程度**：未找到记录
-### 机制解释
-- 由于未找到这两种药物之间的相互作用记录，说明它们在当前的医学文献和数据库中没有已知的相互作用。这意味着在理论上，它们可以一起使用而不会产生已知的药理学问题。
-### 临床建议
-- 尽管目前没有记录表明这两种药物之间存在相互作用，但在开始任何新的药物治疗之前，建议咨询医生或药师，尤其是在您有其他健康状况或正在服用其他药物的情况下。这可以确保您的用药安全性和有效性。
-### 免责声明
-- 请注意，本系统仅供参考，具体用药请遵医嘱。</t>
+          <t>### Drug Interaction Assessment
+- **Daprodustat** and **Menthyl salicylate**: **No record found**
+### Severity Labeling
+- **Interaction Severity**: **Not applicable** (no interactions found)
+### Mechanism Explanation
+- Since there are no recorded interactions between Daprodustat and Menthyl salicylate, it indicates that they do not influence each other's effects in the body. Thus, they can theoretically be taken together without known adverse interactions.
+### Clinical Advice
+- Although there are no known interactions, it is always advisable to consult with a healthcare provider or pharmacist before starting new medications, especially if you are taking other drugs or have underlying health conditions. This ensures safe and effective use of all medications.
+### Disclaimer
+- Please remember that this system is for reference only; always follow your doctor's advice for actual medication use.</t>
         </is>
       </c>
     </row>
@@ -5899,32 +6656,32 @@
 1. **Incadronic Acid**: There are no well-documented major drug interactions with Incadronic acid. However, it is always important to monitor for any unusual symptoms or side effects.
 2. **Amdinocillin**: Amdinocillin is a penicillin antibiotic, and while it generally has a good safety profile, it can interact with other medications. There are no major interactions specifically noted with Incadronic acid or Dexrabeprazole.
 3. **Dexrabeprazole**: This medication is a proton pump inhibitor (PPI) and is generally well-tolerated. It can affect the absorption of certain medications that require an acidic environment for optimal absorption, but there are no major interactions noted with Incadronic acid or Amdinocillin.
-Overall, based on the available data, there are no major or moderate interactions between Incadronic acid, Amdinocillin, and Dexrabeprazole. However, it is always best to consult with your healthcare provider or pharmacist for personalized advice and to discuss any specific concerns you may have.</t>
+Overall, based on the available data, there are no major or moderate interactions between Incadronic acid, Amdinocillin, and Dexrabeprazole. However, it is always best to consult with your healthcare provider or pharmacist for personalized advice and to ensure that your specific health conditions and other medications are taken into account.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>根据提供的信息，以下是您所用药物之间的相互作用分析：
-### 药物相互作用
+          <t>Based on the information provided, here are the drug interactions regarding the medications you are taking:
+### Drug Interactions
 1. **Incadronic acid × Dexrabeprazole**
-   - **严重程度**：Unknown
-   - **描述**：使用 Dexrabeprazole 时，Incadronic acid 的治疗效果可能会降低。
-   - **机制**：Dexrabeprazole 作为一种质子泵抑制剂，可能影响胃酸分泌，从而影响某些药物的吸收或疗效。
-   - **临床建议**：建议在使用这两种药物时进行监测，特别是观察治疗效果是否有所降低。如果有任何不适，及时咨询医生。
+   - **Severity**: Unknown
+   - **Description**: The therapeutic efficacy of Incadronic acid can be decreased when used in combination with Dexrabeprazole.
+   - **Mechanism**: Dexrabeprazole, as a proton pump inhibitor (PPI), may affect gastric acid secretion, which could impact the absorption or effectiveness of Incadronic acid.
+   - **Clinical Advice**: Monitor the effectiveness of Incadronic acid. If you notice any change in your condition or effectiveness of the treatment, consult your healthcare provider for further assessment.
 2. **Dexrabeprazole × Incadronic acid**
-   - **严重程度**：Unknown
-   - **描述**：如上所述，Dexrabeprazole 的使用可能会降低 Incadronic acid 的疗效。
-   - **机制**：同上。
-   - **临床建议**：与上述相同，监测疗效并与医生讨论可能的替代治疗方案。
+   - **Severity**: Unknown
+   - **Description**: As mentioned above, combining Dexrabeprazole with Incadronic acid may reduce the therapeutic efficacy of Incadronic acid.
+   - **Mechanism**: Same as above.
+   - **Clinical Advice**: Same as above; observe for any changes in treatment response and discuss concerns with your healthcare provider.
 3. **Incadronic acid × Amdinocillin**
-   - **未找到记录**
+   - **No record found**
 4. **Amdinocillin × Dexrabeprazole**
-   - **未找到记录**
-### 总结
-- 当前只有 Incadronic acid 和 Dexrabeprazole 之间的相互作用被记录。
-- Amdinocillin 和其他药物之间未发现记录。
-### 免责声明
-请注意，以上信息仅供参考，具体用药应遵医嘱。如有不适或需调整用药，请及时咨询医生。</t>
+   - **No record found**
+### Summary
+- There is a noted potential interaction between Incadronic acid and Dexrabeprazole. 
+- No interactions were found for Amdinocillin with either drug.
+### Disclaimer
+Please remember that this information is for reference only. It's crucial to follow your doctor's advice regarding your medications. If you experience any issues or have further questions, consult your healthcare provider.</t>
         </is>
       </c>
     </row>
@@ -5946,34 +6703,34 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>As of my last training data up to October 2023, there is limited specific information available regarding interactions between Incadronic acid, Amdinocillin, and Dexrabeprazole. 
-1. **Incadronic Acid**: This is a bisphosphonate used primarily for the treatment of osteoporosis. It generally has a low potential for drug interactions, but it is important to avoid taking it with other medications that can affect calcium levels or renal function.
-2. **Amdinocillin**: This is a penicillin antibiotic. It can interact with other medications that affect renal function or that are also excreted via the kidneys. 
+          <t>I do not have specific information on interactions between Incadronic acid, Amdinocillin, and Dexrabeprazole. However, I can provide some general insights:
+1. **Incadronic Acid**: This is a bisphosphonate used primarily for the treatment of osteoporosis. It generally has a low potential for drug interactions, but it is important to avoid taking it with certain medications that can affect calcium levels or renal function.
+2. **Amdinocillin**: This is a penicillin antibiotic. Antibiotics can sometimes interact with other medications, particularly those that are metabolized by the liver or that affect gut flora.
 3. **Dexrabeprazole**: This is a proton pump inhibitor (PPI) used to reduce stomach acid. PPIs can affect the absorption of certain medications, particularly those that require an acidic environment for optimal absorption.
-**Potential Interactions**:
-- **Incadronic Acid and Dexrabeprazole**: There is a theoretical concern that PPIs like Dexrabeprazole may reduce the absorption of bisphosphonates, including Incadronic acid, due to changes in gastric pH. However, the clinical significance of this interaction is not well established and may be considered minor.
-- **Amdinocillin and Dexrabeprazole**: There are no significant interactions reported between Amdinocillin and Dexrabeprazole. However, as with any antibiotic, it is important to monitor for any unexpected effects.
-- **Incadronic Acid and Amdinocillin**: There are no well-documented interactions between these two medications.
-In summary, while there may be minor concerns regarding the interaction between Incadronic acid and Dexrabeprazole, there are no major interactions reported among the three drugs. Always consult with a healthcare provider for personalized advice and to monitor for any potential side effects or interactions.</t>
+While I cannot provide specific interaction data for this combination, it is advisable to monitor for any unusual symptoms or side effects when these medications are used together. Always consult a healthcare provider or a clinical pharmacist for personalized advice and to check for the most current interaction data.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>以下是根据您提供的药物信息所识别的相互作用：
+          <t>Based on the provided drug information, here are the identified potential interactions for the drug pairs mentioned:
 ### 1. Incadronic acid × Dexrabeprazole
-- **相互作用严重程度**：Unknown
-- **机制解释**：当 Incadronic acid 和 Dexrabeprazole 一起使用时，Incadronic acid 的治疗效果可能会减弱。这可能与 Dexrabeprazole 作为质子泵抑制剂（PPI）有关，PPI 可能影响药物在胃肠道中的吸收，从而减少其疗效。
-- **临床建议**：在同时使用这两种药物时，请密切监测 Incadronic acid 的疗效，可能需要调整剂量或选择不同的药物。
-### 2. Amdinocillin × 未找到记录
-- **相互作用严重程度**：未找到记录
-- **机制解释**：未找到 Amdinocillin 与其他药物的相互作用记录，因此无法提供潜在相互作用的机制。
-- **临床建议**：如需使用 Amdinocillin，请遵循医生的处方和建议。
-### 3. Dexrabeprazole × 未找到记录
-- **相互作用严重程度**：未找到记录
-- **机制解释**：未找到 Dexrabeprazole 与其他药物的相互作用记录，因此无法提供潜在相互作用的机制。
-- **临床建议**：如需使用 Dexrabeprazole，请遵循医生的处方和建议。
-### 免责声明
-请注意，本系统仅供参考，具体用药请遵医嘱。</t>
+- **Severity**: Unknown
+- **Mechanism Explanation**: The therapeutic efficacy of Incadronic acid can be decreased when used in combination with Dexrabeprazole. This interaction may occur because Dexrabeprazole, a proton pump inhibitor (PPI), can alter gastric acidity, which may affect the absorption and effectiveness of Incadronic acid.
+- **Clinical Advice**: If these two medications are to be used together, monitor the therapeutic effects of Incadronic acid closely. Consider discussing with your healthcare provider whether dose adjustments are necessary or if alternative treatments might be more suitable.
+### 2. Amdinocillin × Incadronic acid
+- **Severity**: No record found
+- **Mechanism Explanation**: There are no recorded interactions between Amdinocillin and Incadronic acid, indicating that they are generally considered to be safe to use together.
+- **Clinical Advice**: Continue to follow your physician’s recommendations when using these medications concurrently.
+### 3. Amdinocillin × Dexrabeprazole
+- **Severity**: No record found
+- **Mechanism Explanation**: There are no recorded interactions between Amdinocillin and Dexrabeprazole, which suggests they can be safely administered together.
+- **Clinical Advice**: As always, consult your doctor for personalized advice when taking these medications.
+### 4. Dexrabeprazole × Incadronic acid
+- **Severity**: Unknown (repeated entry)
+- **Mechanism Explanation**: This interaction is similar to the one listed above, reiterating that Dexrabeprazole can potentially decrease the efficacy of Incadronic acid.
+- **Clinical Advice**: Monitoring and appropriate adjustments may be necessary when these medications are co-administered.
+### Disclaimer
+Please remember that this system is for reference only—always follow your doctor's advice for the actual medication regimen.</t>
         </is>
       </c>
     </row>
@@ -5996,30 +6753,32 @@
       <c r="D45" t="inlineStr">
         <is>
           <t>I do not have specific interaction data for the combination of Incadronic acid, Amdinocillin, and Dexrabeprazole. However, I can provide some general information:
-1. **Incadronic acid** is a bisphosphonate used for osteoporosis and may have interactions with other medications affecting calcium levels.
-2. **Amdinocillin** is an antibiotic, and while it generally has a low potential for significant drug interactions, it is important to consider the overall health status of the patient and any other medications they may be taking.
-3. **Dexrabeprazole** is a proton pump inhibitor (PPI) that can affect the absorption of certain medications, particularly those that require an acidic environment for optimal absorption.
-While there are no well-documented major interactions among these three drugs, it is always best to consult with a healthcare provider or a clinical pharmacist for personalized advice, especially considering the patient's overall health, other medications, and specific conditions. If you have concerns about specific symptoms or side effects, please discuss them with a healthcare professional.</t>
+1. **Incadronic acid** is a bisphosphonate used for conditions like osteoporosis.
+2. **Amdinocillin** is an antibiotic, and while I don't have specific information on it, antibiotics can sometimes interact with other medications.
+3. **Dexrabeprazole** is a proton pump inhibitor (PPI) used to reduce stomach acid.
+Generally, PPIs like Dexrabeprazole can affect the absorption of certain medications, including some antibiotics, but the specific interaction with Amdinocillin is not well-documented.
+Since I do not have reliable information on the specific interactions between these three drugs, I recommend consulting a healthcare professional or a clinical pharmacist for personalized advice. They can provide the most accurate and safe recommendations based on your health status and medication profile.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>根据提供的信息，以下是对药物组合 Incadronic acid（因卡德酸）、Amdinocillin（阿莫西林）和 Dexrabeprazole（德克拉贝拉唑）的相互作用评估：
-### 药物间相互作用
+          <t>### 药物间相互作用评估
 1. **Incadronic acid × Dexrabeprazole**
    - **严重程度**：Unknown
    - **描述**：使用 Dexrabeprazole 时，Incadronic acid 的治疗效果可能会降低。
 2. **Dexrabeprazole × Incadronic acid**
    - **严重程度**：Unknown
    - **描述**：使用 Dexrabeprazole 时，Incadronic acid 的治疗效果可能会降低。
+3. **Amdinocillin**
+   - **与 Incadronic acid 和 Dexrabeprazole 的相互作用**：**未找到记录**。
 ### 食物禁忌
 - **未找到记录**。
 ### 机制解释
-Dexrabeprazole 是一种质子泵抑制剂（PPI），能够减少胃酸的产生。当与 Incadronic acid 联用时，Dexrabeprazole 可能会影响因卡德酸在胃肠道的吸收，从而降低其疗效。虽然数据库中未记录相互作用的严重程度，但这种影响是可能的。
+Dexrabeprazole 作为一种质子泵抑制剂，可减少胃酸的分泌。其使用可能导致 Incadronic acid 在胃肠道的吸收减少，因此降低其疗效。虽然没有记录具体的相互作用严重程度，但这种影响是值得注意的。
 ### 临床建议
-1. **评估必要性**：如果必须同时使用这三种药物，请咨询医生或药师，以评估 Incadronic acid 的疗效是否可能受到影响。
-2. **监测疗效**：在使用期间，定期监测 Incadronic acid 的疗效，必要时调整用药方案。
-3. **医生指导**：始终遵从医师的建议，任何更改或组合用药都应在专业医疗人员的指导下进行。
+1. **咨询医生**：在考虑同时使用这三种药物时，请务必咨询您的医生，以确保这种组合是安全的并且是必要的。
+2. **监测疗效**：在用药期间定期评估 Incadronic acid 的疗效，必要时进行调整。
+3. **遵循处方**：切勿私自调整药物剂量或停止用药，始终在专业医疗人员的指导下行动。
 ### 免责声明
 请注意，本系统仅供参考，具体用药请遵循您医生的处方和建议。</t>
         </is>
@@ -6043,29 +6802,27 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Based on the information available up to October 2023, here are the potential interactions for the drugs you mentioned:
-1. **Incadronic Acid**: There are no well-documented major drug interactions with Incadronic acid. However, it is always important to monitor for any unusual symptoms or side effects.
-2. **Amdinocillin**: Amdinocillin is a penicillin antibiotic, and it generally has a low potential for significant drug interactions. However, it can interact with other medications that affect renal function or with other antibiotics, so monitoring is advised.
-3. **Levofloxacin**: Levofloxacin can have interactions with certain medications, particularly those that prolong the QT interval (like some antiarrhythmics) and those that affect renal function. It is also important to note that Levofloxacin can interact with antacids, sucralfate, and other products containing magnesium, aluminum, or calcium, which can reduce its absorption.
-**Overall Interaction Assessment**: 
-- There are no major interactions specifically between Incadronic acid, Amdinocillin, and Levofloxacin. However, caution should be exercised with Levofloxacin regarding its interactions with other medications that may affect its absorption or renal function.
-It is always best to consult with your healthcare provider or pharmacist for personalized advice, especially considering your complete medication profile and health status.</t>
+          <t>Based on the information available up to October 2023, here are the potential interactions among Incadronic acid, Amdinocillin, and Levofloxacin:
+1. **Incadronic Acid and Levofloxacin**: There are no significant interactions reported between Incadronic acid and Levofloxacin. However, it is always advisable to monitor for any unusual side effects when taking these medications together.
+2. **Amdinocillin and Levofloxacin**: There are no major interactions reported between Amdinocillin and Levofloxacin. Both are antibiotics but belong to different classes, and they do not typically interfere with each other's efficacy.
+3. **Incadronic Acid and Amdinocillin**: There are no significant interactions reported between Incadronic acid and Amdinocillin.
+Overall, the combination of these three medications does not appear to have major interactions. However, it is essential to consult with your healthcare provider or pharmacist for personalized advice, especially considering your overall health condition and any other medications you may be taking. Always report any unusual symptoms or side effects to your healthcare provider.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>根据您提供的信息，以下是您正在使用的药物组合的相互作用分析：
-### 药物组合: Levofloxacin 和 Amdinocillin
+### 药物组合: **Levofloxacin 和 Amdinocillin**
 - **相互作用严重程度**：Moderate
 - **机制解释**：当 Levofloxacin 与 Amdinocillin 同时使用时，Levofloxacin 的血清浓度可能会增加。这可能是由于 Amdinocillin 影响了体内对 Levofloxacin 的代谢或排泄，从而导致其水平上升。
 - **临床建议**：在使用这两种药物时，应监测 Levofloxacin 的效果和副作用。如果出现不寻常的症状或 Levofloxacin 的副作用加重，请及时咨询医生。
-### 药物组合: Incadronic acid 和 Levofloxacin
+### 药物组合: **Incadronic acid 和 Levofloxacin**
 - **相互作用记录**：未找到记录。
-### 药物组合: Incadronic acid 和 Amdinocillin
+### 药物组合: **Incadronic acid 和 Amdinocillin**
 - **相互作用记录**：未找到记录。
 ### 总结
-- 主要关注 Levofloxacin 和 Amdinocillin 之间的中度相互作用，建议进行监测。
-- 关于 Incadronic acid 与其他两种药物之间，没有记录任何相互作用。
+- 主要关注 **Levofloxacin 和 Amdinocillin** 之间的中度相互作用，建议进行监测。
+- 关于 **Incadronic acid** 与其他两种药物之间，没有记录任何相互作用。
 ### 免责声明
 请注意，本系统仅供参考，具体用药请遵医嘱。如果有任何疑问或症状，请务必咨询您的医生或药师。</t>
         </is>
@@ -6090,28 +6847,28 @@
       <c r="D47" t="inlineStr">
         <is>
           <t>I do not have specific information on interactions between Incadronic acid, Amdinocillin, and Levofloxacin. However, I can provide some general information about each drug:
-1. **Incadronic acid**: This is a bisphosphonate used primarily for the treatment of osteoporosis. It is important to monitor for potential interactions with other medications that affect calcium levels or renal function.
-2. **Amdinocillin**: This is a penicillin antibiotic. It is generally well-tolerated, but it can interact with other medications that affect renal function or that are also metabolized by the liver.
-3. **Levofloxacin**: This is a fluoroquinolone antibiotic. It can have interactions with medications that affect QT interval, as well as those that affect renal function.
-While I cannot provide specific interaction data for the combination of these three drugs, it is always important to consider the overall clinical context, including renal function and any other medications the patient may be taking. For specific interaction information, consulting a drug interaction database or a healthcare professional is recommended.</t>
+1. **Incadronic acid**: This is a bisphosphonate used primarily for the treatment of osteoporosis. It is not commonly associated with many drug interactions, but caution is advised when used with other medications that affect calcium levels.
+2. **Amdinocillin**: This is a penicillin antibiotic. It can interact with other medications that affect renal function or that are also nephrotoxic. It is important to monitor for potential additive effects when used with other antibiotics or medications that may affect the gut flora.
+3. **Levofloxacin**: This is a fluoroquinolone antibiotic. It has known interactions with certain medications, particularly those that prolong the QT interval, as well as with antacids, sucralfate, and other products containing divalent or trivalent cations, which can reduce its absorption.
+Given the lack of specific interaction data for the combination of these three drugs, I recommend consulting a healthcare professional or a drug interaction database for the most accurate and personalized information. Always consider the patient's overall health status and other medications they may be taking.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>以下是关于 Incadronic acid、Amdinocillin 和 Levofloxacin 之间的潜在相互作用的回答：
-### 药物相互作用
+          <t>Here are the potential interactions between Incadronic acid, Amdinocillin, and Levofloxacin:
+### Drug Interactions
 1. **Levofloxacin × Amdinocillin**
-   - **严重程度**：Moderate
-   - **机制解释**：当 Levofloxacin 与 Amdinocillin 同时使用时，Levofloxacin 的血浆浓度可能会升高。这是因为 Amdinocillin 可能影响 Levofloxacin 的代谢或排泄，导致后者在体内的浓度增加。
-   - **临床建议**：在联合使用这两种药物时，应监测 Levofloxacin 的疗效和副作用，必要时调整剂量。
+   - **Severity**: Moderate
+   - **Mechanism Explanation**: The serum concentration of Levofloxacin can be increased when it is combined with Amdinocillin. This interaction may occur because Amdinocillin can affect the metabolism or excretion of Levofloxacin, leading to higher levels of Levofloxacin in the bloodstream.
+   - **Clinical Advice**: Monitor the clinical effects and side effects of Levofloxacin closely when used with Amdinocillin. Adjustments in dosing may be necessary based on the patient's response.
 2. **Amdinocillin × Levofloxacin**
-   - **严重程度**：Moderate
-   - **机制解释**：同样，Amdinocillin 的使用可能增加 Levofloxacin 的血浆浓度，因此类同于上述机制。
-   - **临床建议**：如上所述，在使用这两种药物时，需要定期监测 Levofloxacin 相关的疗效与副作用。
+   - **Severity**: Moderate
+   - **Mechanism Explanation**: Similar to the above, the combined use of Amdinocillin can increase the serum concentration of Levofloxacin, which may result from alterations in the drug's metabolism or elimination process.
+   - **Clinical Advice**: Follow the same recommendations as mentioned; close monitoring of Levofloxacin for efficacy and side effects is advised when it is used concurrently with Amdinocillin.
 3. **Incadronic acid**
-   - **未找到记录**：数据库中没有找到 Incadronic acid 与 Amdinocillin 或 Levofloxacin 之间的相互作用记录。
-### 免责声明
-请注意，本系统仅供参考，具体用药请遵医嘱。</t>
+   - **No record found**: There are no interaction records for Incadronic acid with Amdinocillin or Levofloxacin in the database.
+### Disclaimer
+This system is for reference only; please follow your doctor's advice for actual medication.</t>
         </is>
       </c>
     </row>
@@ -6134,27 +6891,27 @@
       <c r="D48" t="inlineStr">
         <is>
           <t>I do not have specific information on the interaction between Incadronic acid, Amdinocillin, and Levofloxacin. However, I can provide some general guidance:
-1. **Incadronic acid**: This is a bisphosphonate used primarily for osteoporosis. It generally has a low potential for drug interactions.
-2. **Amdinocillin**: This is a penicillin antibiotic. It can interact with other medications, particularly those that affect renal function or other antibiotics.
-3. **Levofloxacin**: This is a fluoroquinolone antibiotic. It has known interactions with certain medications, particularly those that can affect QT interval or renal function.
-While there may not be direct major interactions among these three drugs, the combination of multiple antibiotics can sometimes lead to increased risk of side effects or reduced efficacy. It is always best to consult with a healthcare provider or a clinical pharmacist for a thorough review of your specific situation, including any other medications you may be taking, your health status, and potential risks.
-If you have any specific concerns or symptoms, please reach out to a healthcare professional.</t>
+1. **Incadronic acid** is a bisphosphonate used primarily for osteoporosis and may have specific interactions with other medications, particularly those affecting calcium levels.
+2. **Amdinocillin** is a penicillin antibiotic, and while it generally has a good safety profile, it can interact with other medications that affect renal function or that are also nephrotoxic.
+3. **Levofloxacin** is a fluoroquinolone antibiotic that can have interactions with other drugs, particularly those that prolong the QT interval or affect the central nervous system.
+Given the potential for interactions, especially with antibiotics and bisphosphonates, it is crucial to consult a healthcare professional or a clinical pharmacist for a thorough review of your specific situation, including any other medications you may be taking, your health status, and any underlying conditions.
+In summary, without specific interaction data, I cannot definitively say whether it is safe to take these medications together. Please consult a healthcare provider for personalized advice.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>根据提供的药物信息，以下是对您提问的药物组合的相互作用分析：
-### 药物组合相互作用
+          <t>Based on the drug interaction information available, here is the analysis regarding the safety of taking Incadronic acid, Amdinocillin, and Levofloxacin together:
+### Drug Interaction Analysis
 1. **Amdinocillin × Levofloxacin**
-   - **严重程度**：Moderate
-   - **机制解释**：当 Amdinocillin 与 Levofloxacin 同时使用时，Levofloxacin 的血清浓度可能会增加。这可能是因为 Amdinocillin 影响了 Levofloxacin 的代谢或排泄，使其在体内持续时间更长。
-   - **临床建议**：在同时使用这两种药物时，建议监测 Levofloxacin 的血清浓度，必要时调整剂量或者选择其他抗生素以避免副作用。
-### 其他药物信息
-- **Incadronic acid**：目前未查询到与 Amdinocillin 或 Levofloxacin 之间的直接相互作用记录。因此可以认为在这三种药物中，仅 Amdinocillin 与 Levofloxacin 之间存在显著的相互作用。
-### 结论
-虽然 Incadronic acid 目前未显示与 Amdinocillin 和 Levofloxacin 之间的直接相互作用，但由于 Amdinocillin 和 Levofloxacin 之间的交互可能会影响 Levofloxacin 的浓度，建议在使用这些药物时咨询您的医生或药师以确保使用安全。
-### 免责声明
-请注意，本系统提供的信息仅供参考，具体用药请遵循医嘱。</t>
+   - **Severity**: Moderate
+   - **Mechanism Explanation**: When Amdinocillin is used with Levofloxacin, the serum concentration of Levofloxacin can be increased. This is likely due to Amdinocillin affecting the metabolism or excretion of Levofloxacin, leading to its prolonged presence in the body.
+   - **Clinical Advice**: Monitor the serum concentration of Levofloxacin when taken with Amdinocillin. Consider dosage adjustments or alternative medications to avoid potential side effects.
+2. **Incadronic Acid**: 
+   - **Interactivity**: No record found regarding interactions with Amdinocillin or Levofloxacin.
+### Conclusion
+While there is a moderate interaction between Amdinocillin and Levofloxacin that could affect Levofloxacin levels, there is no known interaction involving Incadronic acid. However, combined use of Amdinocillin and Levofloxacin warrants caution, and it's advisable to consult with your healthcare provider regarding the safety of taking all three medications together.
+### Disclaimer
+Please remember that this information is for reference only; always follow your doctor's advice for actual medication use.</t>
         </is>
       </c>
     </row>
@@ -6177,35 +6934,33 @@
       <c r="D49" t="inlineStr">
         <is>
           <t>Based on the information available up to October 2023, here are the potential interactions for the drugs you mentioned:
-1. **Incadronic Acid**: There are no well-documented major drug interactions with Incadronic acid. However, it is always important to monitor for any unusual symptoms or side effects.
+1. **Incadronic Acid**: There are no well-documented major drug interactions with Incadronic acid. However, it is always important to monitor for any unusual symptoms or changes in health status.
 2. **Amdinocillin**: Amdinocillin is a penicillin antibiotic, and it generally has a low potential for significant drug interactions. However, it can interact with other medications that affect renal function or that are also nephrotoxic.
-3. **Omadacycline**: Omadacycline is a tetracycline antibiotic, and it can interact with certain medications, particularly those that affect the absorption of tetracyclines (like antacids, iron supplements, and calcium supplements). 
-**Overall Interaction Assessment**: 
-- There are no major interactions reported between these three medications. However, it is crucial to consider the individual patient's health status, other medications, and any underlying conditions.
-- Always consult with a healthcare provider or pharmacist for personalized advice, especially if you are taking other medications or have specific health concerns.
-If you have any specific symptoms or concerns, please discuss them with your healthcare provider.</t>
+3. **Omadacycline**: Omadacycline is a tetracycline antibiotic, and it can have interactions with other medications, particularly those that affect the absorption of tetracyclines (such as antacids, iron supplements, and calcium supplements). 
+When combining these three medications, there are no major interactions specifically noted among them. However, it is crucial to consider the overall clinical context, including renal function and any other medications you may be taking.
+Always consult with your healthcare provider or a clinical pharmacist for personalized advice and to ensure safe medication use.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>以下是您所提到的药物组合的相互作用信息：
-### 药物组合：Amdinocillin × Omadacycline
-- **严重程度**：未知
-- **描述**：与Omadacycline联合使用时，Amdinocillin的治疗效果可能会降低。
-- **机制解释**：这可能是因为这两种药物作用于细菌以不同的机制，无效的联合使用可能会导致Amdinocillin的抗菌活性下降。
-- **临床建议**：建议在使用这两种药物时特别注意，医生可能需要根据您的病情调整药物使用策略。
-### 药物组合：Omadacycline × Amdinocillin
-- **严重程度**：未知
-- **描述**：与Amdinocillin联合使用时，Omadacycline的治疗效果可能会降低，具体表现为降低Amdinocillin的疗效。
-- **机制解释**：同上，药物可能在体内以不同的不兼容方式作用于细菌，导致效果降低。
-- **临床建议**：与上述建议相同，建议与医生讨论调整药物使用的可能性。
-### 其他用药注意事项：
-- **Omadacycline的食物禁忌**：
-  - 避免与多价阳离子同时服用，至少在服用Omadacycline后等待4小时再服用含有锌、钙、镁和铁等物质的药物。
-  - Omadacycline应在空腹状态下服用，服用前4小时和服用后2小时内不宜进食。饮水是可以的。
-  - 与抗酸药物分开服用，至少要在Omadacycline服用后等待4小时再服用抗酸药。
-### 免责声明
-请注意，本系统仅供参考，具体用药请遵医嘱。对于您的健康状况，建议与医生详细讨论，确保用药安全和有效。</t>
+          <t>### Drug Interactions
+#### 1. Amdinocillin × Omadacycline
+- **Severity**: Unknown
+- **Description**: The therapeutic efficacy of Amdinocillin can be decreased when used in combination with Omadacycline.
+- **Mechanism Explanation**: This interaction may occur because these drugs can affect the bacteria they target in incompatible ways, potentially leading to a reduced effectiveness of Amdinocillin.
+- **Clinical Advice**: It is advisable to discuss this combination with your healthcare provider. They may need to adjust your medication regimen based on your specific situation and health conditions.
+#### 2. Omadacycline × Amdinocillin
+- **Severity**: Unknown
+- **Description**: The therapeutic efficacy of Amdinocillin can be decreased when used in combination with Omadacycline.
+- **Mechanism Explanation**: Same as above; the interactions between these antibiotics may diminish the effectiveness of treatment.
+- **Clinical Advice**: Consult your doctor regarding the use of these two medications together and whether an alternative approach is necessary.
+### Additional Considerations for Omadacycline
+- **Food Interactions**:
+  - Avoid taking multivalent ions (e.g., zinc, calcium, magnesium, and iron) within 4 hours after taking Omadacycline.
+  - Omadacycline should be taken on an empty stomach, with no food for 4 hours before and 2 hours after administration. Drinking water is acceptable after taking it.
+  - Separate from antacids; wait at least 4 hours after taking Omadacycline to take antacids.
+### Disclaimer
+This system is for reference only. Please follow your doctor's advice for actual medication. Always consult your healthcare professional regarding any medication-related questions or adjustments.</t>
         </is>
       </c>
     </row>
@@ -6227,31 +6982,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>As of my last training data up to October 2023, I do not have specific information regarding interactions between Incadronic acid, Amdinocillin, and Omadacycline. 
+          <t>I do not have specific information on interactions between Incadronic acid, Amdinocillin, and Omadacycline. 
 - **Incadronic acid** is a bisphosphonate used primarily for the treatment of osteoporosis.
 - **Amdinocillin** is a penicillin antibiotic.
 - **Omadacycline** is a tetracycline antibiotic.
-While I can provide general information about potential interactions, the specific combination of these three drugs has not been well-documented in the literature available to me. 
-For the most accurate and up-to-date information, I recommend consulting a healthcare professional or a drug interaction database. Always consider the patient's overall health status, other medications, and specific clinical circumstances when evaluating potential drug interactions.</t>
+While I can provide general information about potential interactions, the specific combination of these three drugs does not have well-documented interactions in the available literature. 
+For the most accurate and personalized information, it is always best to consult a healthcare professional or a clinical pharmacist who can evaluate the patient's complete medication profile and health status.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>以下是 Incadronic acid、Amdinocillin 和 Omadacycline 之间的潜在相互作用：
+          <t>Here are the potential interactions between Incadronic acid, Amdinocillin, and Omadacycline:
 ### 1. Amdinocillin × Omadacycline
-- **严重程度**：未知 (Unknown)
-- **机制解释**：当 Amdinocillin 与 Omadacycline 同时使用时，Amdinocillin 的治疗效果可能会减弱。这可能是因为两种药物在作用机制上相互抵消或竞争，导致 Amdinocillin 的抗菌活性降低。
-- **临床建议**：建议在使用这两种药物时进行仔细监测，并根据患者的反应调整疗程，如果有必要，考虑分开给药或避免联合使用。
+- **Severity**: Unknown
+- **Mechanism Explanation**: The therapeutic efficacy of Amdinocillin can be decreased when used in combination with Omadacycline. This may occur because both drugs could be affecting the same bacterial targets or pathways, which could lead to reduced effectiveness of Amdinocillin.
+- **Clinical Advice**: It is advisable to monitor the patient's response closely if these two medications are used together, and consider separating the dosing schedule or avoiding the combination if appropriate.
 ### 2. Omadacycline × Amdinocillin
-- **严重程度**：未知 (Unknown)
-- **机制解释**：与上述情况相同，Omadacycline 可能会对 Amdinocillin 的效果产生影响，降低其疗效。
-- **临床建议**：同样，监测患者反应是必要的，并根据实际情况调整用药方案。
+- **Severity**: Unknown
+- **Mechanism Explanation**: Similar to the first point, the efficacy of Amdinocillin may be diminished when administered alongside Omadacycline. The interaction could involve competition at the bacterial level or other pharmacodynamic factors that reduce Amdinocillin's effectiveness.
+- **Clinical Advice**: Close monitoring of the patient is recommended when these medications are co-prescribed, along with possible adjustments to therapy as needed.
 ### 3. Incadronic acid
-- **严重程度**：未找到记录
-- **机制解释**：当前无关于 Incadronic acid 与其他药物的相互作用记录。这可能意味着它与 Amdinocillin 和 Omadacycline 没有已知的交互影响。
-- **临床建议**：在使用 Incadronic acid 的同时，与 Amdinocillin 或 Omadacycline 的联合应用应遵医嘱，确保安全性。
-### 免责声明
-上面的信息仅供参考，具体用药请遵医嘱。如有任何不适或用药问题，请咨询专业医师。</t>
+- **Severity**: No record found
+- **Mechanism Explanation**: There are currently no records of any interactions between Incadronic acid and the other two medications (Amdinocillin and Omadacycline). This suggests that Incadronic acid may not have any known adverse interactions when used with these antibiotics.
+- **Clinical Advice**: While there are no documented interactions, always ensure to follow the prescribing healthcare provider’s recommendations when using Incadronic acid alongside any other medications.
+### Disclaimer
+The information provided is for reference only. Always follow your doctor's advice regarding medication use and potential interactions.</t>
         </is>
       </c>
     </row>
@@ -6273,27 +7028,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>I do not have specific information on the interaction between Incadronic acid, Amdinocillin, and Omadacycline. It is important to consult a healthcare professional or a clinical pharmacist for personalized advice regarding drug interactions, as they can provide the most accurate and up-to-date information based on your individual health situation.</t>
+          <t>I do not have specific information on the interaction between Incadronic acid, Amdinocillin, and Omadacycline. Therefore, I cannot provide a definitive answer regarding the safety of taking these medications together. It is essential to consult a healthcare professional or a clinical pharmacist for personalized advice and to evaluate potential interactions based on your individual health status and medication profile.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>根据提供的信息，关于这三种药物之间的相互作用，以下是结构化输出：
-### 药物组合相互作用
+          <t>Based on the available information regarding the interactions among Incadronic acid, Amdinocillin, and Omadacycline, here is a structured assessment:
+### Drug Interaction Assessment
 1. **Amdinocillin × Omadacycline**
-   - **严重程度**: Unknown
-   - **机制解释**: 使用Omadacycline与Amdinocillin联合时，Amdinocillin的治疗效果可能会降低。具体机制未明确说明，可能与药物代谢或对细菌的抗菌活性有关。
-   - **临床建议**: 在联合使用这两种药物时，建议监测疗效，可能需要调整剂量或选择其他替代治疗方案。
-2. **Omadacycline × Amdinocillin**
-   - **严重程度**: Unknown
-   - **机制解释**: 同上。
-### Incadronic acid 的相互作用
-- 当前数据中没有查找到 Incadronic acid 与 Amdinocillin 或 Omadacycline 的具体相互作用记录。
-### 结论
-- **未找到记录**: Incadronic acid 与其他药物的特定相互作用未被记录。
-- **总体建议**: 三种药物的联合使用含有未知的相互作用风险，建议在使用时咨询医疗专业人员，遵医嘱服用。
-### 免责声明
-请注意，本系统仅供参考，具体用药请遵医嘱。</t>
+   - **Severity**: Unknown
+   - **Mechanism Explanation**: The therapeutic efficacy of Amdinocillin may be decreased when used in combination with Omadacycline, although the specific mechanism is not detailed. This may involve interactions related to how these drugs are metabolized or their impact on bacterial effectiveness.
+   - **Clinical Advice**: Monitor the effectiveness of Amdinocillin when taken with Omadacycline. Consult with a healthcare provider to assess the potential need for dose adjustments or alternative therapies based on individual clinical circumstances.
+2. **Incadronic acid**
+   - **Severity**: No record found
+   - **Mechanism Explanation**: There is no recorded interaction between Incadronic acid and either Amdinocillin or Omadacycline in the data provided.
+   - **Clinical Advice**: While no specific interactions are noted with Incadronic acid, it is prudent to discuss the concurrent use of these medications with a healthcare provider.
+### Conclusion
+- **Overall Assessment**: The combination of Amdinocillin and Omadacycline has a potential risk of decreasing Amdinocillin's effectiveness. No specific interaction records involving Incadronic acid were found. Consult your healthcare provider for personalized advice before taking these medications together.
+### Disclaimer
+This system is for reference only; please follow your doctor’s advice regarding medication safety and use.</t>
         </is>
       </c>
     </row>
